--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -38088,7 +38088,9 @@
       <c r="O4" s="100" t="n"/>
       <c r="P4" s="22" t="n"/>
       <c r="Q4" s="100" t="n"/>
-      <c r="R4" s="22" t="n"/>
+      <c r="R4" s="22" t="n">
+        <v>95</v>
+      </c>
       <c r="S4" s="100" t="n"/>
       <c r="T4" s="22" t="n"/>
       <c r="U4" s="100" t="n"/>
@@ -38139,7 +38141,7 @@
       <c r="N5" s="22" t="n"/>
       <c r="O5" s="100" t="n"/>
       <c r="P5" s="22" t="n">
-        <v>1744</v>
+        <v>2166</v>
       </c>
       <c r="Q5" s="100" t="n"/>
       <c r="R5" s="22" t="n"/>
@@ -38504,7 +38506,9 @@
       <c r="O12" s="100" t="n">
         <v>1724</v>
       </c>
-      <c r="P12" s="22" t="n"/>
+      <c r="P12" s="22" t="n">
+        <v>36</v>
+      </c>
       <c r="Q12" s="100" t="n"/>
       <c r="R12" s="22" t="n"/>
       <c r="S12" s="100" t="n"/>
@@ -39969,7 +39973,9 @@
       <c r="O41" s="100" t="n"/>
       <c r="P41" s="22" t="n"/>
       <c r="Q41" s="100" t="n"/>
-      <c r="R41" s="22" t="n"/>
+      <c r="R41" s="22" t="n">
+        <v>28</v>
+      </c>
       <c r="S41" s="100" t="n"/>
       <c r="T41" s="22" t="n"/>
       <c r="U41" s="100" t="n"/>
@@ -40275,7 +40281,9 @@
       <c r="O47" s="100" t="n"/>
       <c r="P47" s="22" t="n"/>
       <c r="Q47" s="100" t="n"/>
-      <c r="R47" s="22" t="n"/>
+      <c r="R47" s="22" t="n">
+        <v>4</v>
+      </c>
       <c r="S47" s="100" t="n"/>
       <c r="T47" s="22" t="n"/>
       <c r="U47" s="100" t="n"/>
@@ -49965,7 +49973,9 @@
       <c r="N46" s="61" t="n"/>
       <c r="O46" s="22" t="n"/>
       <c r="P46" s="61" t="n"/>
-      <c r="Q46" s="22" t="n"/>
+      <c r="Q46" s="22" t="n">
+        <v>12</v>
+      </c>
       <c r="R46" s="61" t="n"/>
       <c r="S46" s="22" t="n"/>
       <c r="T46" s="61" t="n"/>
@@ -50027,7 +50037,9 @@
       <c r="P47" s="61" t="n"/>
       <c r="Q47" s="22" t="n"/>
       <c r="R47" s="61" t="n"/>
-      <c r="S47" s="22" t="n"/>
+      <c r="S47" s="22" t="n">
+        <v>80</v>
+      </c>
       <c r="T47" s="61" t="n"/>
       <c r="U47" s="22" t="n"/>
       <c r="V47" s="61" t="n"/>
@@ -50311,7 +50323,9 @@
       <c r="R52" s="61" t="n">
         <v>88</v>
       </c>
-      <c r="S52" s="22" t="n"/>
+      <c r="S52" s="22" t="n">
+        <v>289</v>
+      </c>
       <c r="T52" s="61" t="n"/>
       <c r="U52" s="22" t="n"/>
       <c r="V52" s="61" t="n"/>
@@ -53227,7 +53241,9 @@
       <c r="N104" s="61" t="n"/>
       <c r="O104" s="22" t="n"/>
       <c r="P104" s="61" t="n"/>
-      <c r="Q104" s="22" t="n"/>
+      <c r="Q104" s="22" t="n">
+        <v>31</v>
+      </c>
       <c r="R104" s="61" t="n"/>
       <c r="S104" s="22" t="n"/>
       <c r="T104" s="61" t="n"/>
@@ -54471,7 +54487,9 @@
       <c r="P126" s="61" t="n"/>
       <c r="Q126" s="22" t="n"/>
       <c r="R126" s="61" t="n"/>
-      <c r="S126" s="22" t="n"/>
+      <c r="S126" s="22" t="n">
+        <v>45</v>
+      </c>
       <c r="T126" s="61" t="n"/>
       <c r="U126" s="22" t="n"/>
       <c r="V126" s="61" t="n"/>
@@ -55367,7 +55385,9 @@
       </c>
       <c r="Q142" s="22" t="n"/>
       <c r="R142" s="61" t="n"/>
-      <c r="S142" s="22" t="n"/>
+      <c r="S142" s="22" t="n">
+        <v>30</v>
+      </c>
       <c r="T142" s="61" t="n"/>
       <c r="U142" s="22" t="n"/>
       <c r="V142" s="61" t="n"/>
@@ -56481,7 +56501,9 @@
       <c r="P162" s="61" t="n"/>
       <c r="Q162" s="22" t="n"/>
       <c r="R162" s="61" t="n"/>
-      <c r="S162" s="22" t="n"/>
+      <c r="S162" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="T162" s="61" t="n"/>
       <c r="U162" s="22" t="n"/>
       <c r="V162" s="61" t="n"/>
@@ -57259,7 +57281,9 @@
       <c r="N176" s="61" t="n"/>
       <c r="O176" s="22" t="n"/>
       <c r="P176" s="61" t="n"/>
-      <c r="Q176" s="22" t="n"/>
+      <c r="Q176" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="R176" s="61" t="n"/>
       <c r="S176" s="22" t="n"/>
       <c r="T176" s="61" t="n"/>
@@ -57767,7 +57791,9 @@
       <c r="P185" s="61" t="n"/>
       <c r="Q185" s="22" t="n"/>
       <c r="R185" s="61" t="n"/>
-      <c r="S185" s="22" t="n"/>
+      <c r="S185" s="22" t="n">
+        <v>198</v>
+      </c>
       <c r="T185" s="61" t="n"/>
       <c r="U185" s="22" t="n"/>
       <c r="V185" s="61" t="n"/>
@@ -61823,7 +61849,9 @@
       <c r="P257" s="61" t="n"/>
       <c r="Q257" s="22" t="n"/>
       <c r="R257" s="61" t="n"/>
-      <c r="S257" s="22" t="n"/>
+      <c r="S257" s="22" t="n">
+        <v>210</v>
+      </c>
       <c r="T257" s="61" t="n"/>
       <c r="U257" s="22" t="n"/>
       <c r="V257" s="61" t="n"/>
@@ -63849,7 +63877,9 @@
       <c r="P293" s="61" t="n"/>
       <c r="Q293" s="22" t="n"/>
       <c r="R293" s="61" t="n"/>
-      <c r="S293" s="22" t="n"/>
+      <c r="S293" s="22" t="n">
+        <v>34</v>
+      </c>
       <c r="T293" s="61" t="n"/>
       <c r="U293" s="22" t="n"/>
       <c r="V293" s="61" t="n"/>
@@ -65851,7 +65881,9 @@
       <c r="P329" s="61" t="n"/>
       <c r="Q329" s="22" t="n"/>
       <c r="R329" s="61" t="n"/>
-      <c r="S329" s="22" t="n"/>
+      <c r="S329" s="22" t="n">
+        <v>168</v>
+      </c>
       <c r="T329" s="61" t="n"/>
       <c r="U329" s="22" t="n"/>
       <c r="V329" s="61" t="n"/>
@@ -66075,7 +66107,9 @@
       <c r="P333" s="61" t="n"/>
       <c r="Q333" s="22" t="n"/>
       <c r="R333" s="61" t="n"/>
-      <c r="S333" s="22" t="n"/>
+      <c r="S333" s="22" t="n">
+        <v>40</v>
+      </c>
       <c r="T333" s="61" t="n"/>
       <c r="U333" s="22" t="n"/>
       <c r="V333" s="61" t="n"/>
@@ -66129,7 +66163,9 @@
       </c>
       <c r="O334" s="22" t="n"/>
       <c r="P334" s="61" t="n"/>
-      <c r="Q334" s="22" t="n"/>
+      <c r="Q334" s="22" t="n">
+        <v>88</v>
+      </c>
       <c r="R334" s="61" t="n"/>
       <c r="S334" s="22" t="n"/>
       <c r="T334" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -38560,7 +38560,9 @@
       </c>
       <c r="P13" s="22" t="n"/>
       <c r="Q13" s="100" t="n"/>
-      <c r="R13" s="22" t="n"/>
+      <c r="R13" s="22" t="n">
+        <v>152</v>
+      </c>
       <c r="S13" s="100" t="n"/>
       <c r="T13" s="22" t="n"/>
       <c r="U13" s="100" t="n"/>
@@ -48397,7 +48399,9 @@
       <c r="R18" s="61" t="n"/>
       <c r="S18" s="22" t="n"/>
       <c r="T18" s="61" t="n"/>
-      <c r="U18" s="22" t="n"/>
+      <c r="U18" s="22" t="n">
+        <v>46</v>
+      </c>
       <c r="V18" s="61" t="n"/>
       <c r="W18" s="22" t="n"/>
       <c r="X18" s="61" t="n"/>
@@ -49131,7 +49135,9 @@
       </c>
       <c r="S31" s="22" t="n"/>
       <c r="T31" s="61" t="n"/>
-      <c r="U31" s="22" t="n"/>
+      <c r="U31" s="22" t="n">
+        <v>26</v>
+      </c>
       <c r="V31" s="61" t="n"/>
       <c r="W31" s="22" t="n"/>
       <c r="X31" s="61" t="n"/>
@@ -55445,7 +55451,9 @@
       <c r="R143" s="61" t="n"/>
       <c r="S143" s="22" t="n"/>
       <c r="T143" s="61" t="n"/>
-      <c r="U143" s="22" t="n"/>
+      <c r="U143" s="22" t="n">
+        <v>3</v>
+      </c>
       <c r="V143" s="61" t="n"/>
       <c r="W143" s="22" t="n"/>
       <c r="X143" s="61" t="n"/>
@@ -55557,7 +55565,9 @@
       <c r="R145" s="61" t="n"/>
       <c r="S145" s="22" t="n"/>
       <c r="T145" s="61" t="n"/>
-      <c r="U145" s="22" t="n"/>
+      <c r="U145" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="V145" s="61" t="n"/>
       <c r="W145" s="22" t="n"/>
       <c r="X145" s="61" t="n"/>
@@ -64327,7 +64337,9 @@
       <c r="R301" s="61" t="n"/>
       <c r="S301" s="22" t="n"/>
       <c r="T301" s="61" t="n"/>
-      <c r="U301" s="22" t="n"/>
+      <c r="U301" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="V301" s="61" t="n"/>
       <c r="W301" s="22" t="n"/>
       <c r="X301" s="61" t="n"/>
@@ -66285,7 +66297,9 @@
       <c r="R336" s="61" t="n"/>
       <c r="S336" s="22" t="n"/>
       <c r="T336" s="61" t="n"/>
-      <c r="U336" s="22" t="n"/>
+      <c r="U336" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="V336" s="61" t="n"/>
       <c r="W336" s="22" t="n"/>
       <c r="X336" s="61" t="n"/>
@@ -66341,7 +66355,9 @@
       <c r="R337" s="61" t="n"/>
       <c r="S337" s="22" t="n"/>
       <c r="T337" s="61" t="n"/>
-      <c r="U337" s="22" t="n"/>
+      <c r="U337" s="22" t="n">
+        <v>22</v>
+      </c>
       <c r="V337" s="61" t="n"/>
       <c r="W337" s="22" t="n"/>
       <c r="X337" s="61" t="n"/>
@@ -67575,7 +67591,9 @@
       <c r="R359" s="61" t="n"/>
       <c r="S359" s="22" t="n"/>
       <c r="T359" s="61" t="n"/>
-      <c r="U359" s="22" t="n"/>
+      <c r="U359" s="22" t="n">
+        <v>9</v>
+      </c>
       <c r="V359" s="61" t="n"/>
       <c r="W359" s="22" t="n"/>
       <c r="X359" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -38564,7 +38564,9 @@
         <v>152</v>
       </c>
       <c r="S13" s="100" t="n"/>
-      <c r="T13" s="22" t="n"/>
+      <c r="T13" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="U13" s="100" t="n"/>
       <c r="V13" s="22" t="n"/>
       <c r="W13" s="100" t="n"/>
@@ -48683,7 +48685,9 @@
       <c r="R23" s="61" t="n"/>
       <c r="S23" s="22" t="n"/>
       <c r="T23" s="61" t="n"/>
-      <c r="U23" s="22" t="n"/>
+      <c r="U23" s="22" t="n">
+        <v>93</v>
+      </c>
       <c r="V23" s="61" t="n"/>
       <c r="W23" s="22" t="n"/>
       <c r="X23" s="61" t="n"/>
@@ -50333,7 +50337,9 @@
         <v>289</v>
       </c>
       <c r="T52" s="61" t="n"/>
-      <c r="U52" s="22" t="n"/>
+      <c r="U52" s="22" t="n">
+        <v>132</v>
+      </c>
       <c r="V52" s="61" t="n"/>
       <c r="W52" s="22" t="n"/>
       <c r="X52" s="61" t="n"/>
@@ -50725,7 +50731,9 @@
       <c r="T59" s="61" t="n">
         <v>93</v>
       </c>
-      <c r="U59" s="22" t="n"/>
+      <c r="U59" s="22" t="n">
+        <v>5</v>
+      </c>
       <c r="V59" s="61" t="n"/>
       <c r="W59" s="22" t="n"/>
       <c r="X59" s="61" t="n"/>
@@ -57863,7 +57871,9 @@
       <c r="R186" s="61" t="n"/>
       <c r="S186" s="22" t="n"/>
       <c r="T186" s="61" t="n"/>
-      <c r="U186" s="22" t="n"/>
+      <c r="U186" s="22" t="n">
+        <v>634</v>
+      </c>
       <c r="V186" s="61" t="n"/>
       <c r="W186" s="22" t="n"/>
       <c r="X186" s="61" t="n"/>
@@ -59889,7 +59899,9 @@
       <c r="R222" s="61" t="n"/>
       <c r="S222" s="22" t="n"/>
       <c r="T222" s="61" t="n"/>
-      <c r="U222" s="22" t="n"/>
+      <c r="U222" s="22" t="n">
+        <v>1119</v>
+      </c>
       <c r="V222" s="61" t="n"/>
       <c r="W222" s="22" t="n"/>
       <c r="X222" s="61" t="n"/>
@@ -64507,7 +64519,9 @@
       </c>
       <c r="S304" s="22" t="n"/>
       <c r="T304" s="61" t="n"/>
-      <c r="U304" s="22" t="n"/>
+      <c r="U304" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="V304" s="61" t="n"/>
       <c r="W304" s="22" t="n"/>
       <c r="X304" s="61" t="n"/>
@@ -66527,7 +66541,9 @@
       </c>
       <c r="S340" s="22" t="n"/>
       <c r="T340" s="61" t="n"/>
-      <c r="U340" s="22" t="n"/>
+      <c r="U340" s="22" t="n">
+        <v>138</v>
+      </c>
       <c r="V340" s="61" t="n"/>
       <c r="W340" s="22" t="n"/>
       <c r="X340" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -38360,7 +38360,9 @@
       <c r="Q9" s="100" t="n"/>
       <c r="R9" s="22" t="n"/>
       <c r="S9" s="100" t="n"/>
-      <c r="T9" s="22" t="n"/>
+      <c r="T9" s="22" t="n">
+        <v>416</v>
+      </c>
       <c r="U9" s="100" t="n"/>
       <c r="V9" s="22" t="n"/>
       <c r="W9" s="100" t="n"/>
@@ -62101,7 +62103,9 @@
       </c>
       <c r="S261" s="22" t="n"/>
       <c r="T261" s="61" t="n"/>
-      <c r="U261" s="22" t="n"/>
+      <c r="U261" s="22" t="n">
+        <v>380</v>
+      </c>
       <c r="V261" s="61" t="n"/>
       <c r="W261" s="22" t="n"/>
       <c r="X261" s="61" t="n"/>
@@ -64237,7 +64241,9 @@
       <c r="R299" s="61" t="n"/>
       <c r="S299" s="22" t="n"/>
       <c r="T299" s="61" t="n"/>
-      <c r="U299" s="22" t="n"/>
+      <c r="U299" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="V299" s="61" t="n"/>
       <c r="W299" s="22" t="n"/>
       <c r="X299" s="61" t="n"/>
@@ -66255,7 +66261,9 @@
       <c r="R335" s="61" t="n"/>
       <c r="S335" s="22" t="n"/>
       <c r="T335" s="61" t="n"/>
-      <c r="U335" s="22" t="n"/>
+      <c r="U335" s="22" t="n">
+        <v>110</v>
+      </c>
       <c r="V335" s="61" t="n"/>
       <c r="W335" s="22" t="n"/>
       <c r="X335" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -48915,7 +48915,9 @@
       <c r="R27" s="61" t="n"/>
       <c r="S27" s="22" t="n"/>
       <c r="T27" s="61" t="n"/>
-      <c r="U27" s="22" t="n"/>
+      <c r="U27" s="22" t="n">
+        <v>55</v>
+      </c>
       <c r="V27" s="61" t="n"/>
       <c r="W27" s="22" t="n"/>
       <c r="X27" s="61" t="n"/>
@@ -48971,7 +48973,9 @@
       <c r="R28" s="61" t="n"/>
       <c r="S28" s="22" t="n"/>
       <c r="T28" s="61" t="n"/>
-      <c r="U28" s="22" t="n"/>
+      <c r="U28" s="22" t="n">
+        <v>52</v>
+      </c>
       <c r="V28" s="61" t="n"/>
       <c r="W28" s="22" t="n"/>
       <c r="X28" s="61" t="n"/>
@@ -49081,7 +49085,9 @@
       </c>
       <c r="Q30" s="22" t="n"/>
       <c r="R30" s="61" t="n"/>
-      <c r="S30" s="22" t="n"/>
+      <c r="S30" s="22" t="n">
+        <v>45</v>
+      </c>
       <c r="T30" s="61" t="n"/>
       <c r="U30" s="22" t="n"/>
       <c r="V30" s="61" t="n"/>
@@ -50281,7 +50287,9 @@
       <c r="T51" s="61" t="n"/>
       <c r="U51" s="22" t="n"/>
       <c r="V51" s="61" t="n"/>
-      <c r="W51" s="22" t="n"/>
+      <c r="W51" s="22" t="n">
+        <v>311</v>
+      </c>
       <c r="X51" s="61" t="n"/>
       <c r="Y51" s="22" t="n"/>
       <c r="Z51" s="61" t="n"/>
@@ -55009,7 +55017,9 @@
       <c r="R135" s="61" t="n"/>
       <c r="S135" s="22" t="n"/>
       <c r="T135" s="61" t="n"/>
-      <c r="U135" s="22" t="n"/>
+      <c r="U135" s="22" t="n">
+        <v>38</v>
+      </c>
       <c r="V135" s="61" t="n"/>
       <c r="W135" s="22" t="n"/>
       <c r="X135" s="61" t="n"/>
@@ -55521,7 +55531,9 @@
       <c r="T144" s="61" t="n"/>
       <c r="U144" s="22" t="n"/>
       <c r="V144" s="61" t="n"/>
-      <c r="W144" s="22" t="n"/>
+      <c r="W144" s="22" t="n">
+        <v>12</v>
+      </c>
       <c r="X144" s="61" t="n"/>
       <c r="Y144" s="22" t="n"/>
       <c r="Z144" s="61" t="n"/>
@@ -55576,7 +55588,7 @@
       <c r="S145" s="22" t="n"/>
       <c r="T145" s="61" t="n"/>
       <c r="U145" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V145" s="61" t="n"/>
       <c r="W145" s="22" t="n"/>
@@ -57027,7 +57039,9 @@
       <c r="R171" s="61" t="n"/>
       <c r="S171" s="22" t="n"/>
       <c r="T171" s="61" t="n"/>
-      <c r="U171" s="22" t="n"/>
+      <c r="U171" s="22" t="n">
+        <v>9</v>
+      </c>
       <c r="V171" s="61" t="n"/>
       <c r="W171" s="22" t="n"/>
       <c r="X171" s="61" t="n"/>
@@ -65079,7 +65093,9 @@
       </c>
       <c r="S314" s="22" t="n"/>
       <c r="T314" s="61" t="n"/>
-      <c r="U314" s="22" t="n"/>
+      <c r="U314" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="V314" s="61" t="n"/>
       <c r="W314" s="22" t="n"/>
       <c r="X314" s="61" t="n"/>
@@ -65301,7 +65317,9 @@
       </c>
       <c r="S318" s="22" t="n"/>
       <c r="T318" s="61" t="n"/>
-      <c r="U318" s="22" t="n"/>
+      <c r="U318" s="22" t="n">
+        <v>4</v>
+      </c>
       <c r="V318" s="61" t="n"/>
       <c r="W318" s="22" t="n"/>
       <c r="X318" s="61" t="n"/>
@@ -66495,7 +66513,9 @@
       <c r="T339" s="61" t="n"/>
       <c r="U339" s="22" t="n"/>
       <c r="V339" s="61" t="n"/>
-      <c r="W339" s="22" t="n"/>
+      <c r="W339" s="22" t="n">
+        <v>192</v>
+      </c>
       <c r="X339" s="61" t="n"/>
       <c r="Y339" s="22" t="n"/>
       <c r="Z339" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -40950,7 +40950,9 @@
       <c r="U60" s="100" t="n">
         <v>1296</v>
       </c>
-      <c r="V60" s="22" t="n"/>
+      <c r="V60" s="22" t="n">
+        <v>1500</v>
+      </c>
       <c r="W60" s="100" t="n"/>
       <c r="X60" s="22" t="n"/>
       <c r="Y60" s="100" t="n"/>
@@ -50913,7 +50915,9 @@
       </c>
       <c r="U62" s="22" t="n"/>
       <c r="V62" s="61" t="n"/>
-      <c r="W62" s="22" t="n"/>
+      <c r="W62" s="22" t="n">
+        <v>117</v>
+      </c>
       <c r="X62" s="61" t="n"/>
       <c r="Y62" s="22" t="n"/>
       <c r="Z62" s="61" t="n"/>
@@ -60147,7 +60151,9 @@
       </c>
       <c r="U226" s="22" t="n"/>
       <c r="V226" s="61" t="n"/>
-      <c r="W226" s="22" t="n"/>
+      <c r="W226" s="22" t="n">
+        <v>4200</v>
+      </c>
       <c r="X226" s="61" t="n"/>
       <c r="Y226" s="22" t="n"/>
       <c r="Z226" s="61" t="n"/>
@@ -66965,7 +66971,9 @@
       </c>
       <c r="U347" s="22" t="n"/>
       <c r="V347" s="61" t="n"/>
-      <c r="W347" s="22" t="n"/>
+      <c r="W347" s="22" t="n">
+        <v>68</v>
+      </c>
       <c r="X347" s="61" t="n"/>
       <c r="Y347" s="22" t="n"/>
       <c r="Z347" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -38088,9 +38088,7 @@
       <c r="O4" s="100" t="n"/>
       <c r="P4" s="22" t="n"/>
       <c r="Q4" s="100" t="n"/>
-      <c r="R4" s="22" t="n">
-        <v>95</v>
-      </c>
+      <c r="R4" s="22" t="n"/>
       <c r="S4" s="100" t="n"/>
       <c r="T4" s="22" t="n"/>
       <c r="U4" s="100" t="n"/>
@@ -38140,9 +38138,7 @@
       <c r="M5" s="100" t="n"/>
       <c r="N5" s="22" t="n"/>
       <c r="O5" s="100" t="n"/>
-      <c r="P5" s="22" t="n">
-        <v>2166</v>
-      </c>
+      <c r="P5" s="22" t="n"/>
       <c r="Q5" s="100" t="n"/>
       <c r="R5" s="22" t="n"/>
       <c r="S5" s="100" t="n"/>
@@ -38184,9 +38180,7 @@
       <c r="G6" s="100" t="n">
         <v>554</v>
       </c>
-      <c r="H6" s="22" t="n">
-        <v>554</v>
-      </c>
+      <c r="H6" s="22" t="n"/>
       <c r="I6" s="100" t="n">
         <v>2600</v>
       </c>
@@ -38244,9 +38238,7 @@
       <c r="K7" s="100" t="n">
         <v>1744</v>
       </c>
-      <c r="L7" s="22" t="n">
-        <v>48</v>
-      </c>
+      <c r="L7" s="22" t="n"/>
       <c r="M7" s="100" t="n">
         <v>422</v>
       </c>
@@ -38354,15 +38346,11 @@
       <c r="O9" s="100" t="n">
         <v>636</v>
       </c>
-      <c r="P9" s="22" t="n">
-        <v>740</v>
-      </c>
+      <c r="P9" s="22" t="n"/>
       <c r="Q9" s="100" t="n"/>
       <c r="R9" s="22" t="n"/>
       <c r="S9" s="100" t="n"/>
-      <c r="T9" s="22" t="n">
-        <v>416</v>
-      </c>
+      <c r="T9" s="22" t="n"/>
       <c r="U9" s="100" t="n"/>
       <c r="V9" s="22" t="n"/>
       <c r="W9" s="100" t="n"/>
@@ -38508,9 +38496,7 @@
       <c r="O12" s="100" t="n">
         <v>1724</v>
       </c>
-      <c r="P12" s="22" t="n">
-        <v>36</v>
-      </c>
+      <c r="P12" s="22" t="n"/>
       <c r="Q12" s="100" t="n"/>
       <c r="R12" s="22" t="n"/>
       <c r="S12" s="100" t="n"/>
@@ -38562,13 +38548,9 @@
       </c>
       <c r="P13" s="22" t="n"/>
       <c r="Q13" s="100" t="n"/>
-      <c r="R13" s="22" t="n">
-        <v>152</v>
-      </c>
+      <c r="R13" s="22" t="n"/>
       <c r="S13" s="100" t="n"/>
-      <c r="T13" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="T13" s="22" t="n"/>
       <c r="U13" s="100" t="n"/>
       <c r="V13" s="22" t="n"/>
       <c r="W13" s="100" t="n"/>
@@ -39979,9 +39961,7 @@
       <c r="O41" s="100" t="n"/>
       <c r="P41" s="22" t="n"/>
       <c r="Q41" s="100" t="n"/>
-      <c r="R41" s="22" t="n">
-        <v>28</v>
-      </c>
+      <c r="R41" s="22" t="n"/>
       <c r="S41" s="100" t="n"/>
       <c r="T41" s="22" t="n"/>
       <c r="U41" s="100" t="n"/>
@@ -40027,9 +40007,7 @@
       <c r="M42" s="100" t="n"/>
       <c r="N42" s="22" t="n"/>
       <c r="O42" s="100" t="n"/>
-      <c r="P42" s="22" t="n">
-        <v>540</v>
-      </c>
+      <c r="P42" s="22" t="n"/>
       <c r="Q42" s="100" t="n"/>
       <c r="R42" s="22" t="n"/>
       <c r="S42" s="100" t="n"/>
@@ -40071,9 +40049,7 @@
       <c r="G43" s="100" t="n">
         <v>20</v>
       </c>
-      <c r="H43" s="22" t="n">
-        <v>64</v>
-      </c>
+      <c r="H43" s="22" t="n"/>
       <c r="I43" s="100" t="n">
         <v>560</v>
       </c>
@@ -40233,9 +40209,7 @@
       </c>
       <c r="N46" s="22" t="n"/>
       <c r="O46" s="100" t="n"/>
-      <c r="P46" s="22" t="n">
-        <v>72</v>
-      </c>
+      <c r="P46" s="22" t="n"/>
       <c r="Q46" s="100" t="n"/>
       <c r="R46" s="22" t="n"/>
       <c r="S46" s="100" t="n"/>
@@ -40287,9 +40261,7 @@
       <c r="O47" s="100" t="n"/>
       <c r="P47" s="22" t="n"/>
       <c r="Q47" s="100" t="n"/>
-      <c r="R47" s="22" t="n">
-        <v>4</v>
-      </c>
+      <c r="R47" s="22" t="n"/>
       <c r="S47" s="100" t="n"/>
       <c r="T47" s="22" t="n"/>
       <c r="U47" s="100" t="n"/>
@@ -40950,9 +40922,7 @@
       <c r="U60" s="100" t="n">
         <v>1296</v>
       </c>
-      <c r="V60" s="22" t="n">
-        <v>1500</v>
-      </c>
+      <c r="V60" s="22" t="n"/>
       <c r="W60" s="100" t="n"/>
       <c r="X60" s="22" t="n"/>
       <c r="Y60" s="100" t="n"/>
@@ -47709,9 +47679,7 @@
       <c r="H6" s="61" t="n"/>
       <c r="I6" s="22" t="n"/>
       <c r="J6" s="61" t="n"/>
-      <c r="K6" s="22" t="n">
-        <v>67</v>
-      </c>
+      <c r="K6" s="22" t="n"/>
       <c r="L6" s="61" t="n"/>
       <c r="M6" s="22" t="n"/>
       <c r="N6" s="61" t="n"/>
@@ -47995,13 +47963,9 @@
       <c r="L11" s="61" t="n">
         <v>22</v>
       </c>
-      <c r="M11" s="22" t="n">
-        <v>15</v>
-      </c>
+      <c r="M11" s="22" t="n"/>
       <c r="N11" s="61" t="n"/>
-      <c r="O11" s="22" t="n">
-        <v>22</v>
-      </c>
+      <c r="O11" s="22" t="n"/>
       <c r="P11" s="61" t="n"/>
       <c r="Q11" s="22" t="n"/>
       <c r="R11" s="61" t="n"/>
@@ -48281,9 +48245,7 @@
       </c>
       <c r="M16" s="22" t="n"/>
       <c r="N16" s="61" t="n"/>
-      <c r="O16" s="22" t="n">
-        <v>74</v>
-      </c>
+      <c r="O16" s="22" t="n"/>
       <c r="P16" s="61" t="n"/>
       <c r="Q16" s="22" t="n"/>
       <c r="R16" s="61" t="n"/>
@@ -48341,9 +48303,7 @@
       <c r="N17" s="61" t="n">
         <v>45</v>
       </c>
-      <c r="O17" s="22" t="n">
-        <v>9</v>
-      </c>
+      <c r="O17" s="22" t="n"/>
       <c r="P17" s="61" t="n"/>
       <c r="Q17" s="22" t="n"/>
       <c r="R17" s="61" t="n"/>
@@ -48405,9 +48365,7 @@
       <c r="R18" s="61" t="n"/>
       <c r="S18" s="22" t="n"/>
       <c r="T18" s="61" t="n"/>
-      <c r="U18" s="22" t="n">
-        <v>46</v>
-      </c>
+      <c r="U18" s="22" t="n"/>
       <c r="V18" s="61" t="n"/>
       <c r="W18" s="22" t="n"/>
       <c r="X18" s="61" t="n"/>
@@ -48571,9 +48529,7 @@
       </c>
       <c r="O21" s="22" t="n"/>
       <c r="P21" s="61" t="n"/>
-      <c r="Q21" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q21" s="22" t="n"/>
       <c r="R21" s="61" t="n"/>
       <c r="S21" s="22" t="n"/>
       <c r="T21" s="61" t="n"/>
@@ -48689,9 +48645,7 @@
       <c r="R23" s="61" t="n"/>
       <c r="S23" s="22" t="n"/>
       <c r="T23" s="61" t="n"/>
-      <c r="U23" s="22" t="n">
-        <v>93</v>
-      </c>
+      <c r="U23" s="22" t="n"/>
       <c r="V23" s="61" t="n"/>
       <c r="W23" s="22" t="n"/>
       <c r="X23" s="61" t="n"/>
@@ -48917,9 +48871,7 @@
       <c r="R27" s="61" t="n"/>
       <c r="S27" s="22" t="n"/>
       <c r="T27" s="61" t="n"/>
-      <c r="U27" s="22" t="n">
-        <v>55</v>
-      </c>
+      <c r="U27" s="22" t="n"/>
       <c r="V27" s="61" t="n"/>
       <c r="W27" s="22" t="n"/>
       <c r="X27" s="61" t="n"/>
@@ -48975,9 +48927,7 @@
       <c r="R28" s="61" t="n"/>
       <c r="S28" s="22" t="n"/>
       <c r="T28" s="61" t="n"/>
-      <c r="U28" s="22" t="n">
-        <v>52</v>
-      </c>
+      <c r="U28" s="22" t="n"/>
       <c r="V28" s="61" t="n"/>
       <c r="W28" s="22" t="n"/>
       <c r="X28" s="61" t="n"/>
@@ -49087,9 +49037,7 @@
       </c>
       <c r="Q30" s="22" t="n"/>
       <c r="R30" s="61" t="n"/>
-      <c r="S30" s="22" t="n">
-        <v>45</v>
-      </c>
+      <c r="S30" s="22" t="n"/>
       <c r="T30" s="61" t="n"/>
       <c r="U30" s="22" t="n"/>
       <c r="V30" s="61" t="n"/>
@@ -49149,9 +49097,7 @@
       </c>
       <c r="S31" s="22" t="n"/>
       <c r="T31" s="61" t="n"/>
-      <c r="U31" s="22" t="n">
-        <v>26</v>
-      </c>
+      <c r="U31" s="22" t="n"/>
       <c r="V31" s="61" t="n"/>
       <c r="W31" s="22" t="n"/>
       <c r="X31" s="61" t="n"/>
@@ -49755,9 +49701,7 @@
       <c r="H42" s="61" t="n"/>
       <c r="I42" s="22" t="n"/>
       <c r="J42" s="61" t="n"/>
-      <c r="K42" s="22" t="n">
-        <v>38</v>
-      </c>
+      <c r="K42" s="22" t="n"/>
       <c r="L42" s="61" t="n"/>
       <c r="M42" s="22" t="n"/>
       <c r="N42" s="61" t="n"/>
@@ -49929,13 +49873,9 @@
       <c r="L45" s="61" t="n">
         <v>63</v>
       </c>
-      <c r="M45" s="22" t="n">
-        <v>93</v>
-      </c>
+      <c r="M45" s="22" t="n"/>
       <c r="N45" s="61" t="n"/>
-      <c r="O45" s="22" t="n">
-        <v>63</v>
-      </c>
+      <c r="O45" s="22" t="n"/>
       <c r="P45" s="61" t="n"/>
       <c r="Q45" s="22" t="n"/>
       <c r="R45" s="61" t="n"/>
@@ -49993,9 +49933,7 @@
       <c r="N46" s="61" t="n"/>
       <c r="O46" s="22" t="n"/>
       <c r="P46" s="61" t="n"/>
-      <c r="Q46" s="22" t="n">
-        <v>12</v>
-      </c>
+      <c r="Q46" s="22" t="n"/>
       <c r="R46" s="61" t="n"/>
       <c r="S46" s="22" t="n"/>
       <c r="T46" s="61" t="n"/>
@@ -50051,15 +49989,11 @@
       <c r="N47" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="O47" s="22" t="n">
-        <v>160</v>
-      </c>
+      <c r="O47" s="22" t="n"/>
       <c r="P47" s="61" t="n"/>
       <c r="Q47" s="22" t="n"/>
       <c r="R47" s="61" t="n"/>
-      <c r="S47" s="22" t="n">
-        <v>80</v>
-      </c>
+      <c r="S47" s="22" t="n"/>
       <c r="T47" s="61" t="n"/>
       <c r="U47" s="22" t="n"/>
       <c r="V47" s="61" t="n"/>
@@ -50289,9 +50223,7 @@
       <c r="T51" s="61" t="n"/>
       <c r="U51" s="22" t="n"/>
       <c r="V51" s="61" t="n"/>
-      <c r="W51" s="22" t="n">
-        <v>311</v>
-      </c>
+      <c r="W51" s="22" t="n"/>
       <c r="X51" s="61" t="n"/>
       <c r="Y51" s="22" t="n"/>
       <c r="Z51" s="61" t="n"/>
@@ -50345,13 +50277,9 @@
       <c r="R52" s="61" t="n">
         <v>88</v>
       </c>
-      <c r="S52" s="22" t="n">
-        <v>289</v>
-      </c>
+      <c r="S52" s="22" t="n"/>
       <c r="T52" s="61" t="n"/>
-      <c r="U52" s="22" t="n">
-        <v>132</v>
-      </c>
+      <c r="U52" s="22" t="n"/>
       <c r="V52" s="61" t="n"/>
       <c r="W52" s="22" t="n"/>
       <c r="X52" s="61" t="n"/>
@@ -50743,9 +50671,7 @@
       <c r="T59" s="61" t="n">
         <v>93</v>
       </c>
-      <c r="U59" s="22" t="n">
-        <v>5</v>
-      </c>
+      <c r="U59" s="22" t="n"/>
       <c r="V59" s="61" t="n"/>
       <c r="W59" s="22" t="n"/>
       <c r="X59" s="61" t="n"/>
@@ -50915,9 +50841,7 @@
       </c>
       <c r="U62" s="22" t="n"/>
       <c r="V62" s="61" t="n"/>
-      <c r="W62" s="22" t="n">
-        <v>117</v>
-      </c>
+      <c r="W62" s="22" t="n"/>
       <c r="X62" s="61" t="n"/>
       <c r="Y62" s="22" t="n"/>
       <c r="Z62" s="61" t="n"/>
@@ -52023,13 +51947,9 @@
       <c r="J82" s="61" t="n"/>
       <c r="K82" s="22" t="n"/>
       <c r="L82" s="61" t="n"/>
-      <c r="M82" s="22" t="n">
-        <v>76</v>
-      </c>
+      <c r="M82" s="22" t="n"/>
       <c r="N82" s="61" t="n"/>
-      <c r="O82" s="22" t="n">
-        <v>62</v>
-      </c>
+      <c r="O82" s="22" t="n"/>
       <c r="P82" s="61" t="n"/>
       <c r="Q82" s="22" t="n"/>
       <c r="R82" s="61" t="n"/>
@@ -52141,9 +52061,7 @@
       <c r="L84" s="61" t="n"/>
       <c r="M84" s="22" t="n"/>
       <c r="N84" s="61" t="n"/>
-      <c r="O84" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="O84" s="22" t="n"/>
       <c r="P84" s="61" t="n"/>
       <c r="Q84" s="22" t="n"/>
       <c r="R84" s="61" t="n"/>
@@ -52201,9 +52119,7 @@
       <c r="L85" s="61" t="n"/>
       <c r="M85" s="22" t="n"/>
       <c r="N85" s="61" t="n"/>
-      <c r="O85" s="22" t="n">
-        <v>6</v>
-      </c>
+      <c r="O85" s="22" t="n"/>
       <c r="P85" s="61" t="n"/>
       <c r="Q85" s="22" t="n"/>
       <c r="R85" s="61" t="n"/>
@@ -52315,9 +52231,7 @@
       <c r="N87" s="61" t="n"/>
       <c r="O87" s="22" t="n"/>
       <c r="P87" s="61" t="n"/>
-      <c r="Q87" s="22" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q87" s="22" t="n"/>
       <c r="R87" s="61" t="n"/>
       <c r="S87" s="22" t="n"/>
       <c r="T87" s="61" t="n"/>
@@ -52371,9 +52285,7 @@
       <c r="L88" s="61" t="n"/>
       <c r="M88" s="22" t="n"/>
       <c r="N88" s="61" t="n"/>
-      <c r="O88" s="22" t="n">
-        <v>14</v>
-      </c>
+      <c r="O88" s="22" t="n"/>
       <c r="P88" s="61" t="n"/>
       <c r="Q88" s="22" t="n"/>
       <c r="R88" s="61" t="n"/>
@@ -52429,9 +52341,7 @@
       <c r="L89" s="61" t="n"/>
       <c r="M89" s="22" t="n"/>
       <c r="N89" s="61" t="n"/>
-      <c r="O89" s="22" t="n">
-        <v>11</v>
-      </c>
+      <c r="O89" s="22" t="n"/>
       <c r="P89" s="61" t="n"/>
       <c r="Q89" s="22" t="n"/>
       <c r="R89" s="61" t="n"/>
@@ -52487,9 +52397,7 @@
       <c r="L90" s="61" t="n"/>
       <c r="M90" s="22" t="n"/>
       <c r="N90" s="61" t="n"/>
-      <c r="O90" s="22" t="n">
-        <v>14</v>
-      </c>
+      <c r="O90" s="22" t="n"/>
       <c r="P90" s="61" t="n"/>
       <c r="Q90" s="22" t="n"/>
       <c r="R90" s="61" t="n"/>
@@ -52927,9 +52835,7 @@
       </c>
       <c r="K98" s="22" t="n"/>
       <c r="L98" s="61" t="n"/>
-      <c r="M98" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="M98" s="22" t="n"/>
       <c r="N98" s="61" t="n"/>
       <c r="O98" s="22" t="n"/>
       <c r="P98" s="61" t="n"/>
@@ -53043,9 +52949,7 @@
       <c r="N100" s="61" t="n"/>
       <c r="O100" s="22" t="n"/>
       <c r="P100" s="61" t="n"/>
-      <c r="Q100" s="22" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q100" s="22" t="n"/>
       <c r="R100" s="61" t="n"/>
       <c r="S100" s="22" t="n"/>
       <c r="T100" s="61" t="n"/>
@@ -53155,9 +53059,7 @@
       </c>
       <c r="M102" s="22" t="n"/>
       <c r="N102" s="61" t="n"/>
-      <c r="O102" s="22" t="n">
-        <v>10</v>
-      </c>
+      <c r="O102" s="22" t="n"/>
       <c r="P102" s="61" t="n"/>
       <c r="Q102" s="22" t="n"/>
       <c r="R102" s="61" t="n"/>
@@ -53269,9 +53171,7 @@
       <c r="N104" s="61" t="n"/>
       <c r="O104" s="22" t="n"/>
       <c r="P104" s="61" t="n"/>
-      <c r="Q104" s="22" t="n">
-        <v>31</v>
-      </c>
+      <c r="Q104" s="22" t="n"/>
       <c r="R104" s="61" t="n"/>
       <c r="S104" s="22" t="n"/>
       <c r="T104" s="61" t="n"/>
@@ -53381,9 +53281,7 @@
       </c>
       <c r="M106" s="22" t="n"/>
       <c r="N106" s="61" t="n"/>
-      <c r="O106" s="22" t="n">
-        <v>1</v>
-      </c>
+      <c r="O106" s="22" t="n"/>
       <c r="P106" s="61" t="n"/>
       <c r="Q106" s="22" t="n"/>
       <c r="R106" s="61" t="n"/>
@@ -53815,9 +53713,7 @@
       <c r="H114" s="61" t="n"/>
       <c r="I114" s="22" t="n"/>
       <c r="J114" s="61" t="n"/>
-      <c r="K114" s="22" t="n">
-        <v>5</v>
-      </c>
+      <c r="K114" s="22" t="n"/>
       <c r="L114" s="61" t="n"/>
       <c r="M114" s="22" t="n"/>
       <c r="N114" s="61" t="n"/>
@@ -53987,9 +53883,7 @@
       </c>
       <c r="K117" s="22" t="n"/>
       <c r="L117" s="61" t="n"/>
-      <c r="M117" s="22" t="n">
-        <v>28</v>
-      </c>
+      <c r="M117" s="22" t="n"/>
       <c r="N117" s="61" t="n"/>
       <c r="O117" s="22" t="n"/>
       <c r="P117" s="61" t="n"/>
@@ -54045,13 +53939,9 @@
       </c>
       <c r="K118" s="22" t="n"/>
       <c r="L118" s="61" t="n"/>
-      <c r="M118" s="22" t="n">
-        <v>12</v>
-      </c>
+      <c r="M118" s="22" t="n"/>
       <c r="N118" s="61" t="n"/>
-      <c r="O118" s="22" t="n">
-        <v>12</v>
-      </c>
+      <c r="O118" s="22" t="n"/>
       <c r="P118" s="61" t="n"/>
       <c r="Q118" s="22" t="n"/>
       <c r="R118" s="61" t="n"/>
@@ -54107,13 +53997,9 @@
       <c r="L119" s="61" t="n">
         <v>58</v>
       </c>
-      <c r="M119" s="22" t="n">
-        <v>34</v>
-      </c>
+      <c r="M119" s="22" t="n"/>
       <c r="N119" s="61" t="n"/>
-      <c r="O119" s="22" t="n">
-        <v>58</v>
-      </c>
+      <c r="O119" s="22" t="n"/>
       <c r="P119" s="61" t="n"/>
       <c r="Q119" s="22" t="n"/>
       <c r="R119" s="61" t="n"/>
@@ -54337,9 +54223,7 @@
       <c r="N123" s="61" t="n"/>
       <c r="O123" s="22" t="n"/>
       <c r="P123" s="61" t="n"/>
-      <c r="Q123" s="22" t="n">
-        <v>38</v>
-      </c>
+      <c r="Q123" s="22" t="n"/>
       <c r="R123" s="61" t="n"/>
       <c r="S123" s="22" t="n"/>
       <c r="T123" s="61" t="n"/>
@@ -54395,13 +54279,9 @@
       <c r="N124" s="61" t="n">
         <v>39</v>
       </c>
-      <c r="O124" s="22" t="n">
-        <v>36</v>
-      </c>
+      <c r="O124" s="22" t="n"/>
       <c r="P124" s="61" t="n"/>
-      <c r="Q124" s="22" t="n">
-        <v>42</v>
-      </c>
+      <c r="Q124" s="22" t="n"/>
       <c r="R124" s="61" t="n"/>
       <c r="S124" s="22" t="n"/>
       <c r="T124" s="61" t="n"/>
@@ -54515,9 +54395,7 @@
       <c r="P126" s="61" t="n"/>
       <c r="Q126" s="22" t="n"/>
       <c r="R126" s="61" t="n"/>
-      <c r="S126" s="22" t="n">
-        <v>45</v>
-      </c>
+      <c r="S126" s="22" t="n"/>
       <c r="T126" s="61" t="n"/>
       <c r="U126" s="22" t="n"/>
       <c r="V126" s="61" t="n"/>
@@ -54683,9 +54561,7 @@
       </c>
       <c r="O129" s="22" t="n"/>
       <c r="P129" s="61" t="n"/>
-      <c r="Q129" s="22" t="n">
-        <v>9</v>
-      </c>
+      <c r="Q129" s="22" t="n"/>
       <c r="R129" s="61" t="n"/>
       <c r="S129" s="22" t="n"/>
       <c r="T129" s="61" t="n"/>
@@ -55021,9 +54897,7 @@
       <c r="R135" s="61" t="n"/>
       <c r="S135" s="22" t="n"/>
       <c r="T135" s="61" t="n"/>
-      <c r="U135" s="22" t="n">
-        <v>38</v>
-      </c>
+      <c r="U135" s="22" t="n"/>
       <c r="V135" s="61" t="n"/>
       <c r="W135" s="22" t="n"/>
       <c r="X135" s="61" t="n"/>
@@ -55075,9 +54949,7 @@
       </c>
       <c r="O136" s="22" t="n"/>
       <c r="P136" s="61" t="n"/>
-      <c r="Q136" s="22" t="n">
-        <v>45</v>
-      </c>
+      <c r="Q136" s="22" t="n"/>
       <c r="R136" s="61" t="n"/>
       <c r="S136" s="22" t="n"/>
       <c r="T136" s="61" t="n"/>
@@ -55415,9 +55287,7 @@
       </c>
       <c r="Q142" s="22" t="n"/>
       <c r="R142" s="61" t="n"/>
-      <c r="S142" s="22" t="n">
-        <v>30</v>
-      </c>
+      <c r="S142" s="22" t="n"/>
       <c r="T142" s="61" t="n"/>
       <c r="U142" s="22" t="n"/>
       <c r="V142" s="61" t="n"/>
@@ -55475,9 +55345,7 @@
       <c r="R143" s="61" t="n"/>
       <c r="S143" s="22" t="n"/>
       <c r="T143" s="61" t="n"/>
-      <c r="U143" s="22" t="n">
-        <v>3</v>
-      </c>
+      <c r="U143" s="22" t="n"/>
       <c r="V143" s="61" t="n"/>
       <c r="W143" s="22" t="n"/>
       <c r="X143" s="61" t="n"/>
@@ -55535,9 +55403,7 @@
       <c r="T144" s="61" t="n"/>
       <c r="U144" s="22" t="n"/>
       <c r="V144" s="61" t="n"/>
-      <c r="W144" s="22" t="n">
-        <v>12</v>
-      </c>
+      <c r="W144" s="22" t="n"/>
       <c r="X144" s="61" t="n"/>
       <c r="Y144" s="22" t="n"/>
       <c r="Z144" s="61" t="n"/>
@@ -55591,9 +55457,7 @@
       <c r="R145" s="61" t="n"/>
       <c r="S145" s="22" t="n"/>
       <c r="T145" s="61" t="n"/>
-      <c r="U145" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="U145" s="22" t="n"/>
       <c r="V145" s="61" t="n"/>
       <c r="W145" s="22" t="n"/>
       <c r="X145" s="61" t="n"/>
@@ -56365,9 +56229,7 @@
       <c r="N159" s="61" t="n"/>
       <c r="O159" s="22" t="n"/>
       <c r="P159" s="61" t="n"/>
-      <c r="Q159" s="22" t="n">
-        <v>33</v>
-      </c>
+      <c r="Q159" s="22" t="n"/>
       <c r="R159" s="61" t="n"/>
       <c r="S159" s="22" t="n"/>
       <c r="T159" s="61" t="n"/>
@@ -56421,9 +56283,7 @@
       </c>
       <c r="M160" s="22" t="n"/>
       <c r="N160" s="61" t="n"/>
-      <c r="O160" s="22" t="n">
-        <v>59</v>
-      </c>
+      <c r="O160" s="22" t="n"/>
       <c r="P160" s="61" t="n"/>
       <c r="Q160" s="22" t="n"/>
       <c r="R160" s="61" t="n"/>
@@ -56537,9 +56397,7 @@
       <c r="P162" s="61" t="n"/>
       <c r="Q162" s="22" t="n"/>
       <c r="R162" s="61" t="n"/>
-      <c r="S162" s="22" t="n">
-        <v>1</v>
-      </c>
+      <c r="S162" s="22" t="n"/>
       <c r="T162" s="61" t="n"/>
       <c r="U162" s="22" t="n"/>
       <c r="V162" s="61" t="n"/>
@@ -56701,9 +56559,7 @@
       </c>
       <c r="M165" s="22" t="n"/>
       <c r="N165" s="61" t="n"/>
-      <c r="O165" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="O165" s="22" t="n"/>
       <c r="P165" s="61" t="n"/>
       <c r="Q165" s="22" t="n"/>
       <c r="R165" s="61" t="n"/>
@@ -56923,9 +56779,7 @@
       <c r="N169" s="61" t="n"/>
       <c r="O169" s="22" t="n"/>
       <c r="P169" s="61" t="n"/>
-      <c r="Q169" s="22" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q169" s="22" t="n"/>
       <c r="R169" s="61" t="n"/>
       <c r="S169" s="22" t="n"/>
       <c r="T169" s="61" t="n"/>
@@ -56979,9 +56833,7 @@
       </c>
       <c r="M170" s="22" t="n"/>
       <c r="N170" s="61" t="n"/>
-      <c r="O170" s="22" t="n">
-        <v>9</v>
-      </c>
+      <c r="O170" s="22" t="n"/>
       <c r="P170" s="61" t="n"/>
       <c r="Q170" s="22" t="n"/>
       <c r="R170" s="61" t="n"/>
@@ -57043,9 +56895,7 @@
       <c r="R171" s="61" t="n"/>
       <c r="S171" s="22" t="n"/>
       <c r="T171" s="61" t="n"/>
-      <c r="U171" s="22" t="n">
-        <v>9</v>
-      </c>
+      <c r="U171" s="22" t="n"/>
       <c r="V171" s="61" t="n"/>
       <c r="W171" s="22" t="n"/>
       <c r="X171" s="61" t="n"/>
@@ -57205,9 +57055,7 @@
       </c>
       <c r="M174" s="22" t="n"/>
       <c r="N174" s="61" t="n"/>
-      <c r="O174" s="22" t="n">
-        <v>6</v>
-      </c>
+      <c r="O174" s="22" t="n"/>
       <c r="P174" s="61" t="n"/>
       <c r="Q174" s="22" t="n"/>
       <c r="R174" s="61" t="n"/>
@@ -57319,9 +57167,7 @@
       <c r="N176" s="61" t="n"/>
       <c r="O176" s="22" t="n"/>
       <c r="P176" s="61" t="n"/>
-      <c r="Q176" s="22" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q176" s="22" t="n"/>
       <c r="R176" s="61" t="n"/>
       <c r="S176" s="22" t="n"/>
       <c r="T176" s="61" t="n"/>
@@ -57545,9 +57391,7 @@
       <c r="N180" s="61" t="n"/>
       <c r="O180" s="22" t="n"/>
       <c r="P180" s="61" t="n"/>
-      <c r="Q180" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q180" s="22" t="n"/>
       <c r="R180" s="61" t="n"/>
       <c r="S180" s="22" t="n"/>
       <c r="T180" s="61" t="n"/>
@@ -57829,9 +57673,7 @@
       <c r="P185" s="61" t="n"/>
       <c r="Q185" s="22" t="n"/>
       <c r="R185" s="61" t="n"/>
-      <c r="S185" s="22" t="n">
-        <v>198</v>
-      </c>
+      <c r="S185" s="22" t="n"/>
       <c r="T185" s="61" t="n"/>
       <c r="U185" s="22" t="n"/>
       <c r="V185" s="61" t="n"/>
@@ -57879,9 +57721,7 @@
       </c>
       <c r="I186" s="22" t="n"/>
       <c r="J186" s="61" t="n"/>
-      <c r="K186" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="K186" s="22" t="n"/>
       <c r="L186" s="61" t="n"/>
       <c r="M186" s="22" t="n"/>
       <c r="N186" s="61" t="n"/>
@@ -57891,9 +57731,7 @@
       <c r="R186" s="61" t="n"/>
       <c r="S186" s="22" t="n"/>
       <c r="T186" s="61" t="n"/>
-      <c r="U186" s="22" t="n">
-        <v>634</v>
-      </c>
+      <c r="U186" s="22" t="n"/>
       <c r="V186" s="61" t="n"/>
       <c r="W186" s="22" t="n"/>
       <c r="X186" s="61" t="n"/>
@@ -59907,9 +59745,7 @@
       </c>
       <c r="I222" s="22" t="n"/>
       <c r="J222" s="61" t="n"/>
-      <c r="K222" s="22" t="n">
-        <v>16</v>
-      </c>
+      <c r="K222" s="22" t="n"/>
       <c r="L222" s="61" t="n"/>
       <c r="M222" s="22" t="n"/>
       <c r="N222" s="61" t="n"/>
@@ -59919,9 +59755,7 @@
       <c r="R222" s="61" t="n"/>
       <c r="S222" s="22" t="n"/>
       <c r="T222" s="61" t="n"/>
-      <c r="U222" s="22" t="n">
-        <v>1119</v>
-      </c>
+      <c r="U222" s="22" t="n"/>
       <c r="V222" s="61" t="n"/>
       <c r="W222" s="22" t="n"/>
       <c r="X222" s="61" t="n"/>
@@ -60151,9 +59985,7 @@
       </c>
       <c r="U226" s="22" t="n"/>
       <c r="V226" s="61" t="n"/>
-      <c r="W226" s="22" t="n">
-        <v>4200</v>
-      </c>
+      <c r="W226" s="22" t="n"/>
       <c r="X226" s="61" t="n"/>
       <c r="Y226" s="22" t="n"/>
       <c r="Z226" s="61" t="n"/>
@@ -61827,9 +61659,7 @@
       <c r="J256" s="61" t="n"/>
       <c r="K256" s="22" t="n"/>
       <c r="L256" s="61" t="n"/>
-      <c r="M256" s="22" t="n">
-        <v>86</v>
-      </c>
+      <c r="M256" s="22" t="n"/>
       <c r="N256" s="61" t="n"/>
       <c r="O256" s="22" t="n"/>
       <c r="P256" s="61" t="n"/>
@@ -61893,9 +61723,7 @@
       <c r="P257" s="61" t="n"/>
       <c r="Q257" s="22" t="n"/>
       <c r="R257" s="61" t="n"/>
-      <c r="S257" s="22" t="n">
-        <v>210</v>
-      </c>
+      <c r="S257" s="22" t="n"/>
       <c r="T257" s="61" t="n"/>
       <c r="U257" s="22" t="n"/>
       <c r="V257" s="61" t="n"/>
@@ -61947,9 +61775,7 @@
       <c r="N258" s="61" t="n"/>
       <c r="O258" s="22" t="n"/>
       <c r="P258" s="61" t="n"/>
-      <c r="Q258" s="22" t="n">
-        <v>17</v>
-      </c>
+      <c r="Q258" s="22" t="n"/>
       <c r="R258" s="61" t="n"/>
       <c r="S258" s="22" t="n"/>
       <c r="T258" s="61" t="n"/>
@@ -62123,9 +61949,7 @@
       </c>
       <c r="S261" s="22" t="n"/>
       <c r="T261" s="61" t="n"/>
-      <c r="U261" s="22" t="n">
-        <v>380</v>
-      </c>
+      <c r="U261" s="22" t="n"/>
       <c r="V261" s="61" t="n"/>
       <c r="W261" s="22" t="n"/>
       <c r="X261" s="61" t="n"/>
@@ -63923,9 +63747,7 @@
       <c r="P293" s="61" t="n"/>
       <c r="Q293" s="22" t="n"/>
       <c r="R293" s="61" t="n"/>
-      <c r="S293" s="22" t="n">
-        <v>34</v>
-      </c>
+      <c r="S293" s="22" t="n"/>
       <c r="T293" s="61" t="n"/>
       <c r="U293" s="22" t="n"/>
       <c r="V293" s="61" t="n"/>
@@ -63977,9 +63799,7 @@
       <c r="N294" s="61" t="n"/>
       <c r="O294" s="22" t="n"/>
       <c r="P294" s="61" t="n"/>
-      <c r="Q294" s="22" t="n">
-        <v>27</v>
-      </c>
+      <c r="Q294" s="22" t="n"/>
       <c r="R294" s="61" t="n"/>
       <c r="S294" s="22" t="n"/>
       <c r="T294" s="61" t="n"/>
@@ -64261,9 +64081,7 @@
       <c r="R299" s="61" t="n"/>
       <c r="S299" s="22" t="n"/>
       <c r="T299" s="61" t="n"/>
-      <c r="U299" s="22" t="n">
-        <v>1</v>
-      </c>
+      <c r="U299" s="22" t="n"/>
       <c r="V299" s="61" t="n"/>
       <c r="W299" s="22" t="n"/>
       <c r="X299" s="61" t="n"/>
@@ -64375,9 +64193,7 @@
       <c r="R301" s="61" t="n"/>
       <c r="S301" s="22" t="n"/>
       <c r="T301" s="61" t="n"/>
-      <c r="U301" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="U301" s="22" t="n"/>
       <c r="V301" s="61" t="n"/>
       <c r="W301" s="22" t="n"/>
       <c r="X301" s="61" t="n"/>
@@ -64545,9 +64361,7 @@
       </c>
       <c r="S304" s="22" t="n"/>
       <c r="T304" s="61" t="n"/>
-      <c r="U304" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="U304" s="22" t="n"/>
       <c r="V304" s="61" t="n"/>
       <c r="W304" s="22" t="n"/>
       <c r="X304" s="61" t="n"/>
@@ -65099,9 +64913,7 @@
       </c>
       <c r="S314" s="22" t="n"/>
       <c r="T314" s="61" t="n"/>
-      <c r="U314" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="U314" s="22" t="n"/>
       <c r="V314" s="61" t="n"/>
       <c r="W314" s="22" t="n"/>
       <c r="X314" s="61" t="n"/>
@@ -65323,9 +65135,7 @@
       </c>
       <c r="S318" s="22" t="n"/>
       <c r="T318" s="61" t="n"/>
-      <c r="U318" s="22" t="n">
-        <v>4</v>
-      </c>
+      <c r="U318" s="22" t="n"/>
       <c r="V318" s="61" t="n"/>
       <c r="W318" s="22" t="n"/>
       <c r="X318" s="61" t="n"/>
@@ -65925,9 +65735,7 @@
       <c r="H329" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="I329" s="22" t="n">
-        <v>176</v>
-      </c>
+      <c r="I329" s="22" t="n"/>
       <c r="J329" s="61" t="n"/>
       <c r="K329" s="22" t="n"/>
       <c r="L329" s="61" t="n"/>
@@ -65937,9 +65745,7 @@
       <c r="P329" s="61" t="n"/>
       <c r="Q329" s="22" t="n"/>
       <c r="R329" s="61" t="n"/>
-      <c r="S329" s="22" t="n">
-        <v>168</v>
-      </c>
+      <c r="S329" s="22" t="n"/>
       <c r="T329" s="61" t="n"/>
       <c r="U329" s="22" t="n"/>
       <c r="V329" s="61" t="n"/>
@@ -65987,9 +65793,7 @@
       <c r="J330" s="61" t="n"/>
       <c r="K330" s="22" t="n"/>
       <c r="L330" s="61" t="n"/>
-      <c r="M330" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="M330" s="22" t="n"/>
       <c r="N330" s="61" t="n"/>
       <c r="O330" s="22" t="n"/>
       <c r="P330" s="61" t="n"/>
@@ -66163,9 +65967,7 @@
       <c r="P333" s="61" t="n"/>
       <c r="Q333" s="22" t="n"/>
       <c r="R333" s="61" t="n"/>
-      <c r="S333" s="22" t="n">
-        <v>40</v>
-      </c>
+      <c r="S333" s="22" t="n"/>
       <c r="T333" s="61" t="n"/>
       <c r="U333" s="22" t="n"/>
       <c r="V333" s="61" t="n"/>
@@ -66219,9 +66021,7 @@
       </c>
       <c r="O334" s="22" t="n"/>
       <c r="P334" s="61" t="n"/>
-      <c r="Q334" s="22" t="n">
-        <v>88</v>
-      </c>
+      <c r="Q334" s="22" t="n"/>
       <c r="R334" s="61" t="n"/>
       <c r="S334" s="22" t="n"/>
       <c r="T334" s="61" t="n"/>
@@ -66279,15 +66079,11 @@
       <c r="P335" s="61" t="n">
         <v>110</v>
       </c>
-      <c r="Q335" s="22" t="n">
-        <v>6</v>
-      </c>
+      <c r="Q335" s="22" t="n"/>
       <c r="R335" s="61" t="n"/>
       <c r="S335" s="22" t="n"/>
       <c r="T335" s="61" t="n"/>
-      <c r="U335" s="22" t="n">
-        <v>110</v>
-      </c>
+      <c r="U335" s="22" t="n"/>
       <c r="V335" s="61" t="n"/>
       <c r="W335" s="22" t="n"/>
       <c r="X335" s="61" t="n"/>
@@ -66343,9 +66139,7 @@
       <c r="R336" s="61" t="n"/>
       <c r="S336" s="22" t="n"/>
       <c r="T336" s="61" t="n"/>
-      <c r="U336" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="U336" s="22" t="n"/>
       <c r="V336" s="61" t="n"/>
       <c r="W336" s="22" t="n"/>
       <c r="X336" s="61" t="n"/>
@@ -66401,9 +66195,7 @@
       <c r="R337" s="61" t="n"/>
       <c r="S337" s="22" t="n"/>
       <c r="T337" s="61" t="n"/>
-      <c r="U337" s="22" t="n">
-        <v>22</v>
-      </c>
+      <c r="U337" s="22" t="n"/>
       <c r="V337" s="61" t="n"/>
       <c r="W337" s="22" t="n"/>
       <c r="X337" s="61" t="n"/>
@@ -66519,9 +66311,7 @@
       <c r="T339" s="61" t="n"/>
       <c r="U339" s="22" t="n"/>
       <c r="V339" s="61" t="n"/>
-      <c r="W339" s="22" t="n">
-        <v>192</v>
-      </c>
+      <c r="W339" s="22" t="n"/>
       <c r="X339" s="61" t="n"/>
       <c r="Y339" s="22" t="n"/>
       <c r="Z339" s="61" t="n"/>
@@ -66575,9 +66365,7 @@
       </c>
       <c r="S340" s="22" t="n"/>
       <c r="T340" s="61" t="n"/>
-      <c r="U340" s="22" t="n">
-        <v>138</v>
-      </c>
+      <c r="U340" s="22" t="n"/>
       <c r="V340" s="61" t="n"/>
       <c r="W340" s="22" t="n"/>
       <c r="X340" s="61" t="n"/>
@@ -66971,9 +66759,7 @@
       </c>
       <c r="U347" s="22" t="n"/>
       <c r="V347" s="61" t="n"/>
-      <c r="W347" s="22" t="n">
-        <v>68</v>
-      </c>
+      <c r="W347" s="22" t="n"/>
       <c r="X347" s="61" t="n"/>
       <c r="Y347" s="22" t="n"/>
       <c r="Z347" s="61" t="n"/>
@@ -67643,9 +67429,7 @@
       <c r="R359" s="61" t="n"/>
       <c r="S359" s="22" t="n"/>
       <c r="T359" s="61" t="n"/>
-      <c r="U359" s="22" t="n">
-        <v>9</v>
-      </c>
+      <c r="U359" s="22" t="n"/>
       <c r="V359" s="61" t="n"/>
       <c r="W359" s="22" t="n"/>
       <c r="X359" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -38088,7 +38088,9 @@
       <c r="O4" s="100" t="n"/>
       <c r="P4" s="22" t="n"/>
       <c r="Q4" s="100" t="n"/>
-      <c r="R4" s="22" t="n"/>
+      <c r="R4" s="22" t="n">
+        <v>95</v>
+      </c>
       <c r="S4" s="100" t="n"/>
       <c r="T4" s="22" t="n"/>
       <c r="U4" s="100" t="n"/>
@@ -38138,7 +38140,9 @@
       <c r="M5" s="100" t="n"/>
       <c r="N5" s="22" t="n"/>
       <c r="O5" s="100" t="n"/>
-      <c r="P5" s="22" t="n"/>
+      <c r="P5" s="22" t="n">
+        <v>2166</v>
+      </c>
       <c r="Q5" s="100" t="n"/>
       <c r="R5" s="22" t="n"/>
       <c r="S5" s="100" t="n"/>
@@ -38180,7 +38184,9 @@
       <c r="G6" s="100" t="n">
         <v>554</v>
       </c>
-      <c r="H6" s="22" t="n"/>
+      <c r="H6" s="22" t="n">
+        <v>554</v>
+      </c>
       <c r="I6" s="100" t="n">
         <v>2600</v>
       </c>
@@ -38238,7 +38244,9 @@
       <c r="K7" s="100" t="n">
         <v>1744</v>
       </c>
-      <c r="L7" s="22" t="n"/>
+      <c r="L7" s="22" t="n">
+        <v>48</v>
+      </c>
       <c r="M7" s="100" t="n">
         <v>422</v>
       </c>
@@ -38346,11 +38354,15 @@
       <c r="O9" s="100" t="n">
         <v>636</v>
       </c>
-      <c r="P9" s="22" t="n"/>
+      <c r="P9" s="22" t="n">
+        <v>740</v>
+      </c>
       <c r="Q9" s="100" t="n"/>
       <c r="R9" s="22" t="n"/>
       <c r="S9" s="100" t="n"/>
-      <c r="T9" s="22" t="n"/>
+      <c r="T9" s="22" t="n">
+        <v>416</v>
+      </c>
       <c r="U9" s="100" t="n"/>
       <c r="V9" s="22" t="n"/>
       <c r="W9" s="100" t="n"/>
@@ -38496,7 +38508,9 @@
       <c r="O12" s="100" t="n">
         <v>1724</v>
       </c>
-      <c r="P12" s="22" t="n"/>
+      <c r="P12" s="22" t="n">
+        <v>36</v>
+      </c>
       <c r="Q12" s="100" t="n"/>
       <c r="R12" s="22" t="n"/>
       <c r="S12" s="100" t="n"/>
@@ -38548,9 +38562,13 @@
       </c>
       <c r="P13" s="22" t="n"/>
       <c r="Q13" s="100" t="n"/>
-      <c r="R13" s="22" t="n"/>
+      <c r="R13" s="22" t="n">
+        <v>152</v>
+      </c>
       <c r="S13" s="100" t="n"/>
-      <c r="T13" s="22" t="n"/>
+      <c r="T13" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="U13" s="100" t="n"/>
       <c r="V13" s="22" t="n"/>
       <c r="W13" s="100" t="n"/>
@@ -39961,7 +39979,9 @@
       <c r="O41" s="100" t="n"/>
       <c r="P41" s="22" t="n"/>
       <c r="Q41" s="100" t="n"/>
-      <c r="R41" s="22" t="n"/>
+      <c r="R41" s="22" t="n">
+        <v>28</v>
+      </c>
       <c r="S41" s="100" t="n"/>
       <c r="T41" s="22" t="n"/>
       <c r="U41" s="100" t="n"/>
@@ -40007,7 +40027,9 @@
       <c r="M42" s="100" t="n"/>
       <c r="N42" s="22" t="n"/>
       <c r="O42" s="100" t="n"/>
-      <c r="P42" s="22" t="n"/>
+      <c r="P42" s="22" t="n">
+        <v>540</v>
+      </c>
       <c r="Q42" s="100" t="n"/>
       <c r="R42" s="22" t="n"/>
       <c r="S42" s="100" t="n"/>
@@ -40049,7 +40071,9 @@
       <c r="G43" s="100" t="n">
         <v>20</v>
       </c>
-      <c r="H43" s="22" t="n"/>
+      <c r="H43" s="22" t="n">
+        <v>64</v>
+      </c>
       <c r="I43" s="100" t="n">
         <v>560</v>
       </c>
@@ -40209,7 +40233,9 @@
       </c>
       <c r="N46" s="22" t="n"/>
       <c r="O46" s="100" t="n"/>
-      <c r="P46" s="22" t="n"/>
+      <c r="P46" s="22" t="n">
+        <v>72</v>
+      </c>
       <c r="Q46" s="100" t="n"/>
       <c r="R46" s="22" t="n"/>
       <c r="S46" s="100" t="n"/>
@@ -40261,7 +40287,9 @@
       <c r="O47" s="100" t="n"/>
       <c r="P47" s="22" t="n"/>
       <c r="Q47" s="100" t="n"/>
-      <c r="R47" s="22" t="n"/>
+      <c r="R47" s="22" t="n">
+        <v>4</v>
+      </c>
       <c r="S47" s="100" t="n"/>
       <c r="T47" s="22" t="n"/>
       <c r="U47" s="100" t="n"/>
@@ -40922,7 +40950,9 @@
       <c r="U60" s="100" t="n">
         <v>1296</v>
       </c>
-      <c r="V60" s="22" t="n"/>
+      <c r="V60" s="22" t="n">
+        <v>1500</v>
+      </c>
       <c r="W60" s="100" t="n"/>
       <c r="X60" s="22" t="n"/>
       <c r="Y60" s="100" t="n"/>
@@ -47679,7 +47709,9 @@
       <c r="H6" s="61" t="n"/>
       <c r="I6" s="22" t="n"/>
       <c r="J6" s="61" t="n"/>
-      <c r="K6" s="22" t="n"/>
+      <c r="K6" s="22" t="n">
+        <v>67</v>
+      </c>
       <c r="L6" s="61" t="n"/>
       <c r="M6" s="22" t="n"/>
       <c r="N6" s="61" t="n"/>
@@ -47963,9 +47995,13 @@
       <c r="L11" s="61" t="n">
         <v>22</v>
       </c>
-      <c r="M11" s="22" t="n"/>
+      <c r="M11" s="22" t="n">
+        <v>15</v>
+      </c>
       <c r="N11" s="61" t="n"/>
-      <c r="O11" s="22" t="n"/>
+      <c r="O11" s="22" t="n">
+        <v>22</v>
+      </c>
       <c r="P11" s="61" t="n"/>
       <c r="Q11" s="22" t="n"/>
       <c r="R11" s="61" t="n"/>
@@ -48245,7 +48281,9 @@
       </c>
       <c r="M16" s="22" t="n"/>
       <c r="N16" s="61" t="n"/>
-      <c r="O16" s="22" t="n"/>
+      <c r="O16" s="22" t="n">
+        <v>74</v>
+      </c>
       <c r="P16" s="61" t="n"/>
       <c r="Q16" s="22" t="n"/>
       <c r="R16" s="61" t="n"/>
@@ -48303,7 +48341,9 @@
       <c r="N17" s="61" t="n">
         <v>45</v>
       </c>
-      <c r="O17" s="22" t="n"/>
+      <c r="O17" s="22" t="n">
+        <v>9</v>
+      </c>
       <c r="P17" s="61" t="n"/>
       <c r="Q17" s="22" t="n"/>
       <c r="R17" s="61" t="n"/>
@@ -48365,7 +48405,9 @@
       <c r="R18" s="61" t="n"/>
       <c r="S18" s="22" t="n"/>
       <c r="T18" s="61" t="n"/>
-      <c r="U18" s="22" t="n"/>
+      <c r="U18" s="22" t="n">
+        <v>46</v>
+      </c>
       <c r="V18" s="61" t="n"/>
       <c r="W18" s="22" t="n"/>
       <c r="X18" s="61" t="n"/>
@@ -48529,7 +48571,9 @@
       </c>
       <c r="O21" s="22" t="n"/>
       <c r="P21" s="61" t="n"/>
-      <c r="Q21" s="22" t="n"/>
+      <c r="Q21" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="R21" s="61" t="n"/>
       <c r="S21" s="22" t="n"/>
       <c r="T21" s="61" t="n"/>
@@ -48645,7 +48689,9 @@
       <c r="R23" s="61" t="n"/>
       <c r="S23" s="22" t="n"/>
       <c r="T23" s="61" t="n"/>
-      <c r="U23" s="22" t="n"/>
+      <c r="U23" s="22" t="n">
+        <v>93</v>
+      </c>
       <c r="V23" s="61" t="n"/>
       <c r="W23" s="22" t="n"/>
       <c r="X23" s="61" t="n"/>
@@ -48871,7 +48917,9 @@
       <c r="R27" s="61" t="n"/>
       <c r="S27" s="22" t="n"/>
       <c r="T27" s="61" t="n"/>
-      <c r="U27" s="22" t="n"/>
+      <c r="U27" s="22" t="n">
+        <v>55</v>
+      </c>
       <c r="V27" s="61" t="n"/>
       <c r="W27" s="22" t="n"/>
       <c r="X27" s="61" t="n"/>
@@ -48927,7 +48975,9 @@
       <c r="R28" s="61" t="n"/>
       <c r="S28" s="22" t="n"/>
       <c r="T28" s="61" t="n"/>
-      <c r="U28" s="22" t="n"/>
+      <c r="U28" s="22" t="n">
+        <v>52</v>
+      </c>
       <c r="V28" s="61" t="n"/>
       <c r="W28" s="22" t="n"/>
       <c r="X28" s="61" t="n"/>
@@ -49037,7 +49087,9 @@
       </c>
       <c r="Q30" s="22" t="n"/>
       <c r="R30" s="61" t="n"/>
-      <c r="S30" s="22" t="n"/>
+      <c r="S30" s="22" t="n">
+        <v>45</v>
+      </c>
       <c r="T30" s="61" t="n"/>
       <c r="U30" s="22" t="n"/>
       <c r="V30" s="61" t="n"/>
@@ -49097,7 +49149,9 @@
       </c>
       <c r="S31" s="22" t="n"/>
       <c r="T31" s="61" t="n"/>
-      <c r="U31" s="22" t="n"/>
+      <c r="U31" s="22" t="n">
+        <v>26</v>
+      </c>
       <c r="V31" s="61" t="n"/>
       <c r="W31" s="22" t="n"/>
       <c r="X31" s="61" t="n"/>
@@ -49701,7 +49755,9 @@
       <c r="H42" s="61" t="n"/>
       <c r="I42" s="22" t="n"/>
       <c r="J42" s="61" t="n"/>
-      <c r="K42" s="22" t="n"/>
+      <c r="K42" s="22" t="n">
+        <v>38</v>
+      </c>
       <c r="L42" s="61" t="n"/>
       <c r="M42" s="22" t="n"/>
       <c r="N42" s="61" t="n"/>
@@ -49873,9 +49929,13 @@
       <c r="L45" s="61" t="n">
         <v>63</v>
       </c>
-      <c r="M45" s="22" t="n"/>
+      <c r="M45" s="22" t="n">
+        <v>93</v>
+      </c>
       <c r="N45" s="61" t="n"/>
-      <c r="O45" s="22" t="n"/>
+      <c r="O45" s="22" t="n">
+        <v>63</v>
+      </c>
       <c r="P45" s="61" t="n"/>
       <c r="Q45" s="22" t="n"/>
       <c r="R45" s="61" t="n"/>
@@ -49933,7 +49993,9 @@
       <c r="N46" s="61" t="n"/>
       <c r="O46" s="22" t="n"/>
       <c r="P46" s="61" t="n"/>
-      <c r="Q46" s="22" t="n"/>
+      <c r="Q46" s="22" t="n">
+        <v>12</v>
+      </c>
       <c r="R46" s="61" t="n"/>
       <c r="S46" s="22" t="n"/>
       <c r="T46" s="61" t="n"/>
@@ -49989,11 +50051,15 @@
       <c r="N47" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="O47" s="22" t="n"/>
+      <c r="O47" s="22" t="n">
+        <v>160</v>
+      </c>
       <c r="P47" s="61" t="n"/>
       <c r="Q47" s="22" t="n"/>
       <c r="R47" s="61" t="n"/>
-      <c r="S47" s="22" t="n"/>
+      <c r="S47" s="22" t="n">
+        <v>80</v>
+      </c>
       <c r="T47" s="61" t="n"/>
       <c r="U47" s="22" t="n"/>
       <c r="V47" s="61" t="n"/>
@@ -50223,7 +50289,9 @@
       <c r="T51" s="61" t="n"/>
       <c r="U51" s="22" t="n"/>
       <c r="V51" s="61" t="n"/>
-      <c r="W51" s="22" t="n"/>
+      <c r="W51" s="22" t="n">
+        <v>311</v>
+      </c>
       <c r="X51" s="61" t="n"/>
       <c r="Y51" s="22" t="n"/>
       <c r="Z51" s="61" t="n"/>
@@ -50277,9 +50345,13 @@
       <c r="R52" s="61" t="n">
         <v>88</v>
       </c>
-      <c r="S52" s="22" t="n"/>
+      <c r="S52" s="22" t="n">
+        <v>289</v>
+      </c>
       <c r="T52" s="61" t="n"/>
-      <c r="U52" s="22" t="n"/>
+      <c r="U52" s="22" t="n">
+        <v>132</v>
+      </c>
       <c r="V52" s="61" t="n"/>
       <c r="W52" s="22" t="n"/>
       <c r="X52" s="61" t="n"/>
@@ -50671,7 +50743,9 @@
       <c r="T59" s="61" t="n">
         <v>93</v>
       </c>
-      <c r="U59" s="22" t="n"/>
+      <c r="U59" s="22" t="n">
+        <v>5</v>
+      </c>
       <c r="V59" s="61" t="n"/>
       <c r="W59" s="22" t="n"/>
       <c r="X59" s="61" t="n"/>
@@ -50841,7 +50915,9 @@
       </c>
       <c r="U62" s="22" t="n"/>
       <c r="V62" s="61" t="n"/>
-      <c r="W62" s="22" t="n"/>
+      <c r="W62" s="22" t="n">
+        <v>117</v>
+      </c>
       <c r="X62" s="61" t="n"/>
       <c r="Y62" s="22" t="n"/>
       <c r="Z62" s="61" t="n"/>
@@ -51947,9 +52023,13 @@
       <c r="J82" s="61" t="n"/>
       <c r="K82" s="22" t="n"/>
       <c r="L82" s="61" t="n"/>
-      <c r="M82" s="22" t="n"/>
+      <c r="M82" s="22" t="n">
+        <v>76</v>
+      </c>
       <c r="N82" s="61" t="n"/>
-      <c r="O82" s="22" t="n"/>
+      <c r="O82" s="22" t="n">
+        <v>62</v>
+      </c>
       <c r="P82" s="61" t="n"/>
       <c r="Q82" s="22" t="n"/>
       <c r="R82" s="61" t="n"/>
@@ -52061,7 +52141,9 @@
       <c r="L84" s="61" t="n"/>
       <c r="M84" s="22" t="n"/>
       <c r="N84" s="61" t="n"/>
-      <c r="O84" s="22" t="n"/>
+      <c r="O84" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="P84" s="61" t="n"/>
       <c r="Q84" s="22" t="n"/>
       <c r="R84" s="61" t="n"/>
@@ -52119,7 +52201,9 @@
       <c r="L85" s="61" t="n"/>
       <c r="M85" s="22" t="n"/>
       <c r="N85" s="61" t="n"/>
-      <c r="O85" s="22" t="n"/>
+      <c r="O85" s="22" t="n">
+        <v>6</v>
+      </c>
       <c r="P85" s="61" t="n"/>
       <c r="Q85" s="22" t="n"/>
       <c r="R85" s="61" t="n"/>
@@ -52231,7 +52315,9 @@
       <c r="N87" s="61" t="n"/>
       <c r="O87" s="22" t="n"/>
       <c r="P87" s="61" t="n"/>
-      <c r="Q87" s="22" t="n"/>
+      <c r="Q87" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="R87" s="61" t="n"/>
       <c r="S87" s="22" t="n"/>
       <c r="T87" s="61" t="n"/>
@@ -52285,7 +52371,9 @@
       <c r="L88" s="61" t="n"/>
       <c r="M88" s="22" t="n"/>
       <c r="N88" s="61" t="n"/>
-      <c r="O88" s="22" t="n"/>
+      <c r="O88" s="22" t="n">
+        <v>14</v>
+      </c>
       <c r="P88" s="61" t="n"/>
       <c r="Q88" s="22" t="n"/>
       <c r="R88" s="61" t="n"/>
@@ -52341,7 +52429,9 @@
       <c r="L89" s="61" t="n"/>
       <c r="M89" s="22" t="n"/>
       <c r="N89" s="61" t="n"/>
-      <c r="O89" s="22" t="n"/>
+      <c r="O89" s="22" t="n">
+        <v>11</v>
+      </c>
       <c r="P89" s="61" t="n"/>
       <c r="Q89" s="22" t="n"/>
       <c r="R89" s="61" t="n"/>
@@ -52397,7 +52487,9 @@
       <c r="L90" s="61" t="n"/>
       <c r="M90" s="22" t="n"/>
       <c r="N90" s="61" t="n"/>
-      <c r="O90" s="22" t="n"/>
+      <c r="O90" s="22" t="n">
+        <v>14</v>
+      </c>
       <c r="P90" s="61" t="n"/>
       <c r="Q90" s="22" t="n"/>
       <c r="R90" s="61" t="n"/>
@@ -52835,7 +52927,9 @@
       </c>
       <c r="K98" s="22" t="n"/>
       <c r="L98" s="61" t="n"/>
-      <c r="M98" s="22" t="n"/>
+      <c r="M98" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="N98" s="61" t="n"/>
       <c r="O98" s="22" t="n"/>
       <c r="P98" s="61" t="n"/>
@@ -52949,7 +53043,9 @@
       <c r="N100" s="61" t="n"/>
       <c r="O100" s="22" t="n"/>
       <c r="P100" s="61" t="n"/>
-      <c r="Q100" s="22" t="n"/>
+      <c r="Q100" s="22" t="n">
+        <v>3</v>
+      </c>
       <c r="R100" s="61" t="n"/>
       <c r="S100" s="22" t="n"/>
       <c r="T100" s="61" t="n"/>
@@ -53059,7 +53155,9 @@
       </c>
       <c r="M102" s="22" t="n"/>
       <c r="N102" s="61" t="n"/>
-      <c r="O102" s="22" t="n"/>
+      <c r="O102" s="22" t="n">
+        <v>10</v>
+      </c>
       <c r="P102" s="61" t="n"/>
       <c r="Q102" s="22" t="n"/>
       <c r="R102" s="61" t="n"/>
@@ -53171,7 +53269,9 @@
       <c r="N104" s="61" t="n"/>
       <c r="O104" s="22" t="n"/>
       <c r="P104" s="61" t="n"/>
-      <c r="Q104" s="22" t="n"/>
+      <c r="Q104" s="22" t="n">
+        <v>31</v>
+      </c>
       <c r="R104" s="61" t="n"/>
       <c r="S104" s="22" t="n"/>
       <c r="T104" s="61" t="n"/>
@@ -53281,7 +53381,9 @@
       </c>
       <c r="M106" s="22" t="n"/>
       <c r="N106" s="61" t="n"/>
-      <c r="O106" s="22" t="n"/>
+      <c r="O106" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="P106" s="61" t="n"/>
       <c r="Q106" s="22" t="n"/>
       <c r="R106" s="61" t="n"/>
@@ -53713,7 +53815,9 @@
       <c r="H114" s="61" t="n"/>
       <c r="I114" s="22" t="n"/>
       <c r="J114" s="61" t="n"/>
-      <c r="K114" s="22" t="n"/>
+      <c r="K114" s="22" t="n">
+        <v>5</v>
+      </c>
       <c r="L114" s="61" t="n"/>
       <c r="M114" s="22" t="n"/>
       <c r="N114" s="61" t="n"/>
@@ -53883,7 +53987,9 @@
       </c>
       <c r="K117" s="22" t="n"/>
       <c r="L117" s="61" t="n"/>
-      <c r="M117" s="22" t="n"/>
+      <c r="M117" s="22" t="n">
+        <v>28</v>
+      </c>
       <c r="N117" s="61" t="n"/>
       <c r="O117" s="22" t="n"/>
       <c r="P117" s="61" t="n"/>
@@ -53939,9 +54045,13 @@
       </c>
       <c r="K118" s="22" t="n"/>
       <c r="L118" s="61" t="n"/>
-      <c r="M118" s="22" t="n"/>
+      <c r="M118" s="22" t="n">
+        <v>12</v>
+      </c>
       <c r="N118" s="61" t="n"/>
-      <c r="O118" s="22" t="n"/>
+      <c r="O118" s="22" t="n">
+        <v>12</v>
+      </c>
       <c r="P118" s="61" t="n"/>
       <c r="Q118" s="22" t="n"/>
       <c r="R118" s="61" t="n"/>
@@ -53997,9 +54107,13 @@
       <c r="L119" s="61" t="n">
         <v>58</v>
       </c>
-      <c r="M119" s="22" t="n"/>
+      <c r="M119" s="22" t="n">
+        <v>34</v>
+      </c>
       <c r="N119" s="61" t="n"/>
-      <c r="O119" s="22" t="n"/>
+      <c r="O119" s="22" t="n">
+        <v>58</v>
+      </c>
       <c r="P119" s="61" t="n"/>
       <c r="Q119" s="22" t="n"/>
       <c r="R119" s="61" t="n"/>
@@ -54223,7 +54337,9 @@
       <c r="N123" s="61" t="n"/>
       <c r="O123" s="22" t="n"/>
       <c r="P123" s="61" t="n"/>
-      <c r="Q123" s="22" t="n"/>
+      <c r="Q123" s="22" t="n">
+        <v>38</v>
+      </c>
       <c r="R123" s="61" t="n"/>
       <c r="S123" s="22" t="n"/>
       <c r="T123" s="61" t="n"/>
@@ -54279,9 +54395,13 @@
       <c r="N124" s="61" t="n">
         <v>39</v>
       </c>
-      <c r="O124" s="22" t="n"/>
+      <c r="O124" s="22" t="n">
+        <v>36</v>
+      </c>
       <c r="P124" s="61" t="n"/>
-      <c r="Q124" s="22" t="n"/>
+      <c r="Q124" s="22" t="n">
+        <v>42</v>
+      </c>
       <c r="R124" s="61" t="n"/>
       <c r="S124" s="22" t="n"/>
       <c r="T124" s="61" t="n"/>
@@ -54395,7 +54515,9 @@
       <c r="P126" s="61" t="n"/>
       <c r="Q126" s="22" t="n"/>
       <c r="R126" s="61" t="n"/>
-      <c r="S126" s="22" t="n"/>
+      <c r="S126" s="22" t="n">
+        <v>45</v>
+      </c>
       <c r="T126" s="61" t="n"/>
       <c r="U126" s="22" t="n"/>
       <c r="V126" s="61" t="n"/>
@@ -54561,7 +54683,9 @@
       </c>
       <c r="O129" s="22" t="n"/>
       <c r="P129" s="61" t="n"/>
-      <c r="Q129" s="22" t="n"/>
+      <c r="Q129" s="22" t="n">
+        <v>9</v>
+      </c>
       <c r="R129" s="61" t="n"/>
       <c r="S129" s="22" t="n"/>
       <c r="T129" s="61" t="n"/>
@@ -54897,7 +55021,9 @@
       <c r="R135" s="61" t="n"/>
       <c r="S135" s="22" t="n"/>
       <c r="T135" s="61" t="n"/>
-      <c r="U135" s="22" t="n"/>
+      <c r="U135" s="22" t="n">
+        <v>38</v>
+      </c>
       <c r="V135" s="61" t="n"/>
       <c r="W135" s="22" t="n"/>
       <c r="X135" s="61" t="n"/>
@@ -54949,7 +55075,9 @@
       </c>
       <c r="O136" s="22" t="n"/>
       <c r="P136" s="61" t="n"/>
-      <c r="Q136" s="22" t="n"/>
+      <c r="Q136" s="22" t="n">
+        <v>45</v>
+      </c>
       <c r="R136" s="61" t="n"/>
       <c r="S136" s="22" t="n"/>
       <c r="T136" s="61" t="n"/>
@@ -55287,7 +55415,9 @@
       </c>
       <c r="Q142" s="22" t="n"/>
       <c r="R142" s="61" t="n"/>
-      <c r="S142" s="22" t="n"/>
+      <c r="S142" s="22" t="n">
+        <v>30</v>
+      </c>
       <c r="T142" s="61" t="n"/>
       <c r="U142" s="22" t="n"/>
       <c r="V142" s="61" t="n"/>
@@ -55345,7 +55475,9 @@
       <c r="R143" s="61" t="n"/>
       <c r="S143" s="22" t="n"/>
       <c r="T143" s="61" t="n"/>
-      <c r="U143" s="22" t="n"/>
+      <c r="U143" s="22" t="n">
+        <v>3</v>
+      </c>
       <c r="V143" s="61" t="n"/>
       <c r="W143" s="22" t="n"/>
       <c r="X143" s="61" t="n"/>
@@ -55403,7 +55535,9 @@
       <c r="T144" s="61" t="n"/>
       <c r="U144" s="22" t="n"/>
       <c r="V144" s="61" t="n"/>
-      <c r="W144" s="22" t="n"/>
+      <c r="W144" s="22" t="n">
+        <v>12</v>
+      </c>
       <c r="X144" s="61" t="n"/>
       <c r="Y144" s="22" t="n"/>
       <c r="Z144" s="61" t="n"/>
@@ -55457,7 +55591,9 @@
       <c r="R145" s="61" t="n"/>
       <c r="S145" s="22" t="n"/>
       <c r="T145" s="61" t="n"/>
-      <c r="U145" s="22" t="n"/>
+      <c r="U145" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="V145" s="61" t="n"/>
       <c r="W145" s="22" t="n"/>
       <c r="X145" s="61" t="n"/>
@@ -56229,7 +56365,9 @@
       <c r="N159" s="61" t="n"/>
       <c r="O159" s="22" t="n"/>
       <c r="P159" s="61" t="n"/>
-      <c r="Q159" s="22" t="n"/>
+      <c r="Q159" s="22" t="n">
+        <v>33</v>
+      </c>
       <c r="R159" s="61" t="n"/>
       <c r="S159" s="22" t="n"/>
       <c r="T159" s="61" t="n"/>
@@ -56283,7 +56421,9 @@
       </c>
       <c r="M160" s="22" t="n"/>
       <c r="N160" s="61" t="n"/>
-      <c r="O160" s="22" t="n"/>
+      <c r="O160" s="22" t="n">
+        <v>59</v>
+      </c>
       <c r="P160" s="61" t="n"/>
       <c r="Q160" s="22" t="n"/>
       <c r="R160" s="61" t="n"/>
@@ -56397,7 +56537,9 @@
       <c r="P162" s="61" t="n"/>
       <c r="Q162" s="22" t="n"/>
       <c r="R162" s="61" t="n"/>
-      <c r="S162" s="22" t="n"/>
+      <c r="S162" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="T162" s="61" t="n"/>
       <c r="U162" s="22" t="n"/>
       <c r="V162" s="61" t="n"/>
@@ -56559,7 +56701,9 @@
       </c>
       <c r="M165" s="22" t="n"/>
       <c r="N165" s="61" t="n"/>
-      <c r="O165" s="22" t="n"/>
+      <c r="O165" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="P165" s="61" t="n"/>
       <c r="Q165" s="22" t="n"/>
       <c r="R165" s="61" t="n"/>
@@ -56779,7 +56923,9 @@
       <c r="N169" s="61" t="n"/>
       <c r="O169" s="22" t="n"/>
       <c r="P169" s="61" t="n"/>
-      <c r="Q169" s="22" t="n"/>
+      <c r="Q169" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="R169" s="61" t="n"/>
       <c r="S169" s="22" t="n"/>
       <c r="T169" s="61" t="n"/>
@@ -56833,7 +56979,9 @@
       </c>
       <c r="M170" s="22" t="n"/>
       <c r="N170" s="61" t="n"/>
-      <c r="O170" s="22" t="n"/>
+      <c r="O170" s="22" t="n">
+        <v>9</v>
+      </c>
       <c r="P170" s="61" t="n"/>
       <c r="Q170" s="22" t="n"/>
       <c r="R170" s="61" t="n"/>
@@ -56895,7 +57043,9 @@
       <c r="R171" s="61" t="n"/>
       <c r="S171" s="22" t="n"/>
       <c r="T171" s="61" t="n"/>
-      <c r="U171" s="22" t="n"/>
+      <c r="U171" s="22" t="n">
+        <v>9</v>
+      </c>
       <c r="V171" s="61" t="n"/>
       <c r="W171" s="22" t="n"/>
       <c r="X171" s="61" t="n"/>
@@ -57055,7 +57205,9 @@
       </c>
       <c r="M174" s="22" t="n"/>
       <c r="N174" s="61" t="n"/>
-      <c r="O174" s="22" t="n"/>
+      <c r="O174" s="22" t="n">
+        <v>6</v>
+      </c>
       <c r="P174" s="61" t="n"/>
       <c r="Q174" s="22" t="n"/>
       <c r="R174" s="61" t="n"/>
@@ -57167,7 +57319,9 @@
       <c r="N176" s="61" t="n"/>
       <c r="O176" s="22" t="n"/>
       <c r="P176" s="61" t="n"/>
-      <c r="Q176" s="22" t="n"/>
+      <c r="Q176" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="R176" s="61" t="n"/>
       <c r="S176" s="22" t="n"/>
       <c r="T176" s="61" t="n"/>
@@ -57391,7 +57545,9 @@
       <c r="N180" s="61" t="n"/>
       <c r="O180" s="22" t="n"/>
       <c r="P180" s="61" t="n"/>
-      <c r="Q180" s="22" t="n"/>
+      <c r="Q180" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="R180" s="61" t="n"/>
       <c r="S180" s="22" t="n"/>
       <c r="T180" s="61" t="n"/>
@@ -57673,7 +57829,9 @@
       <c r="P185" s="61" t="n"/>
       <c r="Q185" s="22" t="n"/>
       <c r="R185" s="61" t="n"/>
-      <c r="S185" s="22" t="n"/>
+      <c r="S185" s="22" t="n">
+        <v>198</v>
+      </c>
       <c r="T185" s="61" t="n"/>
       <c r="U185" s="22" t="n"/>
       <c r="V185" s="61" t="n"/>
@@ -57721,7 +57879,9 @@
       </c>
       <c r="I186" s="22" t="n"/>
       <c r="J186" s="61" t="n"/>
-      <c r="K186" s="22" t="n"/>
+      <c r="K186" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="L186" s="61" t="n"/>
       <c r="M186" s="22" t="n"/>
       <c r="N186" s="61" t="n"/>
@@ -57731,7 +57891,9 @@
       <c r="R186" s="61" t="n"/>
       <c r="S186" s="22" t="n"/>
       <c r="T186" s="61" t="n"/>
-      <c r="U186" s="22" t="n"/>
+      <c r="U186" s="22" t="n">
+        <v>634</v>
+      </c>
       <c r="V186" s="61" t="n"/>
       <c r="W186" s="22" t="n"/>
       <c r="X186" s="61" t="n"/>
@@ -59745,7 +59907,9 @@
       </c>
       <c r="I222" s="22" t="n"/>
       <c r="J222" s="61" t="n"/>
-      <c r="K222" s="22" t="n"/>
+      <c r="K222" s="22" t="n">
+        <v>16</v>
+      </c>
       <c r="L222" s="61" t="n"/>
       <c r="M222" s="22" t="n"/>
       <c r="N222" s="61" t="n"/>
@@ -59755,7 +59919,9 @@
       <c r="R222" s="61" t="n"/>
       <c r="S222" s="22" t="n"/>
       <c r="T222" s="61" t="n"/>
-      <c r="U222" s="22" t="n"/>
+      <c r="U222" s="22" t="n">
+        <v>1119</v>
+      </c>
       <c r="V222" s="61" t="n"/>
       <c r="W222" s="22" t="n"/>
       <c r="X222" s="61" t="n"/>
@@ -59985,7 +60151,9 @@
       </c>
       <c r="U226" s="22" t="n"/>
       <c r="V226" s="61" t="n"/>
-      <c r="W226" s="22" t="n"/>
+      <c r="W226" s="22" t="n">
+        <v>4200</v>
+      </c>
       <c r="X226" s="61" t="n"/>
       <c r="Y226" s="22" t="n"/>
       <c r="Z226" s="61" t="n"/>
@@ -61659,7 +61827,9 @@
       <c r="J256" s="61" t="n"/>
       <c r="K256" s="22" t="n"/>
       <c r="L256" s="61" t="n"/>
-      <c r="M256" s="22" t="n"/>
+      <c r="M256" s="22" t="n">
+        <v>86</v>
+      </c>
       <c r="N256" s="61" t="n"/>
       <c r="O256" s="22" t="n"/>
       <c r="P256" s="61" t="n"/>
@@ -61723,7 +61893,9 @@
       <c r="P257" s="61" t="n"/>
       <c r="Q257" s="22" t="n"/>
       <c r="R257" s="61" t="n"/>
-      <c r="S257" s="22" t="n"/>
+      <c r="S257" s="22" t="n">
+        <v>210</v>
+      </c>
       <c r="T257" s="61" t="n"/>
       <c r="U257" s="22" t="n"/>
       <c r="V257" s="61" t="n"/>
@@ -61775,7 +61947,9 @@
       <c r="N258" s="61" t="n"/>
       <c r="O258" s="22" t="n"/>
       <c r="P258" s="61" t="n"/>
-      <c r="Q258" s="22" t="n"/>
+      <c r="Q258" s="22" t="n">
+        <v>17</v>
+      </c>
       <c r="R258" s="61" t="n"/>
       <c r="S258" s="22" t="n"/>
       <c r="T258" s="61" t="n"/>
@@ -61949,7 +62123,9 @@
       </c>
       <c r="S261" s="22" t="n"/>
       <c r="T261" s="61" t="n"/>
-      <c r="U261" s="22" t="n"/>
+      <c r="U261" s="22" t="n">
+        <v>380</v>
+      </c>
       <c r="V261" s="61" t="n"/>
       <c r="W261" s="22" t="n"/>
       <c r="X261" s="61" t="n"/>
@@ -63747,7 +63923,9 @@
       <c r="P293" s="61" t="n"/>
       <c r="Q293" s="22" t="n"/>
       <c r="R293" s="61" t="n"/>
-      <c r="S293" s="22" t="n"/>
+      <c r="S293" s="22" t="n">
+        <v>34</v>
+      </c>
       <c r="T293" s="61" t="n"/>
       <c r="U293" s="22" t="n"/>
       <c r="V293" s="61" t="n"/>
@@ -63799,7 +63977,9 @@
       <c r="N294" s="61" t="n"/>
       <c r="O294" s="22" t="n"/>
       <c r="P294" s="61" t="n"/>
-      <c r="Q294" s="22" t="n"/>
+      <c r="Q294" s="22" t="n">
+        <v>27</v>
+      </c>
       <c r="R294" s="61" t="n"/>
       <c r="S294" s="22" t="n"/>
       <c r="T294" s="61" t="n"/>
@@ -64081,7 +64261,9 @@
       <c r="R299" s="61" t="n"/>
       <c r="S299" s="22" t="n"/>
       <c r="T299" s="61" t="n"/>
-      <c r="U299" s="22" t="n"/>
+      <c r="U299" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="V299" s="61" t="n"/>
       <c r="W299" s="22" t="n"/>
       <c r="X299" s="61" t="n"/>
@@ -64193,7 +64375,9 @@
       <c r="R301" s="61" t="n"/>
       <c r="S301" s="22" t="n"/>
       <c r="T301" s="61" t="n"/>
-      <c r="U301" s="22" t="n"/>
+      <c r="U301" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="V301" s="61" t="n"/>
       <c r="W301" s="22" t="n"/>
       <c r="X301" s="61" t="n"/>
@@ -64361,7 +64545,9 @@
       </c>
       <c r="S304" s="22" t="n"/>
       <c r="T304" s="61" t="n"/>
-      <c r="U304" s="22" t="n"/>
+      <c r="U304" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="V304" s="61" t="n"/>
       <c r="W304" s="22" t="n"/>
       <c r="X304" s="61" t="n"/>
@@ -64913,7 +65099,9 @@
       </c>
       <c r="S314" s="22" t="n"/>
       <c r="T314" s="61" t="n"/>
-      <c r="U314" s="22" t="n"/>
+      <c r="U314" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="V314" s="61" t="n"/>
       <c r="W314" s="22" t="n"/>
       <c r="X314" s="61" t="n"/>
@@ -65135,7 +65323,9 @@
       </c>
       <c r="S318" s="22" t="n"/>
       <c r="T318" s="61" t="n"/>
-      <c r="U318" s="22" t="n"/>
+      <c r="U318" s="22" t="n">
+        <v>4</v>
+      </c>
       <c r="V318" s="61" t="n"/>
       <c r="W318" s="22" t="n"/>
       <c r="X318" s="61" t="n"/>
@@ -65735,7 +65925,9 @@
       <c r="H329" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="I329" s="22" t="n"/>
+      <c r="I329" s="22" t="n">
+        <v>176</v>
+      </c>
       <c r="J329" s="61" t="n"/>
       <c r="K329" s="22" t="n"/>
       <c r="L329" s="61" t="n"/>
@@ -65745,7 +65937,9 @@
       <c r="P329" s="61" t="n"/>
       <c r="Q329" s="22" t="n"/>
       <c r="R329" s="61" t="n"/>
-      <c r="S329" s="22" t="n"/>
+      <c r="S329" s="22" t="n">
+        <v>168</v>
+      </c>
       <c r="T329" s="61" t="n"/>
       <c r="U329" s="22" t="n"/>
       <c r="V329" s="61" t="n"/>
@@ -65793,7 +65987,9 @@
       <c r="J330" s="61" t="n"/>
       <c r="K330" s="22" t="n"/>
       <c r="L330" s="61" t="n"/>
-      <c r="M330" s="22" t="n"/>
+      <c r="M330" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="N330" s="61" t="n"/>
       <c r="O330" s="22" t="n"/>
       <c r="P330" s="61" t="n"/>
@@ -65967,7 +66163,9 @@
       <c r="P333" s="61" t="n"/>
       <c r="Q333" s="22" t="n"/>
       <c r="R333" s="61" t="n"/>
-      <c r="S333" s="22" t="n"/>
+      <c r="S333" s="22" t="n">
+        <v>40</v>
+      </c>
       <c r="T333" s="61" t="n"/>
       <c r="U333" s="22" t="n"/>
       <c r="V333" s="61" t="n"/>
@@ -66021,7 +66219,9 @@
       </c>
       <c r="O334" s="22" t="n"/>
       <c r="P334" s="61" t="n"/>
-      <c r="Q334" s="22" t="n"/>
+      <c r="Q334" s="22" t="n">
+        <v>88</v>
+      </c>
       <c r="R334" s="61" t="n"/>
       <c r="S334" s="22" t="n"/>
       <c r="T334" s="61" t="n"/>
@@ -66079,11 +66279,15 @@
       <c r="P335" s="61" t="n">
         <v>110</v>
       </c>
-      <c r="Q335" s="22" t="n"/>
+      <c r="Q335" s="22" t="n">
+        <v>6</v>
+      </c>
       <c r="R335" s="61" t="n"/>
       <c r="S335" s="22" t="n"/>
       <c r="T335" s="61" t="n"/>
-      <c r="U335" s="22" t="n"/>
+      <c r="U335" s="22" t="n">
+        <v>110</v>
+      </c>
       <c r="V335" s="61" t="n"/>
       <c r="W335" s="22" t="n"/>
       <c r="X335" s="61" t="n"/>
@@ -66139,7 +66343,9 @@
       <c r="R336" s="61" t="n"/>
       <c r="S336" s="22" t="n"/>
       <c r="T336" s="61" t="n"/>
-      <c r="U336" s="22" t="n"/>
+      <c r="U336" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="V336" s="61" t="n"/>
       <c r="W336" s="22" t="n"/>
       <c r="X336" s="61" t="n"/>
@@ -66195,7 +66401,9 @@
       <c r="R337" s="61" t="n"/>
       <c r="S337" s="22" t="n"/>
       <c r="T337" s="61" t="n"/>
-      <c r="U337" s="22" t="n"/>
+      <c r="U337" s="22" t="n">
+        <v>22</v>
+      </c>
       <c r="V337" s="61" t="n"/>
       <c r="W337" s="22" t="n"/>
       <c r="X337" s="61" t="n"/>
@@ -66311,7 +66519,9 @@
       <c r="T339" s="61" t="n"/>
       <c r="U339" s="22" t="n"/>
       <c r="V339" s="61" t="n"/>
-      <c r="W339" s="22" t="n"/>
+      <c r="W339" s="22" t="n">
+        <v>192</v>
+      </c>
       <c r="X339" s="61" t="n"/>
       <c r="Y339" s="22" t="n"/>
       <c r="Z339" s="61" t="n"/>
@@ -66365,7 +66575,9 @@
       </c>
       <c r="S340" s="22" t="n"/>
       <c r="T340" s="61" t="n"/>
-      <c r="U340" s="22" t="n"/>
+      <c r="U340" s="22" t="n">
+        <v>138</v>
+      </c>
       <c r="V340" s="61" t="n"/>
       <c r="W340" s="22" t="n"/>
       <c r="X340" s="61" t="n"/>
@@ -66759,7 +66971,9 @@
       </c>
       <c r="U347" s="22" t="n"/>
       <c r="V347" s="61" t="n"/>
-      <c r="W347" s="22" t="n"/>
+      <c r="W347" s="22" t="n">
+        <v>68</v>
+      </c>
       <c r="X347" s="61" t="n"/>
       <c r="Y347" s="22" t="n"/>
       <c r="Z347" s="61" t="n"/>
@@ -67429,7 +67643,9 @@
       <c r="R359" s="61" t="n"/>
       <c r="S359" s="22" t="n"/>
       <c r="T359" s="61" t="n"/>
-      <c r="U359" s="22" t="n"/>
+      <c r="U359" s="22" t="n">
+        <v>9</v>
+      </c>
       <c r="V359" s="61" t="n"/>
       <c r="W359" s="22" t="n"/>
       <c r="X359" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -67647,7 +67647,9 @@
         <v>9</v>
       </c>
       <c r="V359" s="61" t="n"/>
-      <c r="W359" s="22" t="n"/>
+      <c r="W359" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="X359" s="61" t="n"/>
       <c r="Y359" s="22" t="n"/>
       <c r="Z359" s="61" t="n">

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -60493,7 +60493,9 @@
       </c>
       <c r="W232" s="22" t="n"/>
       <c r="X232" s="61" t="n"/>
-      <c r="Y232" s="22" t="n"/>
+      <c r="Y232" s="22" t="n">
+        <v>564</v>
+      </c>
       <c r="Z232" s="61" t="n"/>
       <c r="AA232" s="22" t="n"/>
       <c r="AB232" s="61" t="n"/>
@@ -62525,7 +62527,9 @@
       <c r="X268" s="61" t="n">
         <v>224</v>
       </c>
-      <c r="Y268" s="22" t="n"/>
+      <c r="Y268" s="22" t="n">
+        <v>609</v>
+      </c>
       <c r="Z268" s="61" t="n"/>
       <c r="AA268" s="22" t="n"/>
       <c r="AB268" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -48863,7 +48863,9 @@
       <c r="T26" s="61" t="n"/>
       <c r="U26" s="22" t="n"/>
       <c r="V26" s="61" t="n"/>
-      <c r="W26" s="22" t="n"/>
+      <c r="W26" s="22" t="n">
+        <v>85</v>
+      </c>
       <c r="X26" s="61" t="n"/>
       <c r="Y26" s="22" t="n"/>
       <c r="Z26" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -40341,7 +40341,9 @@
       <c r="S48" s="100" t="n"/>
       <c r="T48" s="22" t="n"/>
       <c r="U48" s="100" t="n"/>
-      <c r="V48" s="22" t="n"/>
+      <c r="V48" s="22" t="n">
+        <v>38</v>
+      </c>
       <c r="W48" s="100" t="n"/>
       <c r="X48" s="22" t="n"/>
       <c r="Y48" s="100" t="n"/>
@@ -58121,7 +58123,9 @@
       <c r="T190" s="61" t="n"/>
       <c r="U190" s="22" t="n"/>
       <c r="V190" s="61" t="n"/>
-      <c r="W190" s="22" t="n"/>
+      <c r="W190" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="X190" s="61" t="n"/>
       <c r="Y190" s="22" t="n"/>
       <c r="Z190" s="61" t="n">
@@ -59641,7 +59645,9 @@
       <c r="T217" s="61" t="n"/>
       <c r="U217" s="22" t="n"/>
       <c r="V217" s="61" t="n"/>
-      <c r="W217" s="22" t="n"/>
+      <c r="W217" s="22" t="n">
+        <v>44</v>
+      </c>
       <c r="X217" s="61" t="n"/>
       <c r="Y217" s="22" t="n"/>
       <c r="Z217" s="61" t="n"/>
@@ -65723,7 +65729,9 @@
       <c r="T325" s="61" t="n"/>
       <c r="U325" s="22" t="n"/>
       <c r="V325" s="61" t="n"/>
-      <c r="W325" s="22" t="n"/>
+      <c r="W325" s="22" t="n">
+        <v>15</v>
+      </c>
       <c r="X325" s="61" t="n"/>
       <c r="Y325" s="22" t="n"/>
       <c r="Z325" s="61" t="n"/>
@@ -66233,7 +66241,9 @@
       <c r="T334" s="61" t="n"/>
       <c r="U334" s="22" t="n"/>
       <c r="V334" s="61" t="n"/>
-      <c r="W334" s="22" t="n"/>
+      <c r="W334" s="22" t="n">
+        <v>32</v>
+      </c>
       <c r="X334" s="61" t="n"/>
       <c r="Y334" s="22" t="n"/>
       <c r="Z334" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -38824,7 +38824,9 @@
       <c r="U18" s="100" t="n"/>
       <c r="V18" s="22" t="n"/>
       <c r="W18" s="100" t="n"/>
-      <c r="X18" s="22" t="n"/>
+      <c r="X18" s="22" t="n">
+        <v>2178</v>
+      </c>
       <c r="Y18" s="100" t="n"/>
       <c r="Z18" s="22" t="n"/>
       <c r="AA18" s="100" t="n"/>
@@ -40699,7 +40701,9 @@
       <c r="U55" s="100" t="n"/>
       <c r="V55" s="22" t="n"/>
       <c r="W55" s="100" t="n"/>
-      <c r="X55" s="22" t="n"/>
+      <c r="X55" s="22" t="n">
+        <v>1180</v>
+      </c>
       <c r="Y55" s="100" t="n"/>
       <c r="Z55" s="22" t="n"/>
       <c r="AA55" s="100" t="n"/>
@@ -50471,7 +50475,9 @@
       <c r="V54" s="61" t="n"/>
       <c r="W54" s="22" t="n"/>
       <c r="X54" s="61" t="n"/>
-      <c r="Y54" s="22" t="n"/>
+      <c r="Y54" s="22" t="n">
+        <v>141</v>
+      </c>
       <c r="Z54" s="61" t="n"/>
       <c r="AA54" s="22" t="n"/>
       <c r="AB54" s="61" t="n"/>
@@ -66709,7 +66715,9 @@
       <c r="V342" s="61" t="n"/>
       <c r="W342" s="22" t="n"/>
       <c r="X342" s="61" t="n"/>
-      <c r="Y342" s="22" t="n"/>
+      <c r="Y342" s="22" t="n">
+        <v>20</v>
+      </c>
       <c r="Z342" s="61" t="n"/>
       <c r="AA342" s="22" t="n"/>
       <c r="AB342" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -38088,9 +38088,7 @@
       <c r="O4" s="100" t="n"/>
       <c r="P4" s="22" t="n"/>
       <c r="Q4" s="100" t="n"/>
-      <c r="R4" s="22" t="n">
-        <v>95</v>
-      </c>
+      <c r="R4" s="22" t="n"/>
       <c r="S4" s="100" t="n"/>
       <c r="T4" s="22" t="n"/>
       <c r="U4" s="100" t="n"/>
@@ -38140,9 +38138,7 @@
       <c r="M5" s="100" t="n"/>
       <c r="N5" s="22" t="n"/>
       <c r="O5" s="100" t="n"/>
-      <c r="P5" s="22" t="n">
-        <v>2166</v>
-      </c>
+      <c r="P5" s="22" t="n"/>
       <c r="Q5" s="100" t="n"/>
       <c r="R5" s="22" t="n"/>
       <c r="S5" s="100" t="n"/>
@@ -38184,9 +38180,7 @@
       <c r="G6" s="100" t="n">
         <v>554</v>
       </c>
-      <c r="H6" s="22" t="n">
-        <v>554</v>
-      </c>
+      <c r="H6" s="22" t="n"/>
       <c r="I6" s="100" t="n">
         <v>2600</v>
       </c>
@@ -38244,9 +38238,7 @@
       <c r="K7" s="100" t="n">
         <v>1744</v>
       </c>
-      <c r="L7" s="22" t="n">
-        <v>48</v>
-      </c>
+      <c r="L7" s="22" t="n"/>
       <c r="M7" s="100" t="n">
         <v>422</v>
       </c>
@@ -38354,15 +38346,11 @@
       <c r="O9" s="100" t="n">
         <v>636</v>
       </c>
-      <c r="P9" s="22" t="n">
-        <v>740</v>
-      </c>
+      <c r="P9" s="22" t="n"/>
       <c r="Q9" s="100" t="n"/>
       <c r="R9" s="22" t="n"/>
       <c r="S9" s="100" t="n"/>
-      <c r="T9" s="22" t="n">
-        <v>416</v>
-      </c>
+      <c r="T9" s="22" t="n"/>
       <c r="U9" s="100" t="n"/>
       <c r="V9" s="22" t="n"/>
       <c r="W9" s="100" t="n"/>
@@ -38508,9 +38496,7 @@
       <c r="O12" s="100" t="n">
         <v>1724</v>
       </c>
-      <c r="P12" s="22" t="n">
-        <v>36</v>
-      </c>
+      <c r="P12" s="22" t="n"/>
       <c r="Q12" s="100" t="n"/>
       <c r="R12" s="22" t="n"/>
       <c r="S12" s="100" t="n"/>
@@ -38562,13 +38548,9 @@
       </c>
       <c r="P13" s="22" t="n"/>
       <c r="Q13" s="100" t="n"/>
-      <c r="R13" s="22" t="n">
-        <v>152</v>
-      </c>
+      <c r="R13" s="22" t="n"/>
       <c r="S13" s="100" t="n"/>
-      <c r="T13" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="T13" s="22" t="n"/>
       <c r="U13" s="100" t="n"/>
       <c r="V13" s="22" t="n"/>
       <c r="W13" s="100" t="n"/>
@@ -38824,9 +38806,7 @@
       <c r="U18" s="100" t="n"/>
       <c r="V18" s="22" t="n"/>
       <c r="W18" s="100" t="n"/>
-      <c r="X18" s="22" t="n">
-        <v>2178</v>
-      </c>
+      <c r="X18" s="22" t="n"/>
       <c r="Y18" s="100" t="n"/>
       <c r="Z18" s="22" t="n"/>
       <c r="AA18" s="100" t="n"/>
@@ -39981,9 +39961,7 @@
       <c r="O41" s="100" t="n"/>
       <c r="P41" s="22" t="n"/>
       <c r="Q41" s="100" t="n"/>
-      <c r="R41" s="22" t="n">
-        <v>28</v>
-      </c>
+      <c r="R41" s="22" t="n"/>
       <c r="S41" s="100" t="n"/>
       <c r="T41" s="22" t="n"/>
       <c r="U41" s="100" t="n"/>
@@ -40029,9 +40007,7 @@
       <c r="M42" s="100" t="n"/>
       <c r="N42" s="22" t="n"/>
       <c r="O42" s="100" t="n"/>
-      <c r="P42" s="22" t="n">
-        <v>540</v>
-      </c>
+      <c r="P42" s="22" t="n"/>
       <c r="Q42" s="100" t="n"/>
       <c r="R42" s="22" t="n"/>
       <c r="S42" s="100" t="n"/>
@@ -40073,9 +40049,7 @@
       <c r="G43" s="100" t="n">
         <v>20</v>
       </c>
-      <c r="H43" s="22" t="n">
-        <v>64</v>
-      </c>
+      <c r="H43" s="22" t="n"/>
       <c r="I43" s="100" t="n">
         <v>560</v>
       </c>
@@ -40235,9 +40209,7 @@
       </c>
       <c r="N46" s="22" t="n"/>
       <c r="O46" s="100" t="n"/>
-      <c r="P46" s="22" t="n">
-        <v>72</v>
-      </c>
+      <c r="P46" s="22" t="n"/>
       <c r="Q46" s="100" t="n"/>
       <c r="R46" s="22" t="n"/>
       <c r="S46" s="100" t="n"/>
@@ -40289,9 +40261,7 @@
       <c r="O47" s="100" t="n"/>
       <c r="P47" s="22" t="n"/>
       <c r="Q47" s="100" t="n"/>
-      <c r="R47" s="22" t="n">
-        <v>4</v>
-      </c>
+      <c r="R47" s="22" t="n"/>
       <c r="S47" s="100" t="n"/>
       <c r="T47" s="22" t="n"/>
       <c r="U47" s="100" t="n"/>
@@ -40343,9 +40313,7 @@
       <c r="S48" s="100" t="n"/>
       <c r="T48" s="22" t="n"/>
       <c r="U48" s="100" t="n"/>
-      <c r="V48" s="22" t="n">
-        <v>38</v>
-      </c>
+      <c r="V48" s="22" t="n"/>
       <c r="W48" s="100" t="n"/>
       <c r="X48" s="22" t="n"/>
       <c r="Y48" s="100" t="n"/>
@@ -40701,9 +40669,7 @@
       <c r="U55" s="100" t="n"/>
       <c r="V55" s="22" t="n"/>
       <c r="W55" s="100" t="n"/>
-      <c r="X55" s="22" t="n">
-        <v>1180</v>
-      </c>
+      <c r="X55" s="22" t="n"/>
       <c r="Y55" s="100" t="n"/>
       <c r="Z55" s="22" t="n"/>
       <c r="AA55" s="100" t="n"/>
@@ -40956,9 +40922,7 @@
       <c r="U60" s="100" t="n">
         <v>1296</v>
       </c>
-      <c r="V60" s="22" t="n">
-        <v>1500</v>
-      </c>
+      <c r="V60" s="22" t="n"/>
       <c r="W60" s="100" t="n"/>
       <c r="X60" s="22" t="n"/>
       <c r="Y60" s="100" t="n"/>
@@ -47715,9 +47679,7 @@
       <c r="H6" s="61" t="n"/>
       <c r="I6" s="22" t="n"/>
       <c r="J6" s="61" t="n"/>
-      <c r="K6" s="22" t="n">
-        <v>67</v>
-      </c>
+      <c r="K6" s="22" t="n"/>
       <c r="L6" s="61" t="n"/>
       <c r="M6" s="22" t="n"/>
       <c r="N6" s="61" t="n"/>
@@ -48001,13 +47963,9 @@
       <c r="L11" s="61" t="n">
         <v>22</v>
       </c>
-      <c r="M11" s="22" t="n">
-        <v>15</v>
-      </c>
+      <c r="M11" s="22" t="n"/>
       <c r="N11" s="61" t="n"/>
-      <c r="O11" s="22" t="n">
-        <v>22</v>
-      </c>
+      <c r="O11" s="22" t="n"/>
       <c r="P11" s="61" t="n"/>
       <c r="Q11" s="22" t="n"/>
       <c r="R11" s="61" t="n"/>
@@ -48287,9 +48245,7 @@
       </c>
       <c r="M16" s="22" t="n"/>
       <c r="N16" s="61" t="n"/>
-      <c r="O16" s="22" t="n">
-        <v>74</v>
-      </c>
+      <c r="O16" s="22" t="n"/>
       <c r="P16" s="61" t="n"/>
       <c r="Q16" s="22" t="n"/>
       <c r="R16" s="61" t="n"/>
@@ -48347,9 +48303,7 @@
       <c r="N17" s="61" t="n">
         <v>45</v>
       </c>
-      <c r="O17" s="22" t="n">
-        <v>9</v>
-      </c>
+      <c r="O17" s="22" t="n"/>
       <c r="P17" s="61" t="n"/>
       <c r="Q17" s="22" t="n"/>
       <c r="R17" s="61" t="n"/>
@@ -48411,9 +48365,7 @@
       <c r="R18" s="61" t="n"/>
       <c r="S18" s="22" t="n"/>
       <c r="T18" s="61" t="n"/>
-      <c r="U18" s="22" t="n">
-        <v>46</v>
-      </c>
+      <c r="U18" s="22" t="n"/>
       <c r="V18" s="61" t="n"/>
       <c r="W18" s="22" t="n"/>
       <c r="X18" s="61" t="n"/>
@@ -48577,9 +48529,7 @@
       </c>
       <c r="O21" s="22" t="n"/>
       <c r="P21" s="61" t="n"/>
-      <c r="Q21" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q21" s="22" t="n"/>
       <c r="R21" s="61" t="n"/>
       <c r="S21" s="22" t="n"/>
       <c r="T21" s="61" t="n"/>
@@ -48695,9 +48645,7 @@
       <c r="R23" s="61" t="n"/>
       <c r="S23" s="22" t="n"/>
       <c r="T23" s="61" t="n"/>
-      <c r="U23" s="22" t="n">
-        <v>93</v>
-      </c>
+      <c r="U23" s="22" t="n"/>
       <c r="V23" s="61" t="n"/>
       <c r="W23" s="22" t="n"/>
       <c r="X23" s="61" t="n"/>
@@ -48869,9 +48817,7 @@
       <c r="T26" s="61" t="n"/>
       <c r="U26" s="22" t="n"/>
       <c r="V26" s="61" t="n"/>
-      <c r="W26" s="22" t="n">
-        <v>85</v>
-      </c>
+      <c r="W26" s="22" t="n"/>
       <c r="X26" s="61" t="n"/>
       <c r="Y26" s="22" t="n"/>
       <c r="Z26" s="61" t="n"/>
@@ -48925,9 +48871,7 @@
       <c r="R27" s="61" t="n"/>
       <c r="S27" s="22" t="n"/>
       <c r="T27" s="61" t="n"/>
-      <c r="U27" s="22" t="n">
-        <v>55</v>
-      </c>
+      <c r="U27" s="22" t="n"/>
       <c r="V27" s="61" t="n"/>
       <c r="W27" s="22" t="n"/>
       <c r="X27" s="61" t="n"/>
@@ -48983,9 +48927,7 @@
       <c r="R28" s="61" t="n"/>
       <c r="S28" s="22" t="n"/>
       <c r="T28" s="61" t="n"/>
-      <c r="U28" s="22" t="n">
-        <v>52</v>
-      </c>
+      <c r="U28" s="22" t="n"/>
       <c r="V28" s="61" t="n"/>
       <c r="W28" s="22" t="n"/>
       <c r="X28" s="61" t="n"/>
@@ -49095,9 +49037,7 @@
       </c>
       <c r="Q30" s="22" t="n"/>
       <c r="R30" s="61" t="n"/>
-      <c r="S30" s="22" t="n">
-        <v>45</v>
-      </c>
+      <c r="S30" s="22" t="n"/>
       <c r="T30" s="61" t="n"/>
       <c r="U30" s="22" t="n"/>
       <c r="V30" s="61" t="n"/>
@@ -49157,9 +49097,7 @@
       </c>
       <c r="S31" s="22" t="n"/>
       <c r="T31" s="61" t="n"/>
-      <c r="U31" s="22" t="n">
-        <v>26</v>
-      </c>
+      <c r="U31" s="22" t="n"/>
       <c r="V31" s="61" t="n"/>
       <c r="W31" s="22" t="n"/>
       <c r="X31" s="61" t="n"/>
@@ -49763,9 +49701,7 @@
       <c r="H42" s="61" t="n"/>
       <c r="I42" s="22" t="n"/>
       <c r="J42" s="61" t="n"/>
-      <c r="K42" s="22" t="n">
-        <v>38</v>
-      </c>
+      <c r="K42" s="22" t="n"/>
       <c r="L42" s="61" t="n"/>
       <c r="M42" s="22" t="n"/>
       <c r="N42" s="61" t="n"/>
@@ -49937,13 +49873,9 @@
       <c r="L45" s="61" t="n">
         <v>63</v>
       </c>
-      <c r="M45" s="22" t="n">
-        <v>93</v>
-      </c>
+      <c r="M45" s="22" t="n"/>
       <c r="N45" s="61" t="n"/>
-      <c r="O45" s="22" t="n">
-        <v>63</v>
-      </c>
+      <c r="O45" s="22" t="n"/>
       <c r="P45" s="61" t="n"/>
       <c r="Q45" s="22" t="n"/>
       <c r="R45" s="61" t="n"/>
@@ -50001,9 +49933,7 @@
       <c r="N46" s="61" t="n"/>
       <c r="O46" s="22" t="n"/>
       <c r="P46" s="61" t="n"/>
-      <c r="Q46" s="22" t="n">
-        <v>12</v>
-      </c>
+      <c r="Q46" s="22" t="n"/>
       <c r="R46" s="61" t="n"/>
       <c r="S46" s="22" t="n"/>
       <c r="T46" s="61" t="n"/>
@@ -50059,15 +49989,11 @@
       <c r="N47" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="O47" s="22" t="n">
-        <v>160</v>
-      </c>
+      <c r="O47" s="22" t="n"/>
       <c r="P47" s="61" t="n"/>
       <c r="Q47" s="22" t="n"/>
       <c r="R47" s="61" t="n"/>
-      <c r="S47" s="22" t="n">
-        <v>80</v>
-      </c>
+      <c r="S47" s="22" t="n"/>
       <c r="T47" s="61" t="n"/>
       <c r="U47" s="22" t="n"/>
       <c r="V47" s="61" t="n"/>
@@ -50297,9 +50223,7 @@
       <c r="T51" s="61" t="n"/>
       <c r="U51" s="22" t="n"/>
       <c r="V51" s="61" t="n"/>
-      <c r="W51" s="22" t="n">
-        <v>311</v>
-      </c>
+      <c r="W51" s="22" t="n"/>
       <c r="X51" s="61" t="n"/>
       <c r="Y51" s="22" t="n"/>
       <c r="Z51" s="61" t="n"/>
@@ -50353,13 +50277,9 @@
       <c r="R52" s="61" t="n">
         <v>88</v>
       </c>
-      <c r="S52" s="22" t="n">
-        <v>289</v>
-      </c>
+      <c r="S52" s="22" t="n"/>
       <c r="T52" s="61" t="n"/>
-      <c r="U52" s="22" t="n">
-        <v>132</v>
-      </c>
+      <c r="U52" s="22" t="n"/>
       <c r="V52" s="61" t="n"/>
       <c r="W52" s="22" t="n"/>
       <c r="X52" s="61" t="n"/>
@@ -50475,9 +50395,7 @@
       <c r="V54" s="61" t="n"/>
       <c r="W54" s="22" t="n"/>
       <c r="X54" s="61" t="n"/>
-      <c r="Y54" s="22" t="n">
-        <v>141</v>
-      </c>
+      <c r="Y54" s="22" t="n"/>
       <c r="Z54" s="61" t="n"/>
       <c r="AA54" s="22" t="n"/>
       <c r="AB54" s="61" t="n"/>
@@ -50753,9 +50671,7 @@
       <c r="T59" s="61" t="n">
         <v>93</v>
       </c>
-      <c r="U59" s="22" t="n">
-        <v>5</v>
-      </c>
+      <c r="U59" s="22" t="n"/>
       <c r="V59" s="61" t="n"/>
       <c r="W59" s="22" t="n"/>
       <c r="X59" s="61" t="n"/>
@@ -50925,9 +50841,7 @@
       </c>
       <c r="U62" s="22" t="n"/>
       <c r="V62" s="61" t="n"/>
-      <c r="W62" s="22" t="n">
-        <v>117</v>
-      </c>
+      <c r="W62" s="22" t="n"/>
       <c r="X62" s="61" t="n"/>
       <c r="Y62" s="22" t="n"/>
       <c r="Z62" s="61" t="n"/>
@@ -52033,13 +51947,9 @@
       <c r="J82" s="61" t="n"/>
       <c r="K82" s="22" t="n"/>
       <c r="L82" s="61" t="n"/>
-      <c r="M82" s="22" t="n">
-        <v>76</v>
-      </c>
+      <c r="M82" s="22" t="n"/>
       <c r="N82" s="61" t="n"/>
-      <c r="O82" s="22" t="n">
-        <v>62</v>
-      </c>
+      <c r="O82" s="22" t="n"/>
       <c r="P82" s="61" t="n"/>
       <c r="Q82" s="22" t="n"/>
       <c r="R82" s="61" t="n"/>
@@ -52151,9 +52061,7 @@
       <c r="L84" s="61" t="n"/>
       <c r="M84" s="22" t="n"/>
       <c r="N84" s="61" t="n"/>
-      <c r="O84" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="O84" s="22" t="n"/>
       <c r="P84" s="61" t="n"/>
       <c r="Q84" s="22" t="n"/>
       <c r="R84" s="61" t="n"/>
@@ -52211,9 +52119,7 @@
       <c r="L85" s="61" t="n"/>
       <c r="M85" s="22" t="n"/>
       <c r="N85" s="61" t="n"/>
-      <c r="O85" s="22" t="n">
-        <v>6</v>
-      </c>
+      <c r="O85" s="22" t="n"/>
       <c r="P85" s="61" t="n"/>
       <c r="Q85" s="22" t="n"/>
       <c r="R85" s="61" t="n"/>
@@ -52325,9 +52231,7 @@
       <c r="N87" s="61" t="n"/>
       <c r="O87" s="22" t="n"/>
       <c r="P87" s="61" t="n"/>
-      <c r="Q87" s="22" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q87" s="22" t="n"/>
       <c r="R87" s="61" t="n"/>
       <c r="S87" s="22" t="n"/>
       <c r="T87" s="61" t="n"/>
@@ -52381,9 +52285,7 @@
       <c r="L88" s="61" t="n"/>
       <c r="M88" s="22" t="n"/>
       <c r="N88" s="61" t="n"/>
-      <c r="O88" s="22" t="n">
-        <v>14</v>
-      </c>
+      <c r="O88" s="22" t="n"/>
       <c r="P88" s="61" t="n"/>
       <c r="Q88" s="22" t="n"/>
       <c r="R88" s="61" t="n"/>
@@ -52439,9 +52341,7 @@
       <c r="L89" s="61" t="n"/>
       <c r="M89" s="22" t="n"/>
       <c r="N89" s="61" t="n"/>
-      <c r="O89" s="22" t="n">
-        <v>11</v>
-      </c>
+      <c r="O89" s="22" t="n"/>
       <c r="P89" s="61" t="n"/>
       <c r="Q89" s="22" t="n"/>
       <c r="R89" s="61" t="n"/>
@@ -52497,9 +52397,7 @@
       <c r="L90" s="61" t="n"/>
       <c r="M90" s="22" t="n"/>
       <c r="N90" s="61" t="n"/>
-      <c r="O90" s="22" t="n">
-        <v>14</v>
-      </c>
+      <c r="O90" s="22" t="n"/>
       <c r="P90" s="61" t="n"/>
       <c r="Q90" s="22" t="n"/>
       <c r="R90" s="61" t="n"/>
@@ -52937,9 +52835,7 @@
       </c>
       <c r="K98" s="22" t="n"/>
       <c r="L98" s="61" t="n"/>
-      <c r="M98" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="M98" s="22" t="n"/>
       <c r="N98" s="61" t="n"/>
       <c r="O98" s="22" t="n"/>
       <c r="P98" s="61" t="n"/>
@@ -53053,9 +52949,7 @@
       <c r="N100" s="61" t="n"/>
       <c r="O100" s="22" t="n"/>
       <c r="P100" s="61" t="n"/>
-      <c r="Q100" s="22" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q100" s="22" t="n"/>
       <c r="R100" s="61" t="n"/>
       <c r="S100" s="22" t="n"/>
       <c r="T100" s="61" t="n"/>
@@ -53165,9 +53059,7 @@
       </c>
       <c r="M102" s="22" t="n"/>
       <c r="N102" s="61" t="n"/>
-      <c r="O102" s="22" t="n">
-        <v>10</v>
-      </c>
+      <c r="O102" s="22" t="n"/>
       <c r="P102" s="61" t="n"/>
       <c r="Q102" s="22" t="n"/>
       <c r="R102" s="61" t="n"/>
@@ -53279,9 +53171,7 @@
       <c r="N104" s="61" t="n"/>
       <c r="O104" s="22" t="n"/>
       <c r="P104" s="61" t="n"/>
-      <c r="Q104" s="22" t="n">
-        <v>31</v>
-      </c>
+      <c r="Q104" s="22" t="n"/>
       <c r="R104" s="61" t="n"/>
       <c r="S104" s="22" t="n"/>
       <c r="T104" s="61" t="n"/>
@@ -53391,9 +53281,7 @@
       </c>
       <c r="M106" s="22" t="n"/>
       <c r="N106" s="61" t="n"/>
-      <c r="O106" s="22" t="n">
-        <v>1</v>
-      </c>
+      <c r="O106" s="22" t="n"/>
       <c r="P106" s="61" t="n"/>
       <c r="Q106" s="22" t="n"/>
       <c r="R106" s="61" t="n"/>
@@ -53825,9 +53713,7 @@
       <c r="H114" s="61" t="n"/>
       <c r="I114" s="22" t="n"/>
       <c r="J114" s="61" t="n"/>
-      <c r="K114" s="22" t="n">
-        <v>5</v>
-      </c>
+      <c r="K114" s="22" t="n"/>
       <c r="L114" s="61" t="n"/>
       <c r="M114" s="22" t="n"/>
       <c r="N114" s="61" t="n"/>
@@ -53997,9 +53883,7 @@
       </c>
       <c r="K117" s="22" t="n"/>
       <c r="L117" s="61" t="n"/>
-      <c r="M117" s="22" t="n">
-        <v>28</v>
-      </c>
+      <c r="M117" s="22" t="n"/>
       <c r="N117" s="61" t="n"/>
       <c r="O117" s="22" t="n"/>
       <c r="P117" s="61" t="n"/>
@@ -54055,13 +53939,9 @@
       </c>
       <c r="K118" s="22" t="n"/>
       <c r="L118" s="61" t="n"/>
-      <c r="M118" s="22" t="n">
-        <v>12</v>
-      </c>
+      <c r="M118" s="22" t="n"/>
       <c r="N118" s="61" t="n"/>
-      <c r="O118" s="22" t="n">
-        <v>12</v>
-      </c>
+      <c r="O118" s="22" t="n"/>
       <c r="P118" s="61" t="n"/>
       <c r="Q118" s="22" t="n"/>
       <c r="R118" s="61" t="n"/>
@@ -54117,13 +53997,9 @@
       <c r="L119" s="61" t="n">
         <v>58</v>
       </c>
-      <c r="M119" s="22" t="n">
-        <v>34</v>
-      </c>
+      <c r="M119" s="22" t="n"/>
       <c r="N119" s="61" t="n"/>
-      <c r="O119" s="22" t="n">
-        <v>58</v>
-      </c>
+      <c r="O119" s="22" t="n"/>
       <c r="P119" s="61" t="n"/>
       <c r="Q119" s="22" t="n"/>
       <c r="R119" s="61" t="n"/>
@@ -54347,9 +54223,7 @@
       <c r="N123" s="61" t="n"/>
       <c r="O123" s="22" t="n"/>
       <c r="P123" s="61" t="n"/>
-      <c r="Q123" s="22" t="n">
-        <v>38</v>
-      </c>
+      <c r="Q123" s="22" t="n"/>
       <c r="R123" s="61" t="n"/>
       <c r="S123" s="22" t="n"/>
       <c r="T123" s="61" t="n"/>
@@ -54405,13 +54279,9 @@
       <c r="N124" s="61" t="n">
         <v>39</v>
       </c>
-      <c r="O124" s="22" t="n">
-        <v>36</v>
-      </c>
+      <c r="O124" s="22" t="n"/>
       <c r="P124" s="61" t="n"/>
-      <c r="Q124" s="22" t="n">
-        <v>42</v>
-      </c>
+      <c r="Q124" s="22" t="n"/>
       <c r="R124" s="61" t="n"/>
       <c r="S124" s="22" t="n"/>
       <c r="T124" s="61" t="n"/>
@@ -54525,9 +54395,7 @@
       <c r="P126" s="61" t="n"/>
       <c r="Q126" s="22" t="n"/>
       <c r="R126" s="61" t="n"/>
-      <c r="S126" s="22" t="n">
-        <v>45</v>
-      </c>
+      <c r="S126" s="22" t="n"/>
       <c r="T126" s="61" t="n"/>
       <c r="U126" s="22" t="n"/>
       <c r="V126" s="61" t="n"/>
@@ -54693,9 +54561,7 @@
       </c>
       <c r="O129" s="22" t="n"/>
       <c r="P129" s="61" t="n"/>
-      <c r="Q129" s="22" t="n">
-        <v>9</v>
-      </c>
+      <c r="Q129" s="22" t="n"/>
       <c r="R129" s="61" t="n"/>
       <c r="S129" s="22" t="n"/>
       <c r="T129" s="61" t="n"/>
@@ -55031,9 +54897,7 @@
       <c r="R135" s="61" t="n"/>
       <c r="S135" s="22" t="n"/>
       <c r="T135" s="61" t="n"/>
-      <c r="U135" s="22" t="n">
-        <v>38</v>
-      </c>
+      <c r="U135" s="22" t="n"/>
       <c r="V135" s="61" t="n"/>
       <c r="W135" s="22" t="n"/>
       <c r="X135" s="61" t="n"/>
@@ -55085,9 +54949,7 @@
       </c>
       <c r="O136" s="22" t="n"/>
       <c r="P136" s="61" t="n"/>
-      <c r="Q136" s="22" t="n">
-        <v>45</v>
-      </c>
+      <c r="Q136" s="22" t="n"/>
       <c r="R136" s="61" t="n"/>
       <c r="S136" s="22" t="n"/>
       <c r="T136" s="61" t="n"/>
@@ -55425,9 +55287,7 @@
       </c>
       <c r="Q142" s="22" t="n"/>
       <c r="R142" s="61" t="n"/>
-      <c r="S142" s="22" t="n">
-        <v>30</v>
-      </c>
+      <c r="S142" s="22" t="n"/>
       <c r="T142" s="61" t="n"/>
       <c r="U142" s="22" t="n"/>
       <c r="V142" s="61" t="n"/>
@@ -55485,9 +55345,7 @@
       <c r="R143" s="61" t="n"/>
       <c r="S143" s="22" t="n"/>
       <c r="T143" s="61" t="n"/>
-      <c r="U143" s="22" t="n">
-        <v>3</v>
-      </c>
+      <c r="U143" s="22" t="n"/>
       <c r="V143" s="61" t="n"/>
       <c r="W143" s="22" t="n"/>
       <c r="X143" s="61" t="n"/>
@@ -55545,9 +55403,7 @@
       <c r="T144" s="61" t="n"/>
       <c r="U144" s="22" t="n"/>
       <c r="V144" s="61" t="n"/>
-      <c r="W144" s="22" t="n">
-        <v>12</v>
-      </c>
+      <c r="W144" s="22" t="n"/>
       <c r="X144" s="61" t="n"/>
       <c r="Y144" s="22" t="n"/>
       <c r="Z144" s="61" t="n"/>
@@ -55601,9 +55457,7 @@
       <c r="R145" s="61" t="n"/>
       <c r="S145" s="22" t="n"/>
       <c r="T145" s="61" t="n"/>
-      <c r="U145" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="U145" s="22" t="n"/>
       <c r="V145" s="61" t="n"/>
       <c r="W145" s="22" t="n"/>
       <c r="X145" s="61" t="n"/>
@@ -56375,9 +56229,7 @@
       <c r="N159" s="61" t="n"/>
       <c r="O159" s="22" t="n"/>
       <c r="P159" s="61" t="n"/>
-      <c r="Q159" s="22" t="n">
-        <v>33</v>
-      </c>
+      <c r="Q159" s="22" t="n"/>
       <c r="R159" s="61" t="n"/>
       <c r="S159" s="22" t="n"/>
       <c r="T159" s="61" t="n"/>
@@ -56431,9 +56283,7 @@
       </c>
       <c r="M160" s="22" t="n"/>
       <c r="N160" s="61" t="n"/>
-      <c r="O160" s="22" t="n">
-        <v>59</v>
-      </c>
+      <c r="O160" s="22" t="n"/>
       <c r="P160" s="61" t="n"/>
       <c r="Q160" s="22" t="n"/>
       <c r="R160" s="61" t="n"/>
@@ -56547,9 +56397,7 @@
       <c r="P162" s="61" t="n"/>
       <c r="Q162" s="22" t="n"/>
       <c r="R162" s="61" t="n"/>
-      <c r="S162" s="22" t="n">
-        <v>1</v>
-      </c>
+      <c r="S162" s="22" t="n"/>
       <c r="T162" s="61" t="n"/>
       <c r="U162" s="22" t="n"/>
       <c r="V162" s="61" t="n"/>
@@ -56711,9 +56559,7 @@
       </c>
       <c r="M165" s="22" t="n"/>
       <c r="N165" s="61" t="n"/>
-      <c r="O165" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="O165" s="22" t="n"/>
       <c r="P165" s="61" t="n"/>
       <c r="Q165" s="22" t="n"/>
       <c r="R165" s="61" t="n"/>
@@ -56933,9 +56779,7 @@
       <c r="N169" s="61" t="n"/>
       <c r="O169" s="22" t="n"/>
       <c r="P169" s="61" t="n"/>
-      <c r="Q169" s="22" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q169" s="22" t="n"/>
       <c r="R169" s="61" t="n"/>
       <c r="S169" s="22" t="n"/>
       <c r="T169" s="61" t="n"/>
@@ -56989,9 +56833,7 @@
       </c>
       <c r="M170" s="22" t="n"/>
       <c r="N170" s="61" t="n"/>
-      <c r="O170" s="22" t="n">
-        <v>9</v>
-      </c>
+      <c r="O170" s="22" t="n"/>
       <c r="P170" s="61" t="n"/>
       <c r="Q170" s="22" t="n"/>
       <c r="R170" s="61" t="n"/>
@@ -57053,9 +56895,7 @@
       <c r="R171" s="61" t="n"/>
       <c r="S171" s="22" t="n"/>
       <c r="T171" s="61" t="n"/>
-      <c r="U171" s="22" t="n">
-        <v>9</v>
-      </c>
+      <c r="U171" s="22" t="n"/>
       <c r="V171" s="61" t="n"/>
       <c r="W171" s="22" t="n"/>
       <c r="X171" s="61" t="n"/>
@@ -57215,9 +57055,7 @@
       </c>
       <c r="M174" s="22" t="n"/>
       <c r="N174" s="61" t="n"/>
-      <c r="O174" s="22" t="n">
-        <v>6</v>
-      </c>
+      <c r="O174" s="22" t="n"/>
       <c r="P174" s="61" t="n"/>
       <c r="Q174" s="22" t="n"/>
       <c r="R174" s="61" t="n"/>
@@ -57329,9 +57167,7 @@
       <c r="N176" s="61" t="n"/>
       <c r="O176" s="22" t="n"/>
       <c r="P176" s="61" t="n"/>
-      <c r="Q176" s="22" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q176" s="22" t="n"/>
       <c r="R176" s="61" t="n"/>
       <c r="S176" s="22" t="n"/>
       <c r="T176" s="61" t="n"/>
@@ -57555,9 +57391,7 @@
       <c r="N180" s="61" t="n"/>
       <c r="O180" s="22" t="n"/>
       <c r="P180" s="61" t="n"/>
-      <c r="Q180" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q180" s="22" t="n"/>
       <c r="R180" s="61" t="n"/>
       <c r="S180" s="22" t="n"/>
       <c r="T180" s="61" t="n"/>
@@ -57839,9 +57673,7 @@
       <c r="P185" s="61" t="n"/>
       <c r="Q185" s="22" t="n"/>
       <c r="R185" s="61" t="n"/>
-      <c r="S185" s="22" t="n">
-        <v>198</v>
-      </c>
+      <c r="S185" s="22" t="n"/>
       <c r="T185" s="61" t="n"/>
       <c r="U185" s="22" t="n"/>
       <c r="V185" s="61" t="n"/>
@@ -57889,9 +57721,7 @@
       </c>
       <c r="I186" s="22" t="n"/>
       <c r="J186" s="61" t="n"/>
-      <c r="K186" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="K186" s="22" t="n"/>
       <c r="L186" s="61" t="n"/>
       <c r="M186" s="22" t="n"/>
       <c r="N186" s="61" t="n"/>
@@ -57901,9 +57731,7 @@
       <c r="R186" s="61" t="n"/>
       <c r="S186" s="22" t="n"/>
       <c r="T186" s="61" t="n"/>
-      <c r="U186" s="22" t="n">
-        <v>634</v>
-      </c>
+      <c r="U186" s="22" t="n"/>
       <c r="V186" s="61" t="n"/>
       <c r="W186" s="22" t="n"/>
       <c r="X186" s="61" t="n"/>
@@ -58129,9 +57957,7 @@
       <c r="T190" s="61" t="n"/>
       <c r="U190" s="22" t="n"/>
       <c r="V190" s="61" t="n"/>
-      <c r="W190" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="W190" s="22" t="n"/>
       <c r="X190" s="61" t="n"/>
       <c r="Y190" s="22" t="n"/>
       <c r="Z190" s="61" t="n">
@@ -59651,9 +59477,7 @@
       <c r="T217" s="61" t="n"/>
       <c r="U217" s="22" t="n"/>
       <c r="V217" s="61" t="n"/>
-      <c r="W217" s="22" t="n">
-        <v>44</v>
-      </c>
+      <c r="W217" s="22" t="n"/>
       <c r="X217" s="61" t="n"/>
       <c r="Y217" s="22" t="n"/>
       <c r="Z217" s="61" t="n"/>
@@ -59921,9 +59745,7 @@
       </c>
       <c r="I222" s="22" t="n"/>
       <c r="J222" s="61" t="n"/>
-      <c r="K222" s="22" t="n">
-        <v>16</v>
-      </c>
+      <c r="K222" s="22" t="n"/>
       <c r="L222" s="61" t="n"/>
       <c r="M222" s="22" t="n"/>
       <c r="N222" s="61" t="n"/>
@@ -59933,9 +59755,7 @@
       <c r="R222" s="61" t="n"/>
       <c r="S222" s="22" t="n"/>
       <c r="T222" s="61" t="n"/>
-      <c r="U222" s="22" t="n">
-        <v>1119</v>
-      </c>
+      <c r="U222" s="22" t="n"/>
       <c r="V222" s="61" t="n"/>
       <c r="W222" s="22" t="n"/>
       <c r="X222" s="61" t="n"/>
@@ -60165,9 +59985,7 @@
       </c>
       <c r="U226" s="22" t="n"/>
       <c r="V226" s="61" t="n"/>
-      <c r="W226" s="22" t="n">
-        <v>4200</v>
-      </c>
+      <c r="W226" s="22" t="n"/>
       <c r="X226" s="61" t="n"/>
       <c r="Y226" s="22" t="n"/>
       <c r="Z226" s="61" t="n"/>
@@ -60507,9 +60325,7 @@
       </c>
       <c r="W232" s="22" t="n"/>
       <c r="X232" s="61" t="n"/>
-      <c r="Y232" s="22" t="n">
-        <v>564</v>
-      </c>
+      <c r="Y232" s="22" t="n"/>
       <c r="Z232" s="61" t="n"/>
       <c r="AA232" s="22" t="n"/>
       <c r="AB232" s="61" t="n"/>
@@ -61843,9 +61659,7 @@
       <c r="J256" s="61" t="n"/>
       <c r="K256" s="22" t="n"/>
       <c r="L256" s="61" t="n"/>
-      <c r="M256" s="22" t="n">
-        <v>86</v>
-      </c>
+      <c r="M256" s="22" t="n"/>
       <c r="N256" s="61" t="n"/>
       <c r="O256" s="22" t="n"/>
       <c r="P256" s="61" t="n"/>
@@ -61909,9 +61723,7 @@
       <c r="P257" s="61" t="n"/>
       <c r="Q257" s="22" t="n"/>
       <c r="R257" s="61" t="n"/>
-      <c r="S257" s="22" t="n">
-        <v>210</v>
-      </c>
+      <c r="S257" s="22" t="n"/>
       <c r="T257" s="61" t="n"/>
       <c r="U257" s="22" t="n"/>
       <c r="V257" s="61" t="n"/>
@@ -61963,9 +61775,7 @@
       <c r="N258" s="61" t="n"/>
       <c r="O258" s="22" t="n"/>
       <c r="P258" s="61" t="n"/>
-      <c r="Q258" s="22" t="n">
-        <v>17</v>
-      </c>
+      <c r="Q258" s="22" t="n"/>
       <c r="R258" s="61" t="n"/>
       <c r="S258" s="22" t="n"/>
       <c r="T258" s="61" t="n"/>
@@ -62139,9 +61949,7 @@
       </c>
       <c r="S261" s="22" t="n"/>
       <c r="T261" s="61" t="n"/>
-      <c r="U261" s="22" t="n">
-        <v>380</v>
-      </c>
+      <c r="U261" s="22" t="n"/>
       <c r="V261" s="61" t="n"/>
       <c r="W261" s="22" t="n"/>
       <c r="X261" s="61" t="n"/>
@@ -62541,9 +62349,7 @@
       <c r="X268" s="61" t="n">
         <v>224</v>
       </c>
-      <c r="Y268" s="22" t="n">
-        <v>609</v>
-      </c>
+      <c r="Y268" s="22" t="n"/>
       <c r="Z268" s="61" t="n"/>
       <c r="AA268" s="22" t="n"/>
       <c r="AB268" s="61" t="n"/>
@@ -63941,9 +63747,7 @@
       <c r="P293" s="61" t="n"/>
       <c r="Q293" s="22" t="n"/>
       <c r="R293" s="61" t="n"/>
-      <c r="S293" s="22" t="n">
-        <v>34</v>
-      </c>
+      <c r="S293" s="22" t="n"/>
       <c r="T293" s="61" t="n"/>
       <c r="U293" s="22" t="n"/>
       <c r="V293" s="61" t="n"/>
@@ -63995,9 +63799,7 @@
       <c r="N294" s="61" t="n"/>
       <c r="O294" s="22" t="n"/>
       <c r="P294" s="61" t="n"/>
-      <c r="Q294" s="22" t="n">
-        <v>27</v>
-      </c>
+      <c r="Q294" s="22" t="n"/>
       <c r="R294" s="61" t="n"/>
       <c r="S294" s="22" t="n"/>
       <c r="T294" s="61" t="n"/>
@@ -64279,9 +64081,7 @@
       <c r="R299" s="61" t="n"/>
       <c r="S299" s="22" t="n"/>
       <c r="T299" s="61" t="n"/>
-      <c r="U299" s="22" t="n">
-        <v>1</v>
-      </c>
+      <c r="U299" s="22" t="n"/>
       <c r="V299" s="61" t="n"/>
       <c r="W299" s="22" t="n"/>
       <c r="X299" s="61" t="n"/>
@@ -64393,9 +64193,7 @@
       <c r="R301" s="61" t="n"/>
       <c r="S301" s="22" t="n"/>
       <c r="T301" s="61" t="n"/>
-      <c r="U301" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="U301" s="22" t="n"/>
       <c r="V301" s="61" t="n"/>
       <c r="W301" s="22" t="n"/>
       <c r="X301" s="61" t="n"/>
@@ -64563,9 +64361,7 @@
       </c>
       <c r="S304" s="22" t="n"/>
       <c r="T304" s="61" t="n"/>
-      <c r="U304" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="U304" s="22" t="n"/>
       <c r="V304" s="61" t="n"/>
       <c r="W304" s="22" t="n"/>
       <c r="X304" s="61" t="n"/>
@@ -65117,9 +64913,7 @@
       </c>
       <c r="S314" s="22" t="n"/>
       <c r="T314" s="61" t="n"/>
-      <c r="U314" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="U314" s="22" t="n"/>
       <c r="V314" s="61" t="n"/>
       <c r="W314" s="22" t="n"/>
       <c r="X314" s="61" t="n"/>
@@ -65341,9 +65135,7 @@
       </c>
       <c r="S318" s="22" t="n"/>
       <c r="T318" s="61" t="n"/>
-      <c r="U318" s="22" t="n">
-        <v>4</v>
-      </c>
+      <c r="U318" s="22" t="n"/>
       <c r="V318" s="61" t="n"/>
       <c r="W318" s="22" t="n"/>
       <c r="X318" s="61" t="n"/>
@@ -65735,9 +65527,7 @@
       <c r="T325" s="61" t="n"/>
       <c r="U325" s="22" t="n"/>
       <c r="V325" s="61" t="n"/>
-      <c r="W325" s="22" t="n">
-        <v>15</v>
-      </c>
+      <c r="W325" s="22" t="n"/>
       <c r="X325" s="61" t="n"/>
       <c r="Y325" s="22" t="n"/>
       <c r="Z325" s="61" t="n"/>
@@ -65945,9 +65735,7 @@
       <c r="H329" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="I329" s="22" t="n">
-        <v>176</v>
-      </c>
+      <c r="I329" s="22" t="n"/>
       <c r="J329" s="61" t="n"/>
       <c r="K329" s="22" t="n"/>
       <c r="L329" s="61" t="n"/>
@@ -65957,9 +65745,7 @@
       <c r="P329" s="61" t="n"/>
       <c r="Q329" s="22" t="n"/>
       <c r="R329" s="61" t="n"/>
-      <c r="S329" s="22" t="n">
-        <v>168</v>
-      </c>
+      <c r="S329" s="22" t="n"/>
       <c r="T329" s="61" t="n"/>
       <c r="U329" s="22" t="n"/>
       <c r="V329" s="61" t="n"/>
@@ -66007,9 +65793,7 @@
       <c r="J330" s="61" t="n"/>
       <c r="K330" s="22" t="n"/>
       <c r="L330" s="61" t="n"/>
-      <c r="M330" s="22" t="n">
-        <v>100</v>
-      </c>
+      <c r="M330" s="22" t="n"/>
       <c r="N330" s="61" t="n"/>
       <c r="O330" s="22" t="n"/>
       <c r="P330" s="61" t="n"/>
@@ -66183,9 +65967,7 @@
       <c r="P333" s="61" t="n"/>
       <c r="Q333" s="22" t="n"/>
       <c r="R333" s="61" t="n"/>
-      <c r="S333" s="22" t="n">
-        <v>40</v>
-      </c>
+      <c r="S333" s="22" t="n"/>
       <c r="T333" s="61" t="n"/>
       <c r="U333" s="22" t="n"/>
       <c r="V333" s="61" t="n"/>
@@ -66239,17 +66021,13 @@
       </c>
       <c r="O334" s="22" t="n"/>
       <c r="P334" s="61" t="n"/>
-      <c r="Q334" s="22" t="n">
-        <v>88</v>
-      </c>
+      <c r="Q334" s="22" t="n"/>
       <c r="R334" s="61" t="n"/>
       <c r="S334" s="22" t="n"/>
       <c r="T334" s="61" t="n"/>
       <c r="U334" s="22" t="n"/>
       <c r="V334" s="61" t="n"/>
-      <c r="W334" s="22" t="n">
-        <v>32</v>
-      </c>
+      <c r="W334" s="22" t="n"/>
       <c r="X334" s="61" t="n"/>
       <c r="Y334" s="22" t="n"/>
       <c r="Z334" s="61" t="n"/>
@@ -66301,15 +66079,11 @@
       <c r="P335" s="61" t="n">
         <v>110</v>
       </c>
-      <c r="Q335" s="22" t="n">
-        <v>6</v>
-      </c>
+      <c r="Q335" s="22" t="n"/>
       <c r="R335" s="61" t="n"/>
       <c r="S335" s="22" t="n"/>
       <c r="T335" s="61" t="n"/>
-      <c r="U335" s="22" t="n">
-        <v>110</v>
-      </c>
+      <c r="U335" s="22" t="n"/>
       <c r="V335" s="61" t="n"/>
       <c r="W335" s="22" t="n"/>
       <c r="X335" s="61" t="n"/>
@@ -66365,9 +66139,7 @@
       <c r="R336" s="61" t="n"/>
       <c r="S336" s="22" t="n"/>
       <c r="T336" s="61" t="n"/>
-      <c r="U336" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="U336" s="22" t="n"/>
       <c r="V336" s="61" t="n"/>
       <c r="W336" s="22" t="n"/>
       <c r="X336" s="61" t="n"/>
@@ -66423,9 +66195,7 @@
       <c r="R337" s="61" t="n"/>
       <c r="S337" s="22" t="n"/>
       <c r="T337" s="61" t="n"/>
-      <c r="U337" s="22" t="n">
-        <v>22</v>
-      </c>
+      <c r="U337" s="22" t="n"/>
       <c r="V337" s="61" t="n"/>
       <c r="W337" s="22" t="n"/>
       <c r="X337" s="61" t="n"/>
@@ -66541,9 +66311,7 @@
       <c r="T339" s="61" t="n"/>
       <c r="U339" s="22" t="n"/>
       <c r="V339" s="61" t="n"/>
-      <c r="W339" s="22" t="n">
-        <v>192</v>
-      </c>
+      <c r="W339" s="22" t="n"/>
       <c r="X339" s="61" t="n"/>
       <c r="Y339" s="22" t="n"/>
       <c r="Z339" s="61" t="n"/>
@@ -66597,9 +66365,7 @@
       </c>
       <c r="S340" s="22" t="n"/>
       <c r="T340" s="61" t="n"/>
-      <c r="U340" s="22" t="n">
-        <v>138</v>
-      </c>
+      <c r="U340" s="22" t="n"/>
       <c r="V340" s="61" t="n"/>
       <c r="W340" s="22" t="n"/>
       <c r="X340" s="61" t="n"/>
@@ -66715,9 +66481,7 @@
       <c r="V342" s="61" t="n"/>
       <c r="W342" s="22" t="n"/>
       <c r="X342" s="61" t="n"/>
-      <c r="Y342" s="22" t="n">
-        <v>20</v>
-      </c>
+      <c r="Y342" s="22" t="n"/>
       <c r="Z342" s="61" t="n"/>
       <c r="AA342" s="22" t="n"/>
       <c r="AB342" s="61" t="n"/>
@@ -66995,9 +66759,7 @@
       </c>
       <c r="U347" s="22" t="n"/>
       <c r="V347" s="61" t="n"/>
-      <c r="W347" s="22" t="n">
-        <v>68</v>
-      </c>
+      <c r="W347" s="22" t="n"/>
       <c r="X347" s="61" t="n"/>
       <c r="Y347" s="22" t="n"/>
       <c r="Z347" s="61" t="n"/>
@@ -67667,13 +67429,9 @@
       <c r="R359" s="61" t="n"/>
       <c r="S359" s="22" t="n"/>
       <c r="T359" s="61" t="n"/>
-      <c r="U359" s="22" t="n">
-        <v>9</v>
-      </c>
+      <c r="U359" s="22" t="n"/>
       <c r="V359" s="61" t="n"/>
-      <c r="W359" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="W359" s="22" t="n"/>
       <c r="X359" s="61" t="n"/>
       <c r="Y359" s="22" t="n"/>
       <c r="Z359" s="61" t="n">

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -38088,7 +38088,9 @@
       <c r="O4" s="100" t="n"/>
       <c r="P4" s="22" t="n"/>
       <c r="Q4" s="100" t="n"/>
-      <c r="R4" s="22" t="n"/>
+      <c r="R4" s="22" t="n">
+        <v>95</v>
+      </c>
       <c r="S4" s="100" t="n"/>
       <c r="T4" s="22" t="n"/>
       <c r="U4" s="100" t="n"/>
@@ -38138,7 +38140,9 @@
       <c r="M5" s="100" t="n"/>
       <c r="N5" s="22" t="n"/>
       <c r="O5" s="100" t="n"/>
-      <c r="P5" s="22" t="n"/>
+      <c r="P5" s="22" t="n">
+        <v>2166</v>
+      </c>
       <c r="Q5" s="100" t="n"/>
       <c r="R5" s="22" t="n"/>
       <c r="S5" s="100" t="n"/>
@@ -38180,7 +38184,9 @@
       <c r="G6" s="100" t="n">
         <v>554</v>
       </c>
-      <c r="H6" s="22" t="n"/>
+      <c r="H6" s="22" t="n">
+        <v>554</v>
+      </c>
       <c r="I6" s="100" t="n">
         <v>2600</v>
       </c>
@@ -38238,7 +38244,9 @@
       <c r="K7" s="100" t="n">
         <v>1744</v>
       </c>
-      <c r="L7" s="22" t="n"/>
+      <c r="L7" s="22" t="n">
+        <v>48</v>
+      </c>
       <c r="M7" s="100" t="n">
         <v>422</v>
       </c>
@@ -38346,11 +38354,15 @@
       <c r="O9" s="100" t="n">
         <v>636</v>
       </c>
-      <c r="P9" s="22" t="n"/>
+      <c r="P9" s="22" t="n">
+        <v>740</v>
+      </c>
       <c r="Q9" s="100" t="n"/>
       <c r="R9" s="22" t="n"/>
       <c r="S9" s="100" t="n"/>
-      <c r="T9" s="22" t="n"/>
+      <c r="T9" s="22" t="n">
+        <v>416</v>
+      </c>
       <c r="U9" s="100" t="n"/>
       <c r="V9" s="22" t="n"/>
       <c r="W9" s="100" t="n"/>
@@ -38496,7 +38508,9 @@
       <c r="O12" s="100" t="n">
         <v>1724</v>
       </c>
-      <c r="P12" s="22" t="n"/>
+      <c r="P12" s="22" t="n">
+        <v>36</v>
+      </c>
       <c r="Q12" s="100" t="n"/>
       <c r="R12" s="22" t="n"/>
       <c r="S12" s="100" t="n"/>
@@ -38548,9 +38562,13 @@
       </c>
       <c r="P13" s="22" t="n"/>
       <c r="Q13" s="100" t="n"/>
-      <c r="R13" s="22" t="n"/>
+      <c r="R13" s="22" t="n">
+        <v>152</v>
+      </c>
       <c r="S13" s="100" t="n"/>
-      <c r="T13" s="22" t="n"/>
+      <c r="T13" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="U13" s="100" t="n"/>
       <c r="V13" s="22" t="n"/>
       <c r="W13" s="100" t="n"/>
@@ -38806,7 +38824,9 @@
       <c r="U18" s="100" t="n"/>
       <c r="V18" s="22" t="n"/>
       <c r="W18" s="100" t="n"/>
-      <c r="X18" s="22" t="n"/>
+      <c r="X18" s="22" t="n">
+        <v>2178</v>
+      </c>
       <c r="Y18" s="100" t="n"/>
       <c r="Z18" s="22" t="n"/>
       <c r="AA18" s="100" t="n"/>
@@ -39961,7 +39981,9 @@
       <c r="O41" s="100" t="n"/>
       <c r="P41" s="22" t="n"/>
       <c r="Q41" s="100" t="n"/>
-      <c r="R41" s="22" t="n"/>
+      <c r="R41" s="22" t="n">
+        <v>28</v>
+      </c>
       <c r="S41" s="100" t="n"/>
       <c r="T41" s="22" t="n"/>
       <c r="U41" s="100" t="n"/>
@@ -40007,7 +40029,9 @@
       <c r="M42" s="100" t="n"/>
       <c r="N42" s="22" t="n"/>
       <c r="O42" s="100" t="n"/>
-      <c r="P42" s="22" t="n"/>
+      <c r="P42" s="22" t="n">
+        <v>540</v>
+      </c>
       <c r="Q42" s="100" t="n"/>
       <c r="R42" s="22" t="n"/>
       <c r="S42" s="100" t="n"/>
@@ -40049,7 +40073,9 @@
       <c r="G43" s="100" t="n">
         <v>20</v>
       </c>
-      <c r="H43" s="22" t="n"/>
+      <c r="H43" s="22" t="n">
+        <v>64</v>
+      </c>
       <c r="I43" s="100" t="n">
         <v>560</v>
       </c>
@@ -40209,7 +40235,9 @@
       </c>
       <c r="N46" s="22" t="n"/>
       <c r="O46" s="100" t="n"/>
-      <c r="P46" s="22" t="n"/>
+      <c r="P46" s="22" t="n">
+        <v>72</v>
+      </c>
       <c r="Q46" s="100" t="n"/>
       <c r="R46" s="22" t="n"/>
       <c r="S46" s="100" t="n"/>
@@ -40261,7 +40289,9 @@
       <c r="O47" s="100" t="n"/>
       <c r="P47" s="22" t="n"/>
       <c r="Q47" s="100" t="n"/>
-      <c r="R47" s="22" t="n"/>
+      <c r="R47" s="22" t="n">
+        <v>4</v>
+      </c>
       <c r="S47" s="100" t="n"/>
       <c r="T47" s="22" t="n"/>
       <c r="U47" s="100" t="n"/>
@@ -40313,7 +40343,9 @@
       <c r="S48" s="100" t="n"/>
       <c r="T48" s="22" t="n"/>
       <c r="U48" s="100" t="n"/>
-      <c r="V48" s="22" t="n"/>
+      <c r="V48" s="22" t="n">
+        <v>38</v>
+      </c>
       <c r="W48" s="100" t="n"/>
       <c r="X48" s="22" t="n"/>
       <c r="Y48" s="100" t="n"/>
@@ -40669,7 +40701,9 @@
       <c r="U55" s="100" t="n"/>
       <c r="V55" s="22" t="n"/>
       <c r="W55" s="100" t="n"/>
-      <c r="X55" s="22" t="n"/>
+      <c r="X55" s="22" t="n">
+        <v>1180</v>
+      </c>
       <c r="Y55" s="100" t="n"/>
       <c r="Z55" s="22" t="n"/>
       <c r="AA55" s="100" t="n"/>
@@ -40922,7 +40956,9 @@
       <c r="U60" s="100" t="n">
         <v>1296</v>
       </c>
-      <c r="V60" s="22" t="n"/>
+      <c r="V60" s="22" t="n">
+        <v>1500</v>
+      </c>
       <c r="W60" s="100" t="n"/>
       <c r="X60" s="22" t="n"/>
       <c r="Y60" s="100" t="n"/>
@@ -47679,7 +47715,9 @@
       <c r="H6" s="61" t="n"/>
       <c r="I6" s="22" t="n"/>
       <c r="J6" s="61" t="n"/>
-      <c r="K6" s="22" t="n"/>
+      <c r="K6" s="22" t="n">
+        <v>67</v>
+      </c>
       <c r="L6" s="61" t="n"/>
       <c r="M6" s="22" t="n"/>
       <c r="N6" s="61" t="n"/>
@@ -47963,9 +48001,13 @@
       <c r="L11" s="61" t="n">
         <v>22</v>
       </c>
-      <c r="M11" s="22" t="n"/>
+      <c r="M11" s="22" t="n">
+        <v>15</v>
+      </c>
       <c r="N11" s="61" t="n"/>
-      <c r="O11" s="22" t="n"/>
+      <c r="O11" s="22" t="n">
+        <v>22</v>
+      </c>
       <c r="P11" s="61" t="n"/>
       <c r="Q11" s="22" t="n"/>
       <c r="R11" s="61" t="n"/>
@@ -48245,7 +48287,9 @@
       </c>
       <c r="M16" s="22" t="n"/>
       <c r="N16" s="61" t="n"/>
-      <c r="O16" s="22" t="n"/>
+      <c r="O16" s="22" t="n">
+        <v>74</v>
+      </c>
       <c r="P16" s="61" t="n"/>
       <c r="Q16" s="22" t="n"/>
       <c r="R16" s="61" t="n"/>
@@ -48303,7 +48347,9 @@
       <c r="N17" s="61" t="n">
         <v>45</v>
       </c>
-      <c r="O17" s="22" t="n"/>
+      <c r="O17" s="22" t="n">
+        <v>9</v>
+      </c>
       <c r="P17" s="61" t="n"/>
       <c r="Q17" s="22" t="n"/>
       <c r="R17" s="61" t="n"/>
@@ -48365,7 +48411,9 @@
       <c r="R18" s="61" t="n"/>
       <c r="S18" s="22" t="n"/>
       <c r="T18" s="61" t="n"/>
-      <c r="U18" s="22" t="n"/>
+      <c r="U18" s="22" t="n">
+        <v>46</v>
+      </c>
       <c r="V18" s="61" t="n"/>
       <c r="W18" s="22" t="n"/>
       <c r="X18" s="61" t="n"/>
@@ -48529,7 +48577,9 @@
       </c>
       <c r="O21" s="22" t="n"/>
       <c r="P21" s="61" t="n"/>
-      <c r="Q21" s="22" t="n"/>
+      <c r="Q21" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="R21" s="61" t="n"/>
       <c r="S21" s="22" t="n"/>
       <c r="T21" s="61" t="n"/>
@@ -48645,7 +48695,9 @@
       <c r="R23" s="61" t="n"/>
       <c r="S23" s="22" t="n"/>
       <c r="T23" s="61" t="n"/>
-      <c r="U23" s="22" t="n"/>
+      <c r="U23" s="22" t="n">
+        <v>93</v>
+      </c>
       <c r="V23" s="61" t="n"/>
       <c r="W23" s="22" t="n"/>
       <c r="X23" s="61" t="n"/>
@@ -48817,7 +48869,9 @@
       <c r="T26" s="61" t="n"/>
       <c r="U26" s="22" t="n"/>
       <c r="V26" s="61" t="n"/>
-      <c r="W26" s="22" t="n"/>
+      <c r="W26" s="22" t="n">
+        <v>85</v>
+      </c>
       <c r="X26" s="61" t="n"/>
       <c r="Y26" s="22" t="n"/>
       <c r="Z26" s="61" t="n"/>
@@ -48871,7 +48925,9 @@
       <c r="R27" s="61" t="n"/>
       <c r="S27" s="22" t="n"/>
       <c r="T27" s="61" t="n"/>
-      <c r="U27" s="22" t="n"/>
+      <c r="U27" s="22" t="n">
+        <v>55</v>
+      </c>
       <c r="V27" s="61" t="n"/>
       <c r="W27" s="22" t="n"/>
       <c r="X27" s="61" t="n"/>
@@ -48927,7 +48983,9 @@
       <c r="R28" s="61" t="n"/>
       <c r="S28" s="22" t="n"/>
       <c r="T28" s="61" t="n"/>
-      <c r="U28" s="22" t="n"/>
+      <c r="U28" s="22" t="n">
+        <v>52</v>
+      </c>
       <c r="V28" s="61" t="n"/>
       <c r="W28" s="22" t="n"/>
       <c r="X28" s="61" t="n"/>
@@ -49037,7 +49095,9 @@
       </c>
       <c r="Q30" s="22" t="n"/>
       <c r="R30" s="61" t="n"/>
-      <c r="S30" s="22" t="n"/>
+      <c r="S30" s="22" t="n">
+        <v>45</v>
+      </c>
       <c r="T30" s="61" t="n"/>
       <c r="U30" s="22" t="n"/>
       <c r="V30" s="61" t="n"/>
@@ -49097,7 +49157,9 @@
       </c>
       <c r="S31" s="22" t="n"/>
       <c r="T31" s="61" t="n"/>
-      <c r="U31" s="22" t="n"/>
+      <c r="U31" s="22" t="n">
+        <v>26</v>
+      </c>
       <c r="V31" s="61" t="n"/>
       <c r="W31" s="22" t="n"/>
       <c r="X31" s="61" t="n"/>
@@ -49701,7 +49763,9 @@
       <c r="H42" s="61" t="n"/>
       <c r="I42" s="22" t="n"/>
       <c r="J42" s="61" t="n"/>
-      <c r="K42" s="22" t="n"/>
+      <c r="K42" s="22" t="n">
+        <v>38</v>
+      </c>
       <c r="L42" s="61" t="n"/>
       <c r="M42" s="22" t="n"/>
       <c r="N42" s="61" t="n"/>
@@ -49873,9 +49937,13 @@
       <c r="L45" s="61" t="n">
         <v>63</v>
       </c>
-      <c r="M45" s="22" t="n"/>
+      <c r="M45" s="22" t="n">
+        <v>93</v>
+      </c>
       <c r="N45" s="61" t="n"/>
-      <c r="O45" s="22" t="n"/>
+      <c r="O45" s="22" t="n">
+        <v>63</v>
+      </c>
       <c r="P45" s="61" t="n"/>
       <c r="Q45" s="22" t="n"/>
       <c r="R45" s="61" t="n"/>
@@ -49933,7 +50001,9 @@
       <c r="N46" s="61" t="n"/>
       <c r="O46" s="22" t="n"/>
       <c r="P46" s="61" t="n"/>
-      <c r="Q46" s="22" t="n"/>
+      <c r="Q46" s="22" t="n">
+        <v>12</v>
+      </c>
       <c r="R46" s="61" t="n"/>
       <c r="S46" s="22" t="n"/>
       <c r="T46" s="61" t="n"/>
@@ -49989,11 +50059,15 @@
       <c r="N47" s="61" t="n">
         <v>80</v>
       </c>
-      <c r="O47" s="22" t="n"/>
+      <c r="O47" s="22" t="n">
+        <v>160</v>
+      </c>
       <c r="P47" s="61" t="n"/>
       <c r="Q47" s="22" t="n"/>
       <c r="R47" s="61" t="n"/>
-      <c r="S47" s="22" t="n"/>
+      <c r="S47" s="22" t="n">
+        <v>80</v>
+      </c>
       <c r="T47" s="61" t="n"/>
       <c r="U47" s="22" t="n"/>
       <c r="V47" s="61" t="n"/>
@@ -50223,7 +50297,9 @@
       <c r="T51" s="61" t="n"/>
       <c r="U51" s="22" t="n"/>
       <c r="V51" s="61" t="n"/>
-      <c r="W51" s="22" t="n"/>
+      <c r="W51" s="22" t="n">
+        <v>311</v>
+      </c>
       <c r="X51" s="61" t="n"/>
       <c r="Y51" s="22" t="n"/>
       <c r="Z51" s="61" t="n"/>
@@ -50277,9 +50353,13 @@
       <c r="R52" s="61" t="n">
         <v>88</v>
       </c>
-      <c r="S52" s="22" t="n"/>
+      <c r="S52" s="22" t="n">
+        <v>289</v>
+      </c>
       <c r="T52" s="61" t="n"/>
-      <c r="U52" s="22" t="n"/>
+      <c r="U52" s="22" t="n">
+        <v>132</v>
+      </c>
       <c r="V52" s="61" t="n"/>
       <c r="W52" s="22" t="n"/>
       <c r="X52" s="61" t="n"/>
@@ -50395,7 +50475,9 @@
       <c r="V54" s="61" t="n"/>
       <c r="W54" s="22" t="n"/>
       <c r="X54" s="61" t="n"/>
-      <c r="Y54" s="22" t="n"/>
+      <c r="Y54" s="22" t="n">
+        <v>141</v>
+      </c>
       <c r="Z54" s="61" t="n"/>
       <c r="AA54" s="22" t="n"/>
       <c r="AB54" s="61" t="n"/>
@@ -50671,7 +50753,9 @@
       <c r="T59" s="61" t="n">
         <v>93</v>
       </c>
-      <c r="U59" s="22" t="n"/>
+      <c r="U59" s="22" t="n">
+        <v>5</v>
+      </c>
       <c r="V59" s="61" t="n"/>
       <c r="W59" s="22" t="n"/>
       <c r="X59" s="61" t="n"/>
@@ -50841,7 +50925,9 @@
       </c>
       <c r="U62" s="22" t="n"/>
       <c r="V62" s="61" t="n"/>
-      <c r="W62" s="22" t="n"/>
+      <c r="W62" s="22" t="n">
+        <v>117</v>
+      </c>
       <c r="X62" s="61" t="n"/>
       <c r="Y62" s="22" t="n"/>
       <c r="Z62" s="61" t="n"/>
@@ -51947,9 +52033,13 @@
       <c r="J82" s="61" t="n"/>
       <c r="K82" s="22" t="n"/>
       <c r="L82" s="61" t="n"/>
-      <c r="M82" s="22" t="n"/>
+      <c r="M82" s="22" t="n">
+        <v>76</v>
+      </c>
       <c r="N82" s="61" t="n"/>
-      <c r="O82" s="22" t="n"/>
+      <c r="O82" s="22" t="n">
+        <v>62</v>
+      </c>
       <c r="P82" s="61" t="n"/>
       <c r="Q82" s="22" t="n"/>
       <c r="R82" s="61" t="n"/>
@@ -52061,7 +52151,9 @@
       <c r="L84" s="61" t="n"/>
       <c r="M84" s="22" t="n"/>
       <c r="N84" s="61" t="n"/>
-      <c r="O84" s="22" t="n"/>
+      <c r="O84" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="P84" s="61" t="n"/>
       <c r="Q84" s="22" t="n"/>
       <c r="R84" s="61" t="n"/>
@@ -52119,7 +52211,9 @@
       <c r="L85" s="61" t="n"/>
       <c r="M85" s="22" t="n"/>
       <c r="N85" s="61" t="n"/>
-      <c r="O85" s="22" t="n"/>
+      <c r="O85" s="22" t="n">
+        <v>6</v>
+      </c>
       <c r="P85" s="61" t="n"/>
       <c r="Q85" s="22" t="n"/>
       <c r="R85" s="61" t="n"/>
@@ -52231,7 +52325,9 @@
       <c r="N87" s="61" t="n"/>
       <c r="O87" s="22" t="n"/>
       <c r="P87" s="61" t="n"/>
-      <c r="Q87" s="22" t="n"/>
+      <c r="Q87" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="R87" s="61" t="n"/>
       <c r="S87" s="22" t="n"/>
       <c r="T87" s="61" t="n"/>
@@ -52285,7 +52381,9 @@
       <c r="L88" s="61" t="n"/>
       <c r="M88" s="22" t="n"/>
       <c r="N88" s="61" t="n"/>
-      <c r="O88" s="22" t="n"/>
+      <c r="O88" s="22" t="n">
+        <v>14</v>
+      </c>
       <c r="P88" s="61" t="n"/>
       <c r="Q88" s="22" t="n"/>
       <c r="R88" s="61" t="n"/>
@@ -52341,7 +52439,9 @@
       <c r="L89" s="61" t="n"/>
       <c r="M89" s="22" t="n"/>
       <c r="N89" s="61" t="n"/>
-      <c r="O89" s="22" t="n"/>
+      <c r="O89" s="22" t="n">
+        <v>11</v>
+      </c>
       <c r="P89" s="61" t="n"/>
       <c r="Q89" s="22" t="n"/>
       <c r="R89" s="61" t="n"/>
@@ -52397,7 +52497,9 @@
       <c r="L90" s="61" t="n"/>
       <c r="M90" s="22" t="n"/>
       <c r="N90" s="61" t="n"/>
-      <c r="O90" s="22" t="n"/>
+      <c r="O90" s="22" t="n">
+        <v>14</v>
+      </c>
       <c r="P90" s="61" t="n"/>
       <c r="Q90" s="22" t="n"/>
       <c r="R90" s="61" t="n"/>
@@ -52835,7 +52937,9 @@
       </c>
       <c r="K98" s="22" t="n"/>
       <c r="L98" s="61" t="n"/>
-      <c r="M98" s="22" t="n"/>
+      <c r="M98" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="N98" s="61" t="n"/>
       <c r="O98" s="22" t="n"/>
       <c r="P98" s="61" t="n"/>
@@ -52949,7 +53053,9 @@
       <c r="N100" s="61" t="n"/>
       <c r="O100" s="22" t="n"/>
       <c r="P100" s="61" t="n"/>
-      <c r="Q100" s="22" t="n"/>
+      <c r="Q100" s="22" t="n">
+        <v>3</v>
+      </c>
       <c r="R100" s="61" t="n"/>
       <c r="S100" s="22" t="n"/>
       <c r="T100" s="61" t="n"/>
@@ -53059,7 +53165,9 @@
       </c>
       <c r="M102" s="22" t="n"/>
       <c r="N102" s="61" t="n"/>
-      <c r="O102" s="22" t="n"/>
+      <c r="O102" s="22" t="n">
+        <v>10</v>
+      </c>
       <c r="P102" s="61" t="n"/>
       <c r="Q102" s="22" t="n"/>
       <c r="R102" s="61" t="n"/>
@@ -53171,7 +53279,9 @@
       <c r="N104" s="61" t="n"/>
       <c r="O104" s="22" t="n"/>
       <c r="P104" s="61" t="n"/>
-      <c r="Q104" s="22" t="n"/>
+      <c r="Q104" s="22" t="n">
+        <v>31</v>
+      </c>
       <c r="R104" s="61" t="n"/>
       <c r="S104" s="22" t="n"/>
       <c r="T104" s="61" t="n"/>
@@ -53281,7 +53391,9 @@
       </c>
       <c r="M106" s="22" t="n"/>
       <c r="N106" s="61" t="n"/>
-      <c r="O106" s="22" t="n"/>
+      <c r="O106" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="P106" s="61" t="n"/>
       <c r="Q106" s="22" t="n"/>
       <c r="R106" s="61" t="n"/>
@@ -53713,7 +53825,9 @@
       <c r="H114" s="61" t="n"/>
       <c r="I114" s="22" t="n"/>
       <c r="J114" s="61" t="n"/>
-      <c r="K114" s="22" t="n"/>
+      <c r="K114" s="22" t="n">
+        <v>5</v>
+      </c>
       <c r="L114" s="61" t="n"/>
       <c r="M114" s="22" t="n"/>
       <c r="N114" s="61" t="n"/>
@@ -53883,7 +53997,9 @@
       </c>
       <c r="K117" s="22" t="n"/>
       <c r="L117" s="61" t="n"/>
-      <c r="M117" s="22" t="n"/>
+      <c r="M117" s="22" t="n">
+        <v>28</v>
+      </c>
       <c r="N117" s="61" t="n"/>
       <c r="O117" s="22" t="n"/>
       <c r="P117" s="61" t="n"/>
@@ -53939,9 +54055,13 @@
       </c>
       <c r="K118" s="22" t="n"/>
       <c r="L118" s="61" t="n"/>
-      <c r="M118" s="22" t="n"/>
+      <c r="M118" s="22" t="n">
+        <v>12</v>
+      </c>
       <c r="N118" s="61" t="n"/>
-      <c r="O118" s="22" t="n"/>
+      <c r="O118" s="22" t="n">
+        <v>12</v>
+      </c>
       <c r="P118" s="61" t="n"/>
       <c r="Q118" s="22" t="n"/>
       <c r="R118" s="61" t="n"/>
@@ -53997,9 +54117,13 @@
       <c r="L119" s="61" t="n">
         <v>58</v>
       </c>
-      <c r="M119" s="22" t="n"/>
+      <c r="M119" s="22" t="n">
+        <v>34</v>
+      </c>
       <c r="N119" s="61" t="n"/>
-      <c r="O119" s="22" t="n"/>
+      <c r="O119" s="22" t="n">
+        <v>58</v>
+      </c>
       <c r="P119" s="61" t="n"/>
       <c r="Q119" s="22" t="n"/>
       <c r="R119" s="61" t="n"/>
@@ -54223,7 +54347,9 @@
       <c r="N123" s="61" t="n"/>
       <c r="O123" s="22" t="n"/>
       <c r="P123" s="61" t="n"/>
-      <c r="Q123" s="22" t="n"/>
+      <c r="Q123" s="22" t="n">
+        <v>38</v>
+      </c>
       <c r="R123" s="61" t="n"/>
       <c r="S123" s="22" t="n"/>
       <c r="T123" s="61" t="n"/>
@@ -54279,9 +54405,13 @@
       <c r="N124" s="61" t="n">
         <v>39</v>
       </c>
-      <c r="O124" s="22" t="n"/>
+      <c r="O124" s="22" t="n">
+        <v>36</v>
+      </c>
       <c r="P124" s="61" t="n"/>
-      <c r="Q124" s="22" t="n"/>
+      <c r="Q124" s="22" t="n">
+        <v>42</v>
+      </c>
       <c r="R124" s="61" t="n"/>
       <c r="S124" s="22" t="n"/>
       <c r="T124" s="61" t="n"/>
@@ -54395,7 +54525,9 @@
       <c r="P126" s="61" t="n"/>
       <c r="Q126" s="22" t="n"/>
       <c r="R126" s="61" t="n"/>
-      <c r="S126" s="22" t="n"/>
+      <c r="S126" s="22" t="n">
+        <v>45</v>
+      </c>
       <c r="T126" s="61" t="n"/>
       <c r="U126" s="22" t="n"/>
       <c r="V126" s="61" t="n"/>
@@ -54561,7 +54693,9 @@
       </c>
       <c r="O129" s="22" t="n"/>
       <c r="P129" s="61" t="n"/>
-      <c r="Q129" s="22" t="n"/>
+      <c r="Q129" s="22" t="n">
+        <v>9</v>
+      </c>
       <c r="R129" s="61" t="n"/>
       <c r="S129" s="22" t="n"/>
       <c r="T129" s="61" t="n"/>
@@ -54897,7 +55031,9 @@
       <c r="R135" s="61" t="n"/>
       <c r="S135" s="22" t="n"/>
       <c r="T135" s="61" t="n"/>
-      <c r="U135" s="22" t="n"/>
+      <c r="U135" s="22" t="n">
+        <v>38</v>
+      </c>
       <c r="V135" s="61" t="n"/>
       <c r="W135" s="22" t="n"/>
       <c r="X135" s="61" t="n"/>
@@ -54949,7 +55085,9 @@
       </c>
       <c r="O136" s="22" t="n"/>
       <c r="P136" s="61" t="n"/>
-      <c r="Q136" s="22" t="n"/>
+      <c r="Q136" s="22" t="n">
+        <v>45</v>
+      </c>
       <c r="R136" s="61" t="n"/>
       <c r="S136" s="22" t="n"/>
       <c r="T136" s="61" t="n"/>
@@ -55287,7 +55425,9 @@
       </c>
       <c r="Q142" s="22" t="n"/>
       <c r="R142" s="61" t="n"/>
-      <c r="S142" s="22" t="n"/>
+      <c r="S142" s="22" t="n">
+        <v>30</v>
+      </c>
       <c r="T142" s="61" t="n"/>
       <c r="U142" s="22" t="n"/>
       <c r="V142" s="61" t="n"/>
@@ -55345,7 +55485,9 @@
       <c r="R143" s="61" t="n"/>
       <c r="S143" s="22" t="n"/>
       <c r="T143" s="61" t="n"/>
-      <c r="U143" s="22" t="n"/>
+      <c r="U143" s="22" t="n">
+        <v>3</v>
+      </c>
       <c r="V143" s="61" t="n"/>
       <c r="W143" s="22" t="n"/>
       <c r="X143" s="61" t="n"/>
@@ -55403,7 +55545,9 @@
       <c r="T144" s="61" t="n"/>
       <c r="U144" s="22" t="n"/>
       <c r="V144" s="61" t="n"/>
-      <c r="W144" s="22" t="n"/>
+      <c r="W144" s="22" t="n">
+        <v>12</v>
+      </c>
       <c r="X144" s="61" t="n"/>
       <c r="Y144" s="22" t="n"/>
       <c r="Z144" s="61" t="n"/>
@@ -55457,7 +55601,9 @@
       <c r="R145" s="61" t="n"/>
       <c r="S145" s="22" t="n"/>
       <c r="T145" s="61" t="n"/>
-      <c r="U145" s="22" t="n"/>
+      <c r="U145" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="V145" s="61" t="n"/>
       <c r="W145" s="22" t="n"/>
       <c r="X145" s="61" t="n"/>
@@ -56229,7 +56375,9 @@
       <c r="N159" s="61" t="n"/>
       <c r="O159" s="22" t="n"/>
       <c r="P159" s="61" t="n"/>
-      <c r="Q159" s="22" t="n"/>
+      <c r="Q159" s="22" t="n">
+        <v>33</v>
+      </c>
       <c r="R159" s="61" t="n"/>
       <c r="S159" s="22" t="n"/>
       <c r="T159" s="61" t="n"/>
@@ -56283,7 +56431,9 @@
       </c>
       <c r="M160" s="22" t="n"/>
       <c r="N160" s="61" t="n"/>
-      <c r="O160" s="22" t="n"/>
+      <c r="O160" s="22" t="n">
+        <v>59</v>
+      </c>
       <c r="P160" s="61" t="n"/>
       <c r="Q160" s="22" t="n"/>
       <c r="R160" s="61" t="n"/>
@@ -56397,7 +56547,9 @@
       <c r="P162" s="61" t="n"/>
       <c r="Q162" s="22" t="n"/>
       <c r="R162" s="61" t="n"/>
-      <c r="S162" s="22" t="n"/>
+      <c r="S162" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="T162" s="61" t="n"/>
       <c r="U162" s="22" t="n"/>
       <c r="V162" s="61" t="n"/>
@@ -56559,7 +56711,9 @@
       </c>
       <c r="M165" s="22" t="n"/>
       <c r="N165" s="61" t="n"/>
-      <c r="O165" s="22" t="n"/>
+      <c r="O165" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="P165" s="61" t="n"/>
       <c r="Q165" s="22" t="n"/>
       <c r="R165" s="61" t="n"/>
@@ -56779,7 +56933,9 @@
       <c r="N169" s="61" t="n"/>
       <c r="O169" s="22" t="n"/>
       <c r="P169" s="61" t="n"/>
-      <c r="Q169" s="22" t="n"/>
+      <c r="Q169" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="R169" s="61" t="n"/>
       <c r="S169" s="22" t="n"/>
       <c r="T169" s="61" t="n"/>
@@ -56833,7 +56989,9 @@
       </c>
       <c r="M170" s="22" t="n"/>
       <c r="N170" s="61" t="n"/>
-      <c r="O170" s="22" t="n"/>
+      <c r="O170" s="22" t="n">
+        <v>9</v>
+      </c>
       <c r="P170" s="61" t="n"/>
       <c r="Q170" s="22" t="n"/>
       <c r="R170" s="61" t="n"/>
@@ -56895,7 +57053,9 @@
       <c r="R171" s="61" t="n"/>
       <c r="S171" s="22" t="n"/>
       <c r="T171" s="61" t="n"/>
-      <c r="U171" s="22" t="n"/>
+      <c r="U171" s="22" t="n">
+        <v>9</v>
+      </c>
       <c r="V171" s="61" t="n"/>
       <c r="W171" s="22" t="n"/>
       <c r="X171" s="61" t="n"/>
@@ -57055,7 +57215,9 @@
       </c>
       <c r="M174" s="22" t="n"/>
       <c r="N174" s="61" t="n"/>
-      <c r="O174" s="22" t="n"/>
+      <c r="O174" s="22" t="n">
+        <v>6</v>
+      </c>
       <c r="P174" s="61" t="n"/>
       <c r="Q174" s="22" t="n"/>
       <c r="R174" s="61" t="n"/>
@@ -57167,7 +57329,9 @@
       <c r="N176" s="61" t="n"/>
       <c r="O176" s="22" t="n"/>
       <c r="P176" s="61" t="n"/>
-      <c r="Q176" s="22" t="n"/>
+      <c r="Q176" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="R176" s="61" t="n"/>
       <c r="S176" s="22" t="n"/>
       <c r="T176" s="61" t="n"/>
@@ -57391,7 +57555,9 @@
       <c r="N180" s="61" t="n"/>
       <c r="O180" s="22" t="n"/>
       <c r="P180" s="61" t="n"/>
-      <c r="Q180" s="22" t="n"/>
+      <c r="Q180" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="R180" s="61" t="n"/>
       <c r="S180" s="22" t="n"/>
       <c r="T180" s="61" t="n"/>
@@ -57673,7 +57839,9 @@
       <c r="P185" s="61" t="n"/>
       <c r="Q185" s="22" t="n"/>
       <c r="R185" s="61" t="n"/>
-      <c r="S185" s="22" t="n"/>
+      <c r="S185" s="22" t="n">
+        <v>198</v>
+      </c>
       <c r="T185" s="61" t="n"/>
       <c r="U185" s="22" t="n"/>
       <c r="V185" s="61" t="n"/>
@@ -57721,7 +57889,9 @@
       </c>
       <c r="I186" s="22" t="n"/>
       <c r="J186" s="61" t="n"/>
-      <c r="K186" s="22" t="n"/>
+      <c r="K186" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="L186" s="61" t="n"/>
       <c r="M186" s="22" t="n"/>
       <c r="N186" s="61" t="n"/>
@@ -57731,7 +57901,9 @@
       <c r="R186" s="61" t="n"/>
       <c r="S186" s="22" t="n"/>
       <c r="T186" s="61" t="n"/>
-      <c r="U186" s="22" t="n"/>
+      <c r="U186" s="22" t="n">
+        <v>634</v>
+      </c>
       <c r="V186" s="61" t="n"/>
       <c r="W186" s="22" t="n"/>
       <c r="X186" s="61" t="n"/>
@@ -57957,7 +58129,9 @@
       <c r="T190" s="61" t="n"/>
       <c r="U190" s="22" t="n"/>
       <c r="V190" s="61" t="n"/>
-      <c r="W190" s="22" t="n"/>
+      <c r="W190" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="X190" s="61" t="n"/>
       <c r="Y190" s="22" t="n"/>
       <c r="Z190" s="61" t="n">
@@ -59477,7 +59651,9 @@
       <c r="T217" s="61" t="n"/>
       <c r="U217" s="22" t="n"/>
       <c r="V217" s="61" t="n"/>
-      <c r="W217" s="22" t="n"/>
+      <c r="W217" s="22" t="n">
+        <v>44</v>
+      </c>
       <c r="X217" s="61" t="n"/>
       <c r="Y217" s="22" t="n"/>
       <c r="Z217" s="61" t="n"/>
@@ -59745,7 +59921,9 @@
       </c>
       <c r="I222" s="22" t="n"/>
       <c r="J222" s="61" t="n"/>
-      <c r="K222" s="22" t="n"/>
+      <c r="K222" s="22" t="n">
+        <v>16</v>
+      </c>
       <c r="L222" s="61" t="n"/>
       <c r="M222" s="22" t="n"/>
       <c r="N222" s="61" t="n"/>
@@ -59755,7 +59933,9 @@
       <c r="R222" s="61" t="n"/>
       <c r="S222" s="22" t="n"/>
       <c r="T222" s="61" t="n"/>
-      <c r="U222" s="22" t="n"/>
+      <c r="U222" s="22" t="n">
+        <v>1119</v>
+      </c>
       <c r="V222" s="61" t="n"/>
       <c r="W222" s="22" t="n"/>
       <c r="X222" s="61" t="n"/>
@@ -59985,7 +60165,9 @@
       </c>
       <c r="U226" s="22" t="n"/>
       <c r="V226" s="61" t="n"/>
-      <c r="W226" s="22" t="n"/>
+      <c r="W226" s="22" t="n">
+        <v>4200</v>
+      </c>
       <c r="X226" s="61" t="n"/>
       <c r="Y226" s="22" t="n"/>
       <c r="Z226" s="61" t="n"/>
@@ -60325,7 +60507,9 @@
       </c>
       <c r="W232" s="22" t="n"/>
       <c r="X232" s="61" t="n"/>
-      <c r="Y232" s="22" t="n"/>
+      <c r="Y232" s="22" t="n">
+        <v>564</v>
+      </c>
       <c r="Z232" s="61" t="n"/>
       <c r="AA232" s="22" t="n"/>
       <c r="AB232" s="61" t="n"/>
@@ -61659,7 +61843,9 @@
       <c r="J256" s="61" t="n"/>
       <c r="K256" s="22" t="n"/>
       <c r="L256" s="61" t="n"/>
-      <c r="M256" s="22" t="n"/>
+      <c r="M256" s="22" t="n">
+        <v>86</v>
+      </c>
       <c r="N256" s="61" t="n"/>
       <c r="O256" s="22" t="n"/>
       <c r="P256" s="61" t="n"/>
@@ -61723,7 +61909,9 @@
       <c r="P257" s="61" t="n"/>
       <c r="Q257" s="22" t="n"/>
       <c r="R257" s="61" t="n"/>
-      <c r="S257" s="22" t="n"/>
+      <c r="S257" s="22" t="n">
+        <v>210</v>
+      </c>
       <c r="T257" s="61" t="n"/>
       <c r="U257" s="22" t="n"/>
       <c r="V257" s="61" t="n"/>
@@ -61775,7 +61963,9 @@
       <c r="N258" s="61" t="n"/>
       <c r="O258" s="22" t="n"/>
       <c r="P258" s="61" t="n"/>
-      <c r="Q258" s="22" t="n"/>
+      <c r="Q258" s="22" t="n">
+        <v>17</v>
+      </c>
       <c r="R258" s="61" t="n"/>
       <c r="S258" s="22" t="n"/>
       <c r="T258" s="61" t="n"/>
@@ -61949,7 +62139,9 @@
       </c>
       <c r="S261" s="22" t="n"/>
       <c r="T261" s="61" t="n"/>
-      <c r="U261" s="22" t="n"/>
+      <c r="U261" s="22" t="n">
+        <v>380</v>
+      </c>
       <c r="V261" s="61" t="n"/>
       <c r="W261" s="22" t="n"/>
       <c r="X261" s="61" t="n"/>
@@ -62349,7 +62541,9 @@
       <c r="X268" s="61" t="n">
         <v>224</v>
       </c>
-      <c r="Y268" s="22" t="n"/>
+      <c r="Y268" s="22" t="n">
+        <v>609</v>
+      </c>
       <c r="Z268" s="61" t="n"/>
       <c r="AA268" s="22" t="n"/>
       <c r="AB268" s="61" t="n"/>
@@ -63747,7 +63941,9 @@
       <c r="P293" s="61" t="n"/>
       <c r="Q293" s="22" t="n"/>
       <c r="R293" s="61" t="n"/>
-      <c r="S293" s="22" t="n"/>
+      <c r="S293" s="22" t="n">
+        <v>34</v>
+      </c>
       <c r="T293" s="61" t="n"/>
       <c r="U293" s="22" t="n"/>
       <c r="V293" s="61" t="n"/>
@@ -63799,7 +63995,9 @@
       <c r="N294" s="61" t="n"/>
       <c r="O294" s="22" t="n"/>
       <c r="P294" s="61" t="n"/>
-      <c r="Q294" s="22" t="n"/>
+      <c r="Q294" s="22" t="n">
+        <v>27</v>
+      </c>
       <c r="R294" s="61" t="n"/>
       <c r="S294" s="22" t="n"/>
       <c r="T294" s="61" t="n"/>
@@ -64081,7 +64279,9 @@
       <c r="R299" s="61" t="n"/>
       <c r="S299" s="22" t="n"/>
       <c r="T299" s="61" t="n"/>
-      <c r="U299" s="22" t="n"/>
+      <c r="U299" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="V299" s="61" t="n"/>
       <c r="W299" s="22" t="n"/>
       <c r="X299" s="61" t="n"/>
@@ -64193,7 +64393,9 @@
       <c r="R301" s="61" t="n"/>
       <c r="S301" s="22" t="n"/>
       <c r="T301" s="61" t="n"/>
-      <c r="U301" s="22" t="n"/>
+      <c r="U301" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="V301" s="61" t="n"/>
       <c r="W301" s="22" t="n"/>
       <c r="X301" s="61" t="n"/>
@@ -64361,7 +64563,9 @@
       </c>
       <c r="S304" s="22" t="n"/>
       <c r="T304" s="61" t="n"/>
-      <c r="U304" s="22" t="n"/>
+      <c r="U304" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="V304" s="61" t="n"/>
       <c r="W304" s="22" t="n"/>
       <c r="X304" s="61" t="n"/>
@@ -64913,7 +65117,9 @@
       </c>
       <c r="S314" s="22" t="n"/>
       <c r="T314" s="61" t="n"/>
-      <c r="U314" s="22" t="n"/>
+      <c r="U314" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="V314" s="61" t="n"/>
       <c r="W314" s="22" t="n"/>
       <c r="X314" s="61" t="n"/>
@@ -65135,7 +65341,9 @@
       </c>
       <c r="S318" s="22" t="n"/>
       <c r="T318" s="61" t="n"/>
-      <c r="U318" s="22" t="n"/>
+      <c r="U318" s="22" t="n">
+        <v>4</v>
+      </c>
       <c r="V318" s="61" t="n"/>
       <c r="W318" s="22" t="n"/>
       <c r="X318" s="61" t="n"/>
@@ -65527,7 +65735,9 @@
       <c r="T325" s="61" t="n"/>
       <c r="U325" s="22" t="n"/>
       <c r="V325" s="61" t="n"/>
-      <c r="W325" s="22" t="n"/>
+      <c r="W325" s="22" t="n">
+        <v>15</v>
+      </c>
       <c r="X325" s="61" t="n"/>
       <c r="Y325" s="22" t="n"/>
       <c r="Z325" s="61" t="n"/>
@@ -65735,7 +65945,9 @@
       <c r="H329" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="I329" s="22" t="n"/>
+      <c r="I329" s="22" t="n">
+        <v>176</v>
+      </c>
       <c r="J329" s="61" t="n"/>
       <c r="K329" s="22" t="n"/>
       <c r="L329" s="61" t="n"/>
@@ -65745,7 +65957,9 @@
       <c r="P329" s="61" t="n"/>
       <c r="Q329" s="22" t="n"/>
       <c r="R329" s="61" t="n"/>
-      <c r="S329" s="22" t="n"/>
+      <c r="S329" s="22" t="n">
+        <v>168</v>
+      </c>
       <c r="T329" s="61" t="n"/>
       <c r="U329" s="22" t="n"/>
       <c r="V329" s="61" t="n"/>
@@ -65793,7 +66007,9 @@
       <c r="J330" s="61" t="n"/>
       <c r="K330" s="22" t="n"/>
       <c r="L330" s="61" t="n"/>
-      <c r="M330" s="22" t="n"/>
+      <c r="M330" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="N330" s="61" t="n"/>
       <c r="O330" s="22" t="n"/>
       <c r="P330" s="61" t="n"/>
@@ -65967,7 +66183,9 @@
       <c r="P333" s="61" t="n"/>
       <c r="Q333" s="22" t="n"/>
       <c r="R333" s="61" t="n"/>
-      <c r="S333" s="22" t="n"/>
+      <c r="S333" s="22" t="n">
+        <v>40</v>
+      </c>
       <c r="T333" s="61" t="n"/>
       <c r="U333" s="22" t="n"/>
       <c r="V333" s="61" t="n"/>
@@ -66021,13 +66239,17 @@
       </c>
       <c r="O334" s="22" t="n"/>
       <c r="P334" s="61" t="n"/>
-      <c r="Q334" s="22" t="n"/>
+      <c r="Q334" s="22" t="n">
+        <v>88</v>
+      </c>
       <c r="R334" s="61" t="n"/>
       <c r="S334" s="22" t="n"/>
       <c r="T334" s="61" t="n"/>
       <c r="U334" s="22" t="n"/>
       <c r="V334" s="61" t="n"/>
-      <c r="W334" s="22" t="n"/>
+      <c r="W334" s="22" t="n">
+        <v>32</v>
+      </c>
       <c r="X334" s="61" t="n"/>
       <c r="Y334" s="22" t="n"/>
       <c r="Z334" s="61" t="n"/>
@@ -66079,11 +66301,15 @@
       <c r="P335" s="61" t="n">
         <v>110</v>
       </c>
-      <c r="Q335" s="22" t="n"/>
+      <c r="Q335" s="22" t="n">
+        <v>6</v>
+      </c>
       <c r="R335" s="61" t="n"/>
       <c r="S335" s="22" t="n"/>
       <c r="T335" s="61" t="n"/>
-      <c r="U335" s="22" t="n"/>
+      <c r="U335" s="22" t="n">
+        <v>110</v>
+      </c>
       <c r="V335" s="61" t="n"/>
       <c r="W335" s="22" t="n"/>
       <c r="X335" s="61" t="n"/>
@@ -66139,7 +66365,9 @@
       <c r="R336" s="61" t="n"/>
       <c r="S336" s="22" t="n"/>
       <c r="T336" s="61" t="n"/>
-      <c r="U336" s="22" t="n"/>
+      <c r="U336" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="V336" s="61" t="n"/>
       <c r="W336" s="22" t="n"/>
       <c r="X336" s="61" t="n"/>
@@ -66195,7 +66423,9 @@
       <c r="R337" s="61" t="n"/>
       <c r="S337" s="22" t="n"/>
       <c r="T337" s="61" t="n"/>
-      <c r="U337" s="22" t="n"/>
+      <c r="U337" s="22" t="n">
+        <v>22</v>
+      </c>
       <c r="V337" s="61" t="n"/>
       <c r="W337" s="22" t="n"/>
       <c r="X337" s="61" t="n"/>
@@ -66311,7 +66541,9 @@
       <c r="T339" s="61" t="n"/>
       <c r="U339" s="22" t="n"/>
       <c r="V339" s="61" t="n"/>
-      <c r="W339" s="22" t="n"/>
+      <c r="W339" s="22" t="n">
+        <v>192</v>
+      </c>
       <c r="X339" s="61" t="n"/>
       <c r="Y339" s="22" t="n"/>
       <c r="Z339" s="61" t="n"/>
@@ -66365,7 +66597,9 @@
       </c>
       <c r="S340" s="22" t="n"/>
       <c r="T340" s="61" t="n"/>
-      <c r="U340" s="22" t="n"/>
+      <c r="U340" s="22" t="n">
+        <v>138</v>
+      </c>
       <c r="V340" s="61" t="n"/>
       <c r="W340" s="22" t="n"/>
       <c r="X340" s="61" t="n"/>
@@ -66481,7 +66715,9 @@
       <c r="V342" s="61" t="n"/>
       <c r="W342" s="22" t="n"/>
       <c r="X342" s="61" t="n"/>
-      <c r="Y342" s="22" t="n"/>
+      <c r="Y342" s="22" t="n">
+        <v>20</v>
+      </c>
       <c r="Z342" s="61" t="n"/>
       <c r="AA342" s="22" t="n"/>
       <c r="AB342" s="61" t="n"/>
@@ -66759,7 +66995,9 @@
       </c>
       <c r="U347" s="22" t="n"/>
       <c r="V347" s="61" t="n"/>
-      <c r="W347" s="22" t="n"/>
+      <c r="W347" s="22" t="n">
+        <v>68</v>
+      </c>
       <c r="X347" s="61" t="n"/>
       <c r="Y347" s="22" t="n"/>
       <c r="Z347" s="61" t="n"/>
@@ -67429,9 +67667,13 @@
       <c r="R359" s="61" t="n"/>
       <c r="S359" s="22" t="n"/>
       <c r="T359" s="61" t="n"/>
-      <c r="U359" s="22" t="n"/>
+      <c r="U359" s="22" t="n">
+        <v>9</v>
+      </c>
       <c r="V359" s="61" t="n"/>
-      <c r="W359" s="22" t="n"/>
+      <c r="W359" s="22" t="n">
+        <v>8</v>
+      </c>
       <c r="X359" s="61" t="n"/>
       <c r="Y359" s="22" t="n"/>
       <c r="Z359" s="61" t="n">

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -60225,7 +60225,9 @@
       <c r="V227" s="61" t="n"/>
       <c r="W227" s="22" t="n"/>
       <c r="X227" s="61" t="n"/>
-      <c r="Y227" s="22" t="n"/>
+      <c r="Y227" s="22" t="n">
+        <v>700</v>
+      </c>
       <c r="Z227" s="61" t="n"/>
       <c r="AA227" s="22" t="n"/>
       <c r="AB227" s="61" t="n"/>
@@ -62259,7 +62261,9 @@
       <c r="V263" s="61" t="n"/>
       <c r="W263" s="22" t="n"/>
       <c r="X263" s="61" t="n"/>
-      <c r="Y263" s="22" t="n"/>
+      <c r="Y263" s="22" t="n">
+        <v>550</v>
+      </c>
       <c r="Z263" s="61" t="n"/>
       <c r="AA263" s="22" t="n"/>
       <c r="AB263" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -38416,7 +38416,9 @@
       <c r="U10" s="100" t="n"/>
       <c r="V10" s="22" t="n"/>
       <c r="W10" s="100" t="n"/>
-      <c r="X10" s="22" t="n"/>
+      <c r="X10" s="22" t="n">
+        <v>368</v>
+      </c>
       <c r="Y10" s="100" t="n"/>
       <c r="Z10" s="22" t="n"/>
       <c r="AA10" s="100" t="n"/>
@@ -50983,7 +50985,9 @@
       </c>
       <c r="U63" s="22" t="n"/>
       <c r="V63" s="61" t="n"/>
-      <c r="W63" s="22" t="n"/>
+      <c r="W63" s="22" t="n">
+        <v>206</v>
+      </c>
       <c r="X63" s="61" t="n"/>
       <c r="Y63" s="22" t="n"/>
       <c r="Z63" s="61" t="n"/>
@@ -51989,7 +51993,9 @@
       <c r="V81" s="61" t="n"/>
       <c r="W81" s="22" t="n"/>
       <c r="X81" s="61" t="n"/>
-      <c r="Y81" s="22" t="n"/>
+      <c r="Y81" s="22" t="n">
+        <v>3</v>
+      </c>
       <c r="Z81" s="61" t="n"/>
       <c r="AA81" s="22" t="n"/>
       <c r="AB81" s="61" t="n"/>
@@ -60111,7 +60117,9 @@
       <c r="V225" s="61" t="n"/>
       <c r="W225" s="22" t="n"/>
       <c r="X225" s="61" t="n"/>
-      <c r="Y225" s="22" t="n"/>
+      <c r="Y225" s="22" t="n">
+        <v>300</v>
+      </c>
       <c r="Z225" s="61" t="n"/>
       <c r="AA225" s="22" t="n"/>
       <c r="AB225" s="61" t="n"/>
@@ -65181,7 +65189,9 @@
       <c r="T315" s="61" t="n"/>
       <c r="U315" s="22" t="n"/>
       <c r="V315" s="61" t="n"/>
-      <c r="W315" s="22" t="n"/>
+      <c r="W315" s="22" t="n">
+        <v>25</v>
+      </c>
       <c r="X315" s="61" t="n"/>
       <c r="Y315" s="22" t="n"/>
       <c r="Z315" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -49391,7 +49391,9 @@
       <c r="X35" s="61" t="n"/>
       <c r="Y35" s="22" t="n"/>
       <c r="Z35" s="61" t="n"/>
-      <c r="AA35" s="22" t="n"/>
+      <c r="AA35" s="22" t="n">
+        <v>4</v>
+      </c>
       <c r="AB35" s="61" t="n"/>
       <c r="AC35" s="22" t="n"/>
       <c r="AD35" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -48587,7 +48587,9 @@
       <c r="T21" s="61" t="n"/>
       <c r="U21" s="22" t="n"/>
       <c r="V21" s="61" t="n"/>
-      <c r="W21" s="22" t="n"/>
+      <c r="W21" s="22" t="n">
+        <v>44</v>
+      </c>
       <c r="X21" s="61" t="n"/>
       <c r="Y21" s="22" t="n"/>
       <c r="Z21" s="61" t="n"/>
@@ -49391,9 +49393,7 @@
       <c r="X35" s="61" t="n"/>
       <c r="Y35" s="22" t="n"/>
       <c r="Z35" s="61" t="n"/>
-      <c r="AA35" s="22" t="n">
-        <v>4</v>
-      </c>
+      <c r="AA35" s="22" t="n"/>
       <c r="AB35" s="61" t="n"/>
       <c r="AC35" s="22" t="n"/>
       <c r="AD35" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -48579,9 +48579,7 @@
       </c>
       <c r="O21" s="22" t="n"/>
       <c r="P21" s="61" t="n"/>
-      <c r="Q21" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q21" s="22" t="n"/>
       <c r="R21" s="61" t="n"/>
       <c r="S21" s="22" t="n"/>
       <c r="T21" s="61" t="n"/>
@@ -54701,9 +54699,7 @@
       </c>
       <c r="O129" s="22" t="n"/>
       <c r="P129" s="61" t="n"/>
-      <c r="Q129" s="22" t="n">
-        <v>9</v>
-      </c>
+      <c r="Q129" s="22" t="n"/>
       <c r="R129" s="61" t="n"/>
       <c r="S129" s="22" t="n"/>
       <c r="T129" s="61" t="n"/>
@@ -56719,9 +56715,7 @@
       </c>
       <c r="M165" s="22" t="n"/>
       <c r="N165" s="61" t="n"/>
-      <c r="O165" s="22" t="n">
-        <v>2</v>
-      </c>
+      <c r="O165" s="22" t="n"/>
       <c r="P165" s="61" t="n"/>
       <c r="Q165" s="22" t="n"/>
       <c r="R165" s="61" t="n"/>
@@ -60797,7 +60791,9 @@
       <c r="T237" s="61" t="n"/>
       <c r="U237" s="22" t="n"/>
       <c r="V237" s="61" t="n"/>
-      <c r="W237" s="22" t="n"/>
+      <c r="W237" s="22" t="n">
+        <v>357</v>
+      </c>
       <c r="X237" s="61" t="n">
         <v>357</v>
       </c>
@@ -63623,7 +63619,9 @@
       <c r="X287" s="61" t="n"/>
       <c r="Y287" s="22" t="n"/>
       <c r="Z287" s="61" t="n"/>
-      <c r="AA287" s="22" t="n"/>
+      <c r="AA287" s="22" t="n">
+        <v>129</v>
+      </c>
       <c r="AB287" s="61" t="n"/>
       <c r="AC287" s="22" t="n"/>
       <c r="AD287" s="61" t="n"/>
@@ -66899,7 +66897,9 @@
       </c>
       <c r="U345" s="22" t="n"/>
       <c r="V345" s="61" t="n"/>
-      <c r="W345" s="22" t="n"/>
+      <c r="W345" s="22" t="n">
+        <v>66</v>
+      </c>
       <c r="X345" s="61" t="n"/>
       <c r="Y345" s="22" t="n"/>
       <c r="Z345" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -49279,7 +49279,9 @@
       <c r="X33" s="61" t="n"/>
       <c r="Y33" s="22" t="n"/>
       <c r="Z33" s="61" t="n"/>
-      <c r="AA33" s="22" t="n"/>
+      <c r="AA33" s="22" t="n">
+        <v>4</v>
+      </c>
       <c r="AB33" s="61" t="n"/>
       <c r="AC33" s="22" t="n"/>
       <c r="AD33" s="61" t="n"/>
@@ -62555,7 +62557,9 @@
         <v>609</v>
       </c>
       <c r="Z268" s="61" t="n"/>
-      <c r="AA268" s="22" t="n"/>
+      <c r="AA268" s="22" t="n">
+        <v>24</v>
+      </c>
       <c r="AB268" s="61" t="n"/>
       <c r="AC268" s="22" t="n"/>
       <c r="AD268" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -60859,7 +60859,9 @@
       <c r="Z238" s="61" t="n"/>
       <c r="AA238" s="22" t="n"/>
       <c r="AB238" s="61" t="n"/>
-      <c r="AC238" s="22" t="n"/>
+      <c r="AC238" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="AD238" s="61" t="n"/>
       <c r="AE238" s="22" t="n"/>
       <c r="AF238" s="61" t="n"/>
@@ -62727,7 +62729,9 @@
       </c>
       <c r="Y271" s="22" t="n"/>
       <c r="Z271" s="61" t="n"/>
-      <c r="AA271" s="22" t="n"/>
+      <c r="AA271" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="AB271" s="61" t="n"/>
       <c r="AC271" s="22" t="n"/>
       <c r="AD271" s="61" t="n"/>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -61873,7 +61873,9 @@
       <c r="Z256" s="61" t="n"/>
       <c r="AA256" s="22" t="n"/>
       <c r="AB256" s="61" t="n"/>
-      <c r="AC256" s="22" t="n"/>
+      <c r="AC256" s="22" t="n">
+        <v>200</v>
+      </c>
       <c r="AD256" s="61" t="n">
         <v>50</v>
       </c>

--- a/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
+++ b/data/CANTIDADES_MATERIALES_RECIBIDOS_ACTUALIZADO.xlsx
@@ -49563,7 +49563,9 @@
       <c r="Z38" s="61" t="n"/>
       <c r="AA38" s="22" t="n"/>
       <c r="AB38" s="61" t="n"/>
-      <c r="AC38" s="22" t="n"/>
+      <c r="AC38" s="22" t="n">
+        <v>14</v>
+      </c>
       <c r="AD38" s="61" t="n"/>
       <c r="AE38" s="22" t="n"/>
       <c r="AF38" s="61" t="n"/>
@@ -55673,7 +55675,9 @@
       <c r="Z146" s="61" t="n"/>
       <c r="AA146" s="22" t="n"/>
       <c r="AB146" s="61" t="n"/>
-      <c r="AC146" s="22" t="n"/>
+      <c r="AC146" s="22" t="n">
+        <v>25</v>
+      </c>
       <c r="AD146" s="61" t="n"/>
       <c r="AE146" s="22" t="n"/>
       <c r="AF146" s="61" t="n"/>
@@ -55891,7 +55895,9 @@
       <c r="Z150" s="61" t="n"/>
       <c r="AA150" s="22" t="n"/>
       <c r="AB150" s="61" t="n"/>
-      <c r="AC150" s="22" t="n"/>
+      <c r="AC150" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="AD150" s="61" t="n"/>
       <c r="AE150" s="22" t="n"/>
       <c r="AF150" s="61" t="n"/>
@@ -57685,7 +57691,9 @@
       <c r="Z182" s="61" t="n"/>
       <c r="AA182" s="22" t="n"/>
       <c r="AB182" s="61" t="n"/>
-      <c r="AC182" s="22" t="n"/>
+      <c r="AC182" s="22" t="n">
+        <v>19</v>
+      </c>
       <c r="AD182" s="61" t="n"/>
       <c r="AE182" s="22" t="n"/>
       <c r="AF182" s="61" t="n"/>
@@ -62849,7 +62857,9 @@
       </c>
       <c r="AA273" s="22" t="n"/>
       <c r="AB273" s="61" t="n"/>
-      <c r="AC273" s="22" t="n"/>
+      <c r="AC273" s="22" t="n">
+        <v>100</v>
+      </c>
       <c r="AD273" s="61" t="n"/>
       <c r="AE273" s="22" t="n"/>
       <c r="AF273" s="61" t="n"/>
@@ -65823,7 +65833,9 @@
       <c r="Z326" s="61" t="n"/>
       <c r="AA326" s="22" t="n"/>
       <c r="AB326" s="61" t="n"/>
-      <c r="AC326" s="22" t="n"/>
+      <c r="AC326" s="22" t="n">
+        <v>2</v>
+      </c>
       <c r="AD326" s="61" t="n"/>
       <c r="AE326" s="22" t="n"/>
       <c r="AF326" s="61" t="n"/>
